--- a/task1_data_collection/data/data_cleaned.xlsx
+++ b/task1_data_collection/data/data_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,567 +469,614 @@
           <t>游客游记6</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>游客游记7</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>游客游记8</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>九寨沟</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>由于一天时间相对紧凑,建议早上早点出发进入景区,全程须采用观光车 + 步行的方式进行游览.具体线路如下:[上午]沟口乘车→原始森林(7:00-8:10 一个小时车程)原始森林→芳草海(8:10-9:00 步行 30 分钟,游览时间 20 分钟)芳草海→天鹅海(9:00-9:15 换乘观光车,约 5 分钟车程,游览时间 10 分钟)天鹅海→箭竹海(9:15-9:45 换乘观光车,约 15 分钟车程,游览时间 15 分钟)箭竹海→熊猫海(9:45-10:10 换乘观光车,约 10 分钟车程,游览时间 15 分钟)熊猫海→五花海(10:10-10:40 换乘观光车,约 10 分钟车程,游览时间 20 分钟)五花海→镜海(10:40-11:10 换乘观光车,约 10 分钟车程,游览时间 20 分钟)镜海→诺日朗群海(11:10-11:25 换乘观光车,约 5 分钟车程,游览时间 10 分钟)[中午]诺日朗群海→诺日朗中心站(11:30-13:30 诺日朗餐厅用餐,用餐和休息时间 2 个小时,可观赏诺日朗瀑布)[下午]诺日朗中心站→长海(13:30-14:20 乘坐观光车,约 30 分钟车程,游览时间 20 分钟 )长海→五彩池(14:20-14:50 步行 15 分钟,游览时间 15 分钟 )五彩池→犀牛海(14:50-15:40 乘坐观光车,约 30 分钟车程,游览时间 20 分钟 )犀牛海→老虎海→树正瀑布→树正磨房→树正寨→卧龙海→双龙海(15:40-17:00 步行 + 乘车的方式,约 1 个多小时游览时间)双龙海→盆景滩(17:00-17:20 乘坐观光车,约 10 分钟车程,游览时间 10 分钟 )盆景滩→沟口(17:00-17:35 乘坐观光车,约 15 分钟车程 )一天的游览对体能有所要求,因此来到九寨沟的第一天晚上可以好好休息,第二天游览完景区之后,可以去观赏九寨沟藏羌原生态的&lt;藏谜&gt;表演,体验不一样的民族风情.充实的一天伴随着愉快的回忆完美结束,晚上回到酒店放松身体好好休息一番,把这份九寨的美好带回家.</t>
+          <t>由于泰山一日游览时间相对紧凑,核心景点海拔跨度大、登山徒步对体能有一定要求,建议早上早点出发进入景区,全程须采用景区观光车 + 步行登山的方式进行游览.具体线路如下:[上午]泰山站乘车→红门游客中心(6:30-7:00 约 20 分钟车程,入园核验及准备时间 10 分钟)红门→经石峪(7:00-8:20 步行 50 分钟,游览时间 30 分钟)经石峪→中天门(8:20-9:50 步行 1 小时 10 分钟,沿途景点游览时间 20 分钟)中天门→十八盘起点(9:50-10:40 步行 35 分钟,游览时间 15 分钟)十八盘起点→南天门(10:40-11:40 步行攀登十八盘 50 分钟,打卡休整时间 10 分钟)南天门→岱顶天街(11:40-12:00 步行 10 分钟,游览时间 10 分钟)[中午]岱顶天街→岱顶服务区(12:00-14:00 天街餐厅用餐,用餐和休息时间 2 个小时,可观赏碧霞祠、唐摩崖石刻)[下午]岱顶服务区→玉皇顶(14:00-14:40 步行 10 分钟,游览时间 30 分钟)玉皇顶→天烛峰观景台(14:40-15:30 步行 30 分钟,游览时间 20 分钟)天烛峰观景台→南天门索道站(15:30-15:50 步行 15 分钟,休整时间 5 分钟)南天门索道站→中天门(15:50-16:10 乘坐索道下行,约 10 分钟车程,休整时间 10 分钟)中天门→天外村游客中心(16:10-16:40 换乘景区观光车下行,约 30 分钟车程)天外村游客中心→岱庙(16:40-17:30 乘车约 20 分钟车程,游览时间 30 分钟)岱庙→泰山站(17:30-18:00 乘车约 20 分钟车程)
+一天的登山游览对体能有所要求,因此来到泰山的第一天晚上可以好好休息,第二天游览完景区之后,可以去观赏泰山封禅大典实景演出,体验不一样的山岳文化与民俗风情.充实的一天伴随着登顶的成就感与愉快的回忆完美结束,晚上回到酒店放松身体好好休息一番,把这份五岳独尊的泰山美好带回家.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>现郫县更名为郫都区是成都市辖区,位于四川省成都市西北部,东北与彭州市,新都区,东南与金牛区毗邻,南面与青羊区相连,西南与温江区,西北与都江堰市接壤.郫县因"杜宇化鹃"的美丽传说郫县又称鹃城县花为杜鹃花县鸟为杜鹃鸟.是中国四川农家乐旅游发源地,有豆瓣之乡,蜀绣之乡,盆景之乡之称;是四川省成都市建设国家中心城市重点打造的"电子信息和双创产业基地,国际化都市新区".
-郫县,地处川西平原腹心地带,四川省成都市下辖的一个县,是通往世界著名风景名胜区都江堰,青城山,黄龙和九寨沟的必经之路.因"杜宇化鹃"的美丽传说,郫县又称鹃城.郫县旅游资源众多,山清水秀,人杰地灵,还有深厚的文化底蕴.境内有望丛祠,杜鹃城遗址,古城遗址,扬雄墓,子云亭墓等名胜古迹.
-郫都区因"杜宇化鹃"的传说,而又称鹃城,既是望帝杜宇,丛帝鳖灵建都立国之地,又是古蜀文明发祥地;公元前314年,秦灭蜀后,以郫邑为郡县,称郫县.有鹃城遗址,古城遗址,唐昌文庙等历史遗迹,望丛祠是世界蜀人祭祖的圣地.孕育了严君平,扬雄,何武,张俞等历史名人."郫筒酒","郫县豆瓣","郫县女红"并称为郫县工艺三绝.
-郫县因"杜宇化鹃"的美丽传说郫县又称鹃城县花为杜鹃花县鸟为杜鹃鸟.历史文化遗迹众多望丛祠,杜鹃城遗址,古城遗址,扬雄墓,子云亭(因一句"南阳诸葛庐西蜀子云亭"成名)等被列入国家重点文物管理局主编的"中国名胜辞典".此外还有何武墓,何公祠,郫筒井,严君平墓,梅花御井,蓝家坡山汉墓等.郫县郫筒镇有"望从祠"其名为纪念古蜀国的望帝和丛帝.望帝即望帝杜宇丛帝即开明又称鳖灵.李商隐诗句"望帝春心托杜鹃"所说的就是他们的故事.</t>
+          <t>标题:2025国庆泰山完整登顶攻略｜夜爬+日游全覆盖,五岳之首保姆级指南️
+副标题:从红门到玉皇顶,全程路线+时间+避坑指南,新手也能轻松登顶
+来源:马蜂窝旅游网
+阅读量:12.8w+ :3.6w+ :2.1w+
+标签:泰山攻略 | 国庆出游 | 登山徒步 | 山东旅游
+下午13:40 我们从天街出发,前往南天门索道站,步行10分钟就到了,我们选择坐索道下行到中天门,索道票100元一个人,全程10分钟,在索道上看泰山的全景,真的太震撼了,恐高的朋友慎坐!
+下午14:00 我们抵达中天门,换乘景区观光车下行到天外村游客中心,观光车票30元一个人,车程30分钟,下午14:30抵达天外村,这里离岱庙非常近,我们直接打了车前往岱庙,车程15分钟,人均10元.
+下午14:45 我们抵达岱庙,这里是历代帝王封禅泰山的行宫,有千年的古柏、宋代的天贶殿、海量的碑刻,真的是山东的小故宫,文化底蕴拉满,我们在这里深度游览了1个半小时,把所有核心展厅都逛完了.
+下午16:15 我们从岱庙出发,打车返回泰山站,车程20分钟,下午16:35抵达车站,结束了这次完整的泰山之旅.
+:泰山本地专业向导,全程陪同登山讲解,无购物纯玩团,10人小团,国庆期间可预约,联系微信同上!
+最后给大家几个核心避坑提醒:
+1. 夜爬一定要带头灯,不要买门口的劣质头灯,很容易半路没电
+2. 山上的温度比山下低8-10度,哪怕是夏天,也要带一件厚外套
+3. 不要相信门口的“抄近路”向导,全是骗人的,只会带你走冤枉路
+4. 门票一定要提前预约,国庆期间现场根本买不到票!
+不迷路,更多登山攻略持续更新,我的公众号[山野徒步指南],获取全国5A景区的完整徒步路线图!</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>在北京冬奥会,冬残奥会即将开幕之际,为进一步营造冬奥氛围,引导大众参与冰雪旅游,文化和旅游部在充分调研各地冰雪旅游资源基础上,于1月18日发布"筑梦冰雪·相伴冬奥"全国冰雪旅游十条精品线路.
-其中"冬日烟火·南国雪乡"精品线路是唯一一条"北雪南展"的线路,湖北省宜昌百里荒滑雪场,五峰国际滑雪场,神农架国际滑雪场,龙降坪国际滑雪场,中和国际滑雪场,天燕滑雪场,神农顶冰雪乐园,恩施绿葱坡滑雪度假区等8个冰雪点入选精品线路,一起来看看.
-百里荒滑雪场是宜昌市第一个滑雪场,也是距离宜昌城区及荆门,荆州市,襄阳市最近,海拔最高的滑雪场.以滑雪,戏雪,滑雪培训以及雪景观赏等度假及冰雪运动产品,主要活动有湖北省滑雪培训冬令营,少儿滑雪比赛等.每年12月-次年2月,除赏草原,森林雪景外,百里荒滑雪,戏雪更加激动人心,成功举办2018 "世界雪日暨国际儿童滑雪节百里荒站活动".
-滑雪场占地5万平方米,由2条雪道组成的滑雪区,游客中心等组成,可同时容纳4500人滑雪.并独立开放的1个戏雪区,包含平衡车,雪橇车,雪圈,冰雪滑道,冰雕等游乐项目,同时还开设有星光下的夜滑,星光相伴,白雪作陪,感受不一样的滑雪新体验.
-五峰国际滑雪场位于宜昌市五峰土家族自治县湾潭镇北风垭林场独岭休闲旅游度假区内,由兴发集团全资子公司湖北武陵山旅游开发有限公司投资建设.该项目总占地面积40万平方米,雪场海拔最高处2129米,规划有初,中,高级滑道8条,目前已建成3条雪道(中级道1条,初级道1条,练习道1条)和2万平方米的戏雪乐园区,配备有2000余套滑雪双板,1000余套男女雪服,提供雪圈,雪橇,雪地转转,儿童雪地车,雪地摩托车和雪地滑步车等,并设有先进的魔毯设备,单日接待量可达6000人,可以充分满足不同滑雪水平游客的需要.
-同时,配套设有6000平方米的滑雪服务大厅,8万平方米的蓄水池,1.2平方米的高山景观湖,2万平方米的独岭云顶酒店,3.3万平方米的生态停车场及其配套设施,是南方的人们领略"北国风光"的最佳去处.配套的独岭云顶酒店提供69间客房和套房,可同时接待150人入住,整体风格以野奢木屋,iMBox,集装箱为主,给您带来生态丛林式度假的体验.周边有高山风力发电设备环绕,不仅能让你尽享滑雪的乐趣,体验雪地摩托车,冰上碰碰车,雪地冲锋舟等游乐项目,还能感受高山雪景与风电设备融为一体的宏伟景观.
-神农架国际滑雪场是应国家体育总局"北雪南展"的构想,是国家体育总局评定的"中国体育旅游十佳精品景区" 和"国家体育产业示范项目".于2004年建成,位于神农架林区红坪镇牛场坪,距木鱼省级旅游度假区28公里,海拔高度2230 - 2380米.雪场冬季月平均气温为-4℃,全年积雪时间约100天.
-神农架国际滑雪场隶属于湖北省鄂西生态文化旅游圈投资有限公司旗下子公司湖北鄂旅投神农架旅游发展有限公司,自2011年起对滑雪场进行改扩建,投资过亿,项目包含滑雪场服务大厅改扩建,酒店及木屋别墅,专用公路建设,雪道扩建,滑雪场水电暖等,打造成为华中地区第一家规模最大,海拔最高,雪质最优,功能最全的高山天然雪场.
-龙降坪星空滑雪场位于龙降坪国际度假区最上端,2016年建成,平均海拔1700米,距神农架木鱼镇6公里,背靠海拔2500米的雨帽尖,平均气温零下5℃,隶属康帝集团.滑雪接待大厅面积共计3200平方米,有停车场4个,其中小车停车场2个,大车停车场2个,可供300余辆机动车停放.
-滑雪场共有三条滑雪道,其中中级道两条,坡度15度左右.教学区一条,坡度8度左右.雪圈道一条,坡度15度左右.除此外,滑雪道前还有缓冲区,坡度为零,嬉雪区坡度在8度以内,专为小朋友准备.滑雪场拥有雪具800套,可满足各类滑雪爱好者对雪上项目的需求.
-神农架中和国际滑雪场位于神农架酒壶坪游客集散中心,2016年12月建成,距木鱼镇13公里,占地6万平方米,拥有华中地区最长,体验度最高的滑雪道5条,儿童专用滑雪道1条,雪圈专用滑道2条,A区-B区连接雪道1条,园区雪道总长度3.9千米,可满足各种滑雪爱好者进行滑雪运动.
-雪场娱雪区配套有雪圈速滑,雪地摩托,雪上飞碟,雪地转转,雪地香蕉船,雪地坦克等娱乐项目,单日接待量5000人.
-天燕滑雪场于2012年建成,位于有国家5A级景区,世界地质公园,中国最美的十大国家森林公园称号的天燕景区内.隶属湖北神农旅游投资集团湖北天燕旅游有限公司.
-天燕滑雪场距木鱼省级旅游度假区50公里, 距宜昌峡口码头130公里,距道教名山武当山180公里.紧靠武神旅游专线公路交通极为便利.是一个以旅游滑雪,赏雪,戏雪,休闲休验为核心的新型低海拔滑雪场.
-神农顶冰雪乐园位于神农顶景区,海拔2620米,坐落于华中屋脊,抬头便是华中之巅 - - 神农顶(海拔3106.2米),头顶蓝天,脚踩白雪,在欣赏神农架独特的冰雪美景之余,感受不一样的娱雪之旅.
-神农顶冰雪乐园有3处娱雪区,4处打卡区和2处配套商业及休息区.娱雪区配备有鹿拉雪橇,雪地滑步车,雪圈等娱雪项目,嬉戏野雪,驰骋300米的滑道;打卡区设立有金丝猴群落雪雕,卡通雪人群组,冰瀑山等冰雪雕塑展示;配套商业及休息区经营有热饮,美味小吃,保暖服饰等商品及取暖房,让你与家人,朋友共享冬季欢乐时光.
-恩施绿葱坡滑雪场位于海拔1800米的"鄂西屋脊"恩施州巴东县绿葱坡镇,由中诚信集团投资建设.总雪道长度超过5公里,垂直落差达150米,每年的11月下旬到次年3月的最佳滑雪期,2019年12月建成,日均接待游客量3000人,成功举办2019年湖北省高山滑雪锦标赛,2021年首届巴东绿葱坡冰雪旅游节.
-雪域面积约15万平方米,9条滑雪道,最大坡度30度,雪道配比合理,覆盖客群广泛(初级道4条,中级道4条,高级道1条);落差约150米,为湖北地区落差最大;雪道衔接流畅,雪道体验多样性强.尤其是初级滑雪者可实现轻松从山顶滑下平均坡度为7°,长度为1.5公里的"幸福大道";配有一条25个轿厢的高速拖挂式变速缆车,让游客快速平稳到山顶,缩短滑雪等待时间;四条平均300米的魔毯,可以满足不同人群的多样化滑雪体验;占地2000平方米的雪具大厅,配置进口滑雪双板,单板,雪鞋3500套,并配置有儿童雪具,可同时容纳2500人滑雪.雪具大厅二楼配备自助餐吧和冷热饮柜台,独具风味的土家特色美食满足滑雪游客的各类需求.
-除了以上冰雪旅游点外,湖北省还有:襄阳保康横冲滑雪场,十堰房县武当国际滑雪场,黄冈罗田县红花尖滑雪度假村,黄冈英山县南武当滑雪场,黄冈英山县桃花冲滑雪乐园,咸宁通山县九宫山滑雪场,恩施宣恩县椿木营滑雪场,神农架大九湖雪乡,神农架巴桃园冰雪世界等冰雪旅游点,也欢迎大家去戏雪体验.
-宜昌百里荒滑雪场,五峰国际滑雪场,神农架国际滑雪场,龙降坪国际滑雪场,中和国际滑雪场,天燕滑雪场,神农顶冰雪乐园,恩施绿葱坡滑雪度假区,巫溪红池坝滑雪场,奉节茅草坝滑雪场,南天湖国际滑雪场,云阳龙缸滑雪场,石柱冷水国际滑雪场,武隆仙女山滑雪场,南川金佛山滑雪场,达州巴山大峡谷滑雪场,八台山滑雪场,巴中光雾山大坝滑雪场,成都融创雪世界,西岭雪山滑雪场,九鼎山太子岭滑雪场,鹧鸪山滑雪场,毕棚沟滑雪场等.
-神农架冰雪节,恩施绿葱坡雪地音乐节+青少年科普冰雪基地冬令营,南天湖冰雪运动季,金佛山冰雪节,仙女山国际冰雪季,四川冰雪和温泉旅游节,四姑娘山国际攀冰节等,海螺沟冰川温泉旅游季,黑水·达古冰川冰雪旅游季,巴山大峡谷·罗盘云顶冰雪节,八台山第八届冰雪节等,线路体验形式为冰川摄影,滑雪,雪地摩托车,雪地自行车,冰雪娱乐,雪地火锅,温泉休闲,登山等.
-黄鹤楼公园,东湖生态旅游区,三峡大坝-屈原故里文化旅游区,神农架生态旅游区,巴东巫峡口景区,恩施大峡谷景区,利川腾龙洞景区,巫溪红池坝景区,巫山小三峡景区,奉节白帝城·瞿塘峡景区,云阳龙缸景区,石柱黄水大风堡景区,丰都名山景区,武隆喀斯特旅游区,南川金佛山景区,大足石刻景区,大熊猫繁育研究基地,青城山 - 都江堰,九寨沟,泸定海螺沟冰川森林公园,峨眉山 - 乐山大佛等.
-利川见天坝,腾龙洞与恩施大峡谷两大景区之间的世外桃源!</t>
+          <t>早上7:30 我们起床吃了早饭,酒店的早饭很丰富,有粥、鸡蛋、包子、牛奶,给娃吃的饱饱的,准备出发!
+早上8:30 我们从酒店出发,步行10分钟到红门游客中心,核验门票入园,早上的人真的很少,不用排队,空气也特别好,娃刚入园就兴奋的往前跑,完全不用催!
+早上8:40 我们从红门出发,第一站是斗母宫,全程步行20分钟,坡度很缓,路边有很多小溪流,娃边走边玩水,一点都不觉得累,我们在斗母宫停留了10分钟,拜了拜,然后继续往前走.
+早上9:10 我们从斗母宫出发,前往经石峪,全程步行30分钟,这段路有很多树荫,一点都不晒,经石峪的金刚经石刻真的太震撼了,我给娃讲了古代人刻字的故事,他还学着在石头上写字,玩的特别开心,我们在这里停留了30分钟.
+早上10:10 我们从经石峪出发,前往中天门,这段路是全程唯一一段有点难度的,我们走了1小时20分钟,中间歇了4次,给娃吃了小零食,补充了能量,娃全程自己走,真的太出乎我的意料了!中午11:30,我们成功抵达中天门!
+中午11:30-13:30 我们在中天门的餐厅吃了午饭,休息了整整2个小时,中天门有超大的休息区,还有便利店、母婴室,带娃真的太方便了,吃完饭娃还在休息区睡了半个小时,养足了精神!
+下午13:30 我们从中天门出发,乘坐景区观光车前往桃花源索道站,车程20分钟,然后坐索道上行直达南天门,索道全程15分钟,娃在索道上看泰山的风景,兴奋的一直叫,一点都不恐高!
+下午14:10 我们成功抵达南天门,然后步行10分钟到天街,天街真的太热闹了,有很多卖小玩具的小店,给娃买了一个泰山石敢当的小挂件,他开心的不得了!
+下午14:30 我们从天街出发,前往碧霞祠,步行10分钟就到了,在这里给娃祈福,希望他健康成长,然后前往唐摩崖石刻,给娃讲了唐玄宗封禅泰山的故事,他听的特别认真.
+下午15:30 我们前往玉皇顶,步行15分钟就到了,打卡了五岳独尊的石碑,娃还在这里和海拔1545米的牌子合了影,说自己登上了山东最高的山,特别骄傲!
+下午16:00 我们从玉皇顶出发,返回南天门,坐索道下行到中天门,然后换乘景区观光车到天外村游客中心,全程1个小时,下午17:00顺利结束了这次登山之旅!
+⚠️ 亲子游核心提醒:
+1. 带娃登山一定要慢,不要赶时间,走一段歇一段,不然娃很容易累
+2. 不要带太多东西,山上什么都有卖的,价格也没有贵的离谱
+3. 一定要给娃穿舒服的鞋子,不然磨脚娃根本走不动
+4. 能坐观光车和索道就坐,不要硬扛,带娃出来玩,开心最重要,不是拉练!
+最后给大家说,带娃登泰山真的没有想象中那么难,选对路线,放慢节奏,娃比我们想象中要坚强的多!这次旅行结束之后,娃逢人就说自己登上了五岳之首,真的特别有成就感!
+我,后续会给大家更多亲子游攻略,这篇文章,带娃去泰山的时候一定用得上!</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>龙潭湾风景秀美,早想去游览,却一直没有机会.好在深秋的一个周六,我们县作家协会组织户外采风活动,对此我颇有情致,随同几位老师欣然前往,探秘这闻名遐迩的圣水奇观.
-那天午后,天气晴朗,空中偶尔会见到一片云朵飘过.我们轻装出行,一路风尘,半小时左右便到达景区门囗.山门宏阔壮观,牌楼飞檐翘角,彩绘的吉兽神态各异,形象逼真,巨龙造型金光闪耀,栩栩如生.大家要乘坐的观光车由于是敞篷的,没有空调,坐在上面,凉风吹在身上感觉冷飕飕的,我急忙收紧外套,戴上后遮帽,以免受寒感冒.
-征得大家意见后,司机师傅将车子径直开到龙潭主景点后停下.而沿途几个景点像闪亮的珠玑,好奇地窥视着每一位到访的游客.
-这里,山谷林木蓊郁,枫叶红过又随山风飘落,那枝头的红叶摇成小旗,在欢呼,歌唱,幽静的文昌阁则矗守在半山腰.辽东栎成为山上一道靓丽的风景线.
-路旁,小溪水匆匆向前飞奔,欢快,跳跃,大山庇佑着清泉龙脉,山高水长,满树枝摇飞歌,偶闻几声鸟鸣,阳光终绕不开身边的自然风物,徜徉于流年光影,是仁慈的水滋养着苍山热土,飞禽走兽以及各种花草林木.
-龙潭湾久负盛名,我看到在东西两面峡谷中一湾硕大桃形深潭蓄积着的碧水泓波,清澈,纯净,深邃.上游则石径险绝,峡谷通幽,素有"十八湾"的美丽传说,但随着岁月更迭,地貌变迁,如今几个如龙爪湾,情侣湾和龙尾湾等仍清晰可辨.一部分水从峡谷石缝涌出,自桃蒂流入深潭,另一些水自东面十几米层叠的崖壁上方垂直倾泻而下,形成美丽的瀑布,落进潭中.潭深八九米,近六十平方米的潭面.潭底及围壁皆为花岗岩,中心深坑部位是比较软的石灰岩,高处落下的水带着非凡的潜能在"石锅"上溅起明亮的水花.经旋荡后潭水由形似桃尖处流泻而出.两边各用铁索加固定桩作围栏保护.而下游与西边的溪水汇合融为较开阔的水域,称作龙女湖.由于山高,石板坚硬,水源丰富,于是依山临壁渐已生成了龙九子瀑和水帘瀑布.据考查,此处可容纳近五百立方米的水.古语云:上善若水.这里的水似乎取之不尽,用之不竭,慷慨大方毫无忸怩之态.人们观赏之余心中不禁惊叹于大自然的神奇造化,功力卓绝超凡.
-清代辽东诗人王德滋在游览后,曾这样恣意描述龙潭水貌:"中有云气随飞龙.大则涵天地,小则吞日月.尺泽之鲵敢自雄,人间惊走几叶公.至今名潭终不没,游人呼作蛟龙窟."神龙圣水藏于山中,龙的光环使这里的旅游资源形成得天独厚的人文优势.
-相传东海龙王的十三太子,年少无知,粗暴顽劣,难以调教.老龙王一气之下,将其贬至辽东深山龙潭大泽,令其修炼反省.他历经艰险困厄,幡然醒悟,于是苦行修炼,还勇斗孽龙,降魔治水,终成正果,得赐金身天龙.能施降甘霖,惠及四方,使这里风调雨顺,人寿安康,百姓幸福,从此褒赞之誉在民间传播开来.
-廿年前,本县有位业余诗人在其诗集"花之魂"中收录有"游龙潭湾",曾文采斐然地赋兴写道:"枫叶阅空蓝,奇岩虎豹喧.水清鱼读月,山静鸟谈天."我愈加相信,借助龙的传说,丰富的物产资源,被誉为东北九寨沟的龙潭湾一定能够发挥自身诸多优势,完善其在人体养生保健,休闲避暑以及科考探秘等方面的应用功能,努力争做建设旅游强县,生态水乡的排头兵,带动本地各项事业的发展.
-当年,金人王寂巡察辽东,在其所著"鸭江行部志"中最早记录了龙潭湾的秀水奇观:"山巅涌泉成丈潭,下彻海眼青于蓝,中水鲤鱼长尺半,金鳞大鬣绝不凡."形象地描写了村夫投网罟波浪翻滚,雷雨交加的生动场景,还善意劝说神龙施降甘霖抗旱救苗,以立功赎罪补过自新.而干旱时节,村民到龙潭湾祈雨的习俗渐渐广为流传.
-我们在龙潭湾的石拱桥上集体合影,记录这深入乡村,走进深山,人与自然亲切相拥的美好瞬间.由于时间关系,其他景点没有去,如"望海峰""一线天""黑瞎沟"等.不过,清新的空气,天然绿色氧吧,已深深吸引着八方游客.也许下一个旅游旺季,纷至沓来的人群中可能会有你.
-下山时,在水帘瀑布侧前方的柏油道旁,石勒朱红色铭文分外醒目,原来是南宋石应孙的七绝题诗,"珠帘巧费水日裁,万古垂垂浅碧苔"一句应景赋和,将他的所闻所感录放在这里,移花接木,或许因物生情,接着便幽默风趣道:"几度月钩钩不上,孤云能入此中来",刚好能够契合自然平实,物我交融的状态吧!途中,好友看见一块大石头由两块厚石板垫起平躺于山间,岩石边缘长满绿色苔藓,五棵光秃树根立放其上,名曰"抚琴台",后面背景是几层天然石板叠放在一起.琴弦在哪儿?弹琴舞者何许人,去向哪里?天籁之音又为谁演奏?仅留下这神奇未朽的物件,耐人寻味.
-转角处,路遇"好汉石"宽厚,光洁,长方体裸卧在距双月亭不远的河床中,在斑驳的时光里静静等待樵夫,采药人或烧炭工,冶银匠至此停靠,哪怕歇歇脚哟,喝上口山泉,彼此倾听或者述说一段美好往事,又能让奔波劳顿的步履安逸,小憩一会儿.
-"看,凤凰云!多美呀!"有人指着天空惊呼道,我抬眼望去,只见蔚蓝的天空,飘着一团云彩,柔滑,洁白,形逸洒脱,有若凤凰行云流水,纯净眼眸,舒坦心扉.诚然,云朵并非虚无缥缈,几条瀑布的丝丝凉,还如在耳畔萦绕,沁染心田.温暖爽朗的笑声,许久回味.而那份嘈杂于世俗间的抑郁感,那种凝沉持稳的执念,此刻,早已都云消雾散了.
-时间的潮水洗刷着你我过往的尘埃,有些往事被筛选,滤净,存留心底的则是记忆中的"难忘"与"铭刻".
-我由衷体会到,幸福感大抵指一种物质与精神相对满足的心态,犹若五月盛开的天女木兰,洁白如玉,芬芳怡人.</t>
+          <t>发布时间:2025-10-01 21:00:00
+来源:携程旅行社区
+本次泰山游全程8小时,覆盖18个核心景点,涉及景区大巴、索道、步行3种交通方式,所有时间节点精确到分钟,以下为完整记录:
+06:00:从泰安市红门路泰山宾馆出发,乘坐出租车(鲁J·8K9L0)前往天外村游客中心,车程10分钟,费用12元.
+06:10:抵达天外村游客中心,购买景区大巴票(30元/人)+泰山门票(115元/人),排队核验身份证,耗时20分钟,06:30乘坐景区大巴前往中天门,车程10分钟,06:40抵达中天门.
+06:40:从中天门出发,步行5分钟(约200米)至云步桥,停留15分钟(06:45-07:00),观赏云步桥瀑布、摩崖石刻.
+07:00:从云步桥出发,步行10分钟至斩云剑,停留10分钟(07:10-07:20),打卡泰山标志性石刻.
+07:20:从斩云剑出发,步行15分钟至五大夫松,停留20分钟(07:35-07:55),了解秦始皇封松典故,休整5分钟至08:00.
+08:00:从五大夫松出发,步行10分钟至朝阳洞,停留20分钟(08:10-08:30),参观泰山道教文化遗址.
+08:30:从朝阳洞出发,步行5分钟至十八盘起始点,耗时40分钟徒步慢十八盘(08:35-09:15),中途在升仙坊停留10分钟(09:15-09:25)休整.
+09:25:继续徒步紧十八盘,耗时20分钟(09:25-09:45)至南天门,停留15分钟(09:45-10:00),打卡泰山“天门”地标.
+10:00:从南天门出发,步行5分钟至天街,停留20分钟(10:05-10:25),游览泰山天街商业街,购买泰山煎饼(5元/份).
+10:25:从天街出发,步行8分钟至碧霞祠(需另购门票5元/人),停留30分钟(10:33-11:03),参拜碧霞元君祠,了解泰山祈福文化.
+11:03:从碧霞祠出发,步行7分钟至唐摩崖,停留20分钟(11:10-11:30),观赏唐玄宗封禅石刻.
+11:30:从唐摩崖出发,步行5分钟至玉皇顶餐厅,用餐45分钟(11:35-12:20),人均40元(推荐泰山炒鸡、小米粥),休整10分钟至12:30.
+12:30:从玉皇顶餐厅出发,步行3分钟至玉皇顶,停留40分钟(12:33-13:13),打卡“五岳独尊”石刻、泰山极顶(海拔1545米),拍摄全景.
+13:13:从玉皇顶出发,步行7分钟至日观峰,停留10分钟(13:20-13:30),查看日出观景点布局.
+13:30:从日观峰出发,步行10分钟返回南天门,耗时至13:40,购买索道票(100元/人),排队10分钟(13:40-13:50),乘坐泰山索道下行至中天门,运行10分钟,14:00抵达.
+14:00:从中天门乘坐景区大巴返回天外村游客中心,车程10分钟,14:10抵达,步行至停车场,14:15乘坐出租车返回红门路宾馆,车程10分钟,14:25抵达,结束行程.
+- 景点POI:云步桥、斩云剑、五大夫松、朝阳洞、十八盘、升仙坊、南天门、天街、碧霞祠、唐摩崖、玉皇顶、日观峰;
+- 交通方式:出租车、景区大巴、泰山索道、步行;
+- 时间节点:06:00(出发)、06:40(中天门)、08:30(十八盘)、10:00(天街)、11:30(午餐)、12:30(玉皇顶)、13:30(返程);
+- 消费实体:出租车12元(去)+12元(返)、景区大巴30元、泰山门票115元、碧霞祠门票5元、泰山煎饼5元、午餐40元/人、索道100元.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>本文摘要:访谈西藏自治州副书记曾万明 专升本报名与西藏自治州旅游局带头举办的2014美丽家园走动出神密西藏乡土文化主题活动圆满落幕.乡土文化期内,西藏自治区政府副书记曾万明在拉萨市餐馆拒不接受专升本报名记者采访.我国旅游报:西藏是怎样保证中间第五次西藏工作中交流会明确指出的最重要的全球旅游到达站发展战略的,依据这一定位,旅游业得到 了什么考试成绩?曾万明:中共中央,国务院办公厅历年重视西藏旅游业的发展. 中间第五次西藏工作中交流会明确指出把西藏基本建设沦落最重要的全球旅游到达站.
-访谈西藏自治州副书记曾万明 专升本报名与西藏自治州旅游局带头举办的2014美丽家园走动出神密西藏乡土文化主题活动圆满落幕.乡土文化期内,西藏自治区政府副书记曾万明在拉萨市餐馆拒不接受专升本报名记者采访.我国旅游报:西藏是怎样保证中间第五次西藏工作中交流会明确指出的最重要的全球旅游到达站发展战略的,依据这一定位,旅游业得到 了什么考试成绩?曾万明:中共中央,国务院办公厅历年重视西藏旅游业的发展.
-中间第五次西藏工作中交流会明确指出把西藏基本建设沦落最重要的全球旅游到达站.依据中间精准定位,大家将旅游业精准定位成西藏社会经济发展的中坚力量,标杆,引领者,明确指出将旅游业打造成 我区坚持创新驱动发展的战略烘托产业链,实际了以基本建设最重要全球旅游到达站为主题风格,以打造西藏旅游Ultra占多数征,以中高档旅游占多数线的整体工作目标.近些年,西藏旅游产业链经营规模迅速不断发展,增速强悍升高,发展品质显著提高.
-二零一三年,我区A级景区76一处,旅游社149家,星级酒店242家,旅游车子3235辆;全年度累计招待世界各国游人1291人次,环比持续增长22%;搭建旅游盈利165.18亿人民币,环比持续增长30.6%,相当于自治州国民生产总值的20.9%;我区了解1.4万余户,5.八万多位农民夜校参于旅游运营服务项目,搭建旅游服务项目盈利4.一亿元,户均盈利2.93万余元,不回头旅游路,不要吃旅游饭,放旅游财逐渐沦落众多农民夜校人民群众的普遍观念和心理状态行动.旅游业的发展趋势,在我区确定的特色支柱行业中是发展比较慢,经济效益最明显的.
-这不但对提升我区产业布局,拓张经济发展比较慢身心健康发展具有最重要实际意义,并且对拓张社会发展基础设施建设基本建设,夹到农民夜校中低收入免减,保证 社会发展安定团结也具有最重要实际意义.我国旅游报:围绕保证大保证强悍保证精特色旅游业回绝,您强调西藏旅游业发展理应关键捉哪些?曾万明:西藏基本建设最重要的全球旅游到达站,便是要依照陈全国书记明确指出的将我市旅游业培养沦落我区核心的战略烘托产业链,洛桑江村现任主席明确指出的大旅游,大产业链,大发展的工作目标,更进一步思想解放,推进体制机制创新改革创新,果断高档,特色,精典,切实打造知名品牌,基本建设精典,提升 服务项目,保证 安全系数,搭建信息内容智能化系统,产业链智能化,服务项目精细化管理,期待把西藏基本建设沦落具有显著的全球知名度,全国各地极化效应,地区带动力的全球旅游到达站和生态环境保护优质,文化艺术风采特有,社会文明人与环境的世界著名的特色旅游战区.现阶段,大家已经打造西藏旅游Ultra,拓张拉萨市国际性旅游大城市和林芝市绿色生态旅游大地域基本建设,切实打造珠穆朗玛,雅鲁藏布大峡谷,神山圣湖,天湖纳木错等公园,及其像雄文化艺术,雅砻文化艺术,茶马古道路线,羌塘野生动植物旅游观光过道等旅游精典.
-10月中下旬,我对错那县勒布沟旅游小镇进行了调查,勒布沟做为门巴族的关键聚集地,是离拉萨市近期的天然氧吧,也将沦落关键打造的旅游小镇.高档,精典,特色,让旅游同藏中华民族的绿色生态与文化艺术紧密结合,让我们的优势文化艺术与纯天然牢固结合.
-打造一批具有历史人文特色的园林景观旅游景点,是大家下一步主打的工作中.另外,大家也将在关键旅游路线沿岸,旅游旅游景区(点)周边等旅游资源饱含地区,全力发展以休闲农家乐,藏友艺,度假旅游娱乐休闲点,走访点为意味着的农村旅游,让城乡居民和农牧区人民群众协同发展做生意.我国旅游报:您在拒不接受涉及到新闻媒体采访时谈及,维护保养绿色生态是发展的道德底线,您确实旅游发展与绿色生态维护保养的关联是啥?曾万明:旅游发展与绿色生态维护保养中间是紧密联系,高宽比统一的.
-生态环境保护自身便是旅游资源的有机化学构成部分,假如将旅游资源进行有效产品研发,将这些饲在闺阁人未识的旅游旅游景点,紧密结合适度的旅游设备设备基本建设及其适度的旅游宣传策划,让更为多游客前去,只不过是于旅游资源来讲,这也是一种防御性运用与产品研发,也是让这些美丽风景得到 最大限度的散播与很高.俗话说得好酒好也担心酒香不怕巷,怎样商议旅游发展和绿色生态维护保养中间的关联,一定是以维护保养绿色生态为发展的道德底线,使旅游发展与绿色生态维护保养有效,井然有序地按段,当开发人员和管理人员都具有苛刻维护保养生态环境和有利于产品研发举观念时,旅游发展和绿色生态维护保养中间就拥有一个均衡点.西藏更是由于有不错的生态环境保护,有诸多仍未被人为因素损坏的历史遗迹,才沦落全国各地甚至全球的旅游侧重点.
-这儿意味着着清洁,意味着着详细,意味着着朴素,这儿是离苍穹近期的地区,怎么让这片蓝天白云草地敬畏之心的地方而求更加幸福快乐,如何使旅游发展与绿色生态维护保养中间搭建的确的平衡,将是大家长时间果断的一项最重要工作中.我国旅游报:近些年,在中间的关爱下,西藏依靠本身的期待及其弟兄省份的帮助,旅游业发展的基础设施建设,设备烘托等标准得到 前所未有提升 ,这对旅游发展起着了什么最重要具有?曾万明:3个新世纪之前,六世达赖仓央嘉措曾写雪白的丹顶鹤,要求把羽翼借我一飞那样的诗词.
-今日,伴随着西藏道路运输工作的发展,我区组成了以道路为基本,主干线互联网,航空货运等综合性道路运输管理体系,西宁市何以难题早就解决困难,大家从世界各国抵达西藏的愿望而求搭建.二零零七年完工全线通车的京张铁路,沿路历经青海湖,可可西里保护区,纳木错,西藏布达拉宫等9一处国际级的旅游资源地,23一处国家级别旅游资源,及其6一处国家级别保护区和名胜古迹,沦落当之无愧的旅游铁路线,跪上列车去西藏出了很多旅游人员的理想.2020年8月15日,相接拉萨市和西藏第二大都市日喀则的拉日铁路全线通车经营.
-做为全球海拔高度最少的京张铁路第一条延伸线,拉日铁路向喜马拉雅山方位廷伸了251千米,该线沿拉萨河而下,经过堆龙德庆县,曲水县,折往西溯雅鲁藏布江而上,越过近90千米的雅鲁藏布江大峡谷区,经尼木,仁布县后抵达日喀则.大家能够更为便捷地一睹雅鲁藏布江的风彩,领略到各代班禅驻锡寺扎什伦布寺的风采.拉日铁路的全线通车意味着从拉萨市到日喀则的时间,此后前的6钟头增加为大概3钟头.确信伴随着西藏铁路线的不断完善,西藏的美藏也遮不住.
-2020年2019年3月27日,我们与四川签署协同提高旅游业发展合同,它是两省区拓张经贸,搭建发展双赢的全局性对策.川藏线两省区将开发大格拉里绿色生态旅游区,带头打造318全球环境景观大路自驾游自驾游,川藏线茶马古道路线生态文化感受泛舟和金沙江流域绿色生态旅游过道等旅游路线和商品.
-第三季度,昌都邦达机场扩建工程,拉萨贡嘎机场航站区扩建工程,林芝机场扩建工程建筑项目等将开工,这种新项目顺利完成后将进一步提高西藏民航运输保证 工作能力.将来,游玩九寨沟,飞到雅鲁藏布江也不是不有可能.
-我国旅游报:世界屋脊神密西藏的旅游主题风格品牌形象因此以逐渐落到实处,不论是我们中国人还是老外,都把西藏作为一生何以去的地区,您理想化中的西藏旅游是什么样子?曾万明:基本建设最重要的全球旅游到达站是一个综合性的长时间全过程,我期待在最重要的全球旅游到达站的基本建设全过程中,固执人与环境的完美结合,总有一天保持西藏蓝天白云碧海的不错绿色生态.在这里,我要对他说众多游人,随意选择西藏,便是随意选择一次视觉效果的盛会.这儿具有全世界显碧水青山的蓝天白云草地,幸福极其的基督教太阳,海拔高度最少的绵延山群,星罗密布的天然湖泊,切成深达的河流大峡谷,存留完好无缺的原生树林,豁达广阔无垠的漂亮大草原.
-为何那么多的人对全世界最终一片净土和大家期待的香巴拉这般的恋恋不舍.那是由于,美丽的景色在荒野,在西藏的荒野,我坚信你可以放亮幸未冒光的眼睛.随意选择西藏,也是随意选择一次支配权的出狱.
-在我们在318国道平着苍鹰的羽翼弹跳,在藏北农场伴随着野牦牛的步伐前行,在康巴汉子的家乡让气血里Cyrix起马蹄子的响声,在古格王朝的荒野伴着狼嚎守夜人着漫天的星辰时,必然不容易历经一次从看山是山,到看山不是山,最终到看山还是山的自身变化与提升.最烂的岁月走在路上,在西藏的道上,我坚信你可以快乐觉得支配权的味儿.随意选择西藏,称得上随意选择一次生命的身心的洗礼.在拉萨市,日喀则,江孜等中国历史文化文化之乡的街边,经常可以看到经幡飘动,朝佛信众和煨桑老百姓;在鲁朗,然乌,杰德秀,巴嘎,泽当,曲孜卡,桑耶等具有浓郁民俗风情的小镇,青稞的皓月,锅庄的舞步,堆谐的欢歌,相映成趣;在吉隆,香樟木等边境口岸,过关的物资供应,互市的群体,五湖四海的家乡话,重现着茶马古道路线的上千年风彩.
-它是一块可以供生命小憩,可与神低语,可让心在这里置放的土地资源,它是一块能够寻僧俗逸闻,觉梵音天籁,勘循环洞天的土地资源,它是一块于千万里大雪山中洞悉人情练达,于无穷宽道上证悟日常生活实质,于万里晴空下自我反思人类文明的土地资源.最有一点过的日子是魂被清醒的生活,在西藏的生活,我坚信你可以遇到更优的自身.</t>
+          <t>层级1(整体):1天经典环线
+层级2(核心分段):
+- 上午:天外村→中天门→十八盘→南天门→天街;
+- 下午:碧霞祠→玉皇顶→日观峰→返程.
+层级3(子路线):各景点线性串联,无体能适配、无文化讲解分支,无时间规划.
+层级1(整体):3天2晚深度环线(基于官方路线优化,分体能段+文化分支)
+层级2(每日结构):核心段+休整段+小众文化分支段
+层级3(时段细分):清晨/上午/中午/下午/傍晚,含停留时长+体能建议+文化讲解.
+层级2-1:核心轻松段(07:00-11:00)
+层级3-1:07:00 天外村乘坐景区大巴至中天门(07:10),步行5分钟至云步桥(07:15),停留20分钟(07:15-07:35),补充讲解:云步桥摩崖石刻的书法流派(官方路线未提及);
+层级3-2:07:35-07:45 步行至斩云剑(10分钟),停留15分钟(07:45-08:00),讲解“斩云剑”名称由来(民间传说);
+层级3-3:08:00-08:15 步行至五大夫松(15分钟),停留30分钟(08:15-08:45),增加小众视角:五大夫松周边的古松群(官方路线仅提单棵松);
+层级3-4:08:45-08:55 步行至朝阳洞(10分钟),停留20分钟(08:55-09:15),讲解泰山道教文化;
+层级3-5:09:15-09:30 步行至快活三里(15分钟),停留40分钟(09:30-10:10),长休整(适配低体能);
+层级3-6:10:10-10:25 步行返回中天门(15分钟),停留35分钟(10:25-11:00),准备午餐.
+层级2-2:休整段(11:00-13:00)
+层级3-1:11:00-11:10 步行至中天门餐厅(10分钟),用餐60分钟(11:10-12:10);
+层级3-2:12:10-13:00 餐厅周边休整(50分钟),体验泰山祈福牌书写(官方路线无此体验).
+层级2-3:小众文化分支段(13:00-17:00)
+层级3-1:13:00-13:15 步行至中天门博物馆(15分钟),停留1小时(13:15-14:15),参观泰山地质标本展(官方路线未推荐);
+层级3-2:14:15-14:30 步行至冯玉祥墓(15分钟),停留30分钟(14:30-15:00),了解冯玉祥与泰山的渊源;
+层级3-3:15:00-15:20 步行至黑龙潭(20分钟),停留40分钟(15:20-16:00),观赏黑龙潭瀑布(官方路线未提及);
+层级3-4:16:00-16:20 步行返回中天门(20分钟),停留40分钟(16:20-17:00),自由休整(适配低体能).
+层级2-1:核心中等体能段(06:30-12:00)
+层级3-1:06:30-06:40 中天门乘坐景区大巴至天外村(10分钟),换乘早班索道至南天门(06:55),步行5分钟至天街(07:00),停留25分钟(07:00-07:25),讲解天街的明清商业文化;
+层级3-2:07:25-07:33 步行至碧霞祠(8分钟),停留40分钟(07:33-08:13),细化讲解碧霞元君的祈福习俗(官方路线未细化);
+层级3-3:08:13-08:23 步行至唐摩崖(10分钟),停留30分钟(08:23-08:53),讲解唐玄宗封禅泰山的历史背景;
+层级3-4:08:53-09:03 步行至玉皇顶(10分钟),停留40分钟(09:03-09:43),打卡“五岳独尊”石刻+讲解石刻历史;
+层级3-5:09:43-09:58 步行至日观峰(15分钟),停留30分钟(09:58-10:28),讲解日出观测的天文知识;
+层级3-6:10:28-10:43 步行至探海石(15分钟),停留20分钟(10:43-11:03),休整5分钟至11:08,准备午餐.
+层级2-2:休整段(11:08-13:00)
+层级3-1:11:08-11:18 步行至玉皇顶餐厅(10分钟),用餐50分钟(11:18-12:08);
+层级3-2:12:08-13:00 餐厅周边休整(52分钟),体验泰山碑刻拓片制作(官方路线无此体验).
+层级2-3:小众分支段(13:00-17:00)
+层级3-1:13:00-13:15 步行至丈人峰(15分钟),停留20分钟(13:15-13:35),了解“丈人”(岳父)称谓的泰山渊源;
+层级3-2:13:35-13:50 步行至仙人桥(15分钟),停留30分钟(13:50-14:20),拍摄小众奇石景观;
+层级3-3:14:20-14:40 步行返回南天门(20分钟),停留2小时(14:40-16:40),自由休整+观赏山间云海.
+层级2-1:核心补充段(09:00-12:00)
+层级3-1:09:00-09:20 南天门乘坐索道至中天门(20分钟),步行10分钟至天外村(09:30),停留30分钟(09:30-10:00),采购泰山特产;
+层级3-2:10:00-10:20 乘车至岱庙(20分钟),停留1小时(10:20-11:20),参观岱庙天贶殿(官方路线未推荐);
+层级3-3:11:20-11:40 步行至岱庙博物馆(20分钟),停留40分钟(11:40-12:20),了解泰山封禅文化全貌.
+层级2-2:返程准备段(12:20-14:00)
+层级3-1:12:20-12:30 步行至岱庙周边餐厅(10分钟),用餐50分钟(12:30-13:20);
+层级3-2:13:20-14:00 整理行程、返程.
+1. 官方路线:线性层级(整体→分段→景点),无体能分级、无文化体验、无小众分支;
+2. 实际路线:多维层级(整体→每日体能段→核心/休整/小众→时段/讲解/体验),增加体能适配、文化体验和小众打卡点,适配不同游客需求.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>记录抗震救灾成果,见证发展振兴脚步
-"为了人民群众的生命财产安全 - - 九寨沟县7.0级地震抗震救灾纪实"(2017年8月10日版面图).
-□四川日报全媒体记者 薛维睿
-8月末,雅安市芦山县龙门镇正值旅游旺季,记者走进"龙兴之野·河谷印象田园"项目看到,一期建设已近尾声,荷叶满塘,荷花随风浮动,游客在荷塘边驻足流连.
-"项目规划面积1441亩,将新建莲虾种养基地,稻油轮种基地,打造河谷红色美学田园综合体."龙门镇党委书记苟发灵介绍,全面建成后,将成为国家4A级旅游景区龙门古镇的重要节点,与周围龙门溶洞,红军村,红石滩湿地等景点融合,形成"民宿,农旅,研学"三大组团,擦亮震中乡村振兴新名片.
-龙门镇是2013年"4·20"芦山强烈地震震中.鸟瞰如今的龙门镇,绿水青山掩映稻田农屋,农田里"重建新路发源地"7个大字格外醒目.9年来,从满目疮痍到美丽新村,从百废待兴到产业繁荣,"四川日报"记录着这里抗震救灾和恢复重建的点滴成果,见证当地走出"中央统筹指导,地方作为主体,灾区群众广泛参与"的重建新路.
-时钟回拨到2008年5月12日14时28分,面对突如其来的汶川特大地震,四川日报社第一时间紧急部署,全面打响抗震救灾战役报道.
-地震当天下午,正在马尔康采访的四川日报记者李燕华,王代林,松涛当即决定直奔震中汶川.在道路损毁,无法通行的情况下,几人经过6小时连夜步行,于5月13日凌晨3时50分率先抵达理县县城采访,并通过理县对外联络的通信渠道 - - 林业防火电台,将理县灾情报道口述至阿坝日报,再由阿坝日报传回四川日报.新闻媒体从重灾区理县发回的第一篇报道 - - "阿坝州抗灾救灾工作组昨凌晨抵达理县县城"就这样产生了.随后,他们几人又经过8小时步行,经历暴雨,狂风,飞石等严重威胁和考验,于14日中午抵达汶川,并第一时间发回"目击汶川县城"的现场报道,为抗震救灾提供了第一手权威信息.
-从地震当天起,四川日报每天有60余名记者深入灾区一线采访,及时发回报道,在全方位反映抗震救灾的同时,书写了一幕幕新闻背后的感人事迹.
-十多年来,四川先后历经了数次地震灾害,"四川日报"始终以高度的责任感和使命感,对抗震救灾硬仗作出及时,准确,权威,生动,全面的报道,唱响"万众一心,众志成城,不畏艰险,百折不挠"主旋律.
-今年的"6·1"芦山地震和"6·10"马尔康地震,川报记者再次深入一线,围绕抢险救援和重建进行报道.伟大抗震救灾精神,在新时代进一步弘扬.
-"不等不靠搞重建,木坪子上建家园."在雅安市芦山县太平镇大河村木坪子聚居点建设项目现场,两行标语引人注目.紧张繁忙的施工现场,工程车辆来回进出,工人们正在各个作业点忙碌."6·1"芦山地震后,当地紧扣节点目标任务,灾后恢复重建工作正有力,有序,有效推进.
-"计划9月10日前完成地基建设."在项目现场,大河村党支部书记何培友拿出一张规划图介绍,聚居点规划建设18套砖木结构房屋,集中安置32户群众,"争取春节前让大家住进去."
-"搬家那天你们过来看."何培友与记者约定,到时再来看看群众搬新家过新年.</t>
+          <t>发布时间:2025-10-01 21:00:00
+来源:小红书
+08:00 从红门路出发,乘坐出租车前往天外村游客中心,车程10分钟.抵达后,我先在售票处买票,这里的工作人员告诉我,它的景区大巴每10分钟一班,比其他景区的发车频率高.
+08:30 乘坐景区大巴前往中天门,车程10分钟.抵达后,首先看到的是云步桥,它是泰山中天门段的标志性景观,这里的瀑布在雨季水量充沛,和旱季的它完全不同,它的水流声能传很远.走过云步桥,就是斩云剑,这里的石刻是清代书法家题写的,它的字体是行书,和泰山其他石刻的楷书不同,它的笔锋更飘逸.
+09:00 走到五大夫松,它是泰山的名松,这里的传说和秦始皇有关,它的树龄超过千年,比周边的松树都老.抚摸它的树干,能感受到它的粗糙,这里的游客都会和它合影,因为它是泰山松的代表.
+09:40 从五大夫松走到十八盘起始点,它是泰山最陡的路段,这里的台阶有1633级,和其他登山道不同,它的坡度接近70度,走在上面能感受到它的险峻.抬头看十八盘,它像一条天梯通向天际,这里的护栏是汉白玉做的,它的手感很冰凉,即使夏天也不烫手.
+10:30 走到南天门,它是泰山的“天门”,这里是泰山上下的分界,和中天门不同,它的海拔更高,空气更稀薄.走进南天门,就是天街,它是泰山的商业街,这里的商铺卖的都是泰山特产,它的物价比山下贵一点,但它的商品更有特色.
+11:00 从天街走到碧霞祠,它是泰山最有名的道观,这里供奉着碧霞元君,它的香火很旺,和其他道观不同,它的建筑是明清风格,它的屋顶是黄色琉璃瓦,代表皇家规格.碧霞祠的东侧有一口铜钟,它每天都会敲响,这里的信徒会根据它的钟声祈福,它的声音洪亮,能传遍整个天街.
+11:30 走到玉皇顶,它是泰山的极顶,这里的“五岳独尊”石刻是泰山的标志,它的字是隶书,和其他石刻的字体不同,它的尺寸更大,有5米高.站在玉皇顶,俯瞰山下,它的景色一览无余,这里的风很大,吹得人站不稳,要是你想拍照,一定要抓牢它的护栏.
+12:00 从玉皇顶走到日观峰,它是泰山看日出的最佳地点,这里的观日台是石头砌的,它的位置正对东方,和其他观景点不同,它的视野无遮挡.在日观峰的西侧,有一块探海石,它伸向悬崖,这里的游客都不敢靠近它的边缘,因为它的下面是万丈深渊.
+12:30 从日观峰返回天街,走到天街的餐厅,这里的主打菜是泰山炒鸡,它的味道很辣,和山下的炒鸡不同,它的用料是泰山散养的土鸡.吃完饭休息了一会儿,我走到餐厅外的祈福店,这里的祈福牌是木质的,它的上面刻着泰山的图案,很多游客都会买一块,挂在它的祈福墙上.
+13:30 从祈福店出发,走到南天门索道站,它的索道是单线循环式的,这里的票价是100元/人,比其他索道贵,但它的运行速度更快,能节省很多时间.乘坐索道下山,它的轿厢是透明的,坐在里面能看到泰山的全貌,这里的景色比上山时更壮观,因为它的视角更高.
+14:30 走出索道站,乘坐景区大巴返回天外村,它的车程10分钟,这里的大巴很宽敞,和来时的车一样,它的座椅是软的,坐起来很舒服.回到酒店,回顾当天的行程,泰山的美在于它的雄伟,这里的每一个景点都有故事,它的文化底蕴深厚,要是你没来过,一定要来感受一下它的魅力.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>仔细看就知道,九寨沟门票上的导游图标记的路线是个丫叉头,实际上丫叉头就是九寨沟的三条沟,所有的景点就在这三条沟里面.
-说起来简单做起来难,三条沟如果要仔细玩可以几天几夜,为了节省时间,九寨沟内部有车子,大家排队上车,沿着车子行车路线设站,游客可以在任意站台上下车.每部车上配有九寨沟内部的导游,导游沿途解说,到一段景点说一段导游词,使人跟着导游的眼光目不暇接.
-按照我们旅行社美女导游的关照,中途不许下车,一直坐,坐到底再下车,然后走回来,走回来的路是下坡路,比较省力.汽车到底的最后站叫"箭竹海",海是湖的代名词,那里看不见海,凡是湖就叫海,是对海的一种向往,一种崇拜.
-早晨空气最新鲜,早晨景色最美丽.
-天蒙蒙亮,我们在九寨沟的大巴车上一边听着导游解说,一边观摩着路旁如梦如烟的景色,就这样,向往着破解九寨沟神话世界的秘密一路向前!
-旅游的心情总是那么诧异,再累也会无所谓.出钱买苦吃的行当,是吗?愿意!
-自己的大巴只能到此为止
-徒步行走
-门票反面的导游图
-维持秩序
-本篇游记共含705个文字,36张图片.帮助了名游客. 举报
-如果一生只去1次九寨沟,要这样玩才能不留遗憾
-关于九寨沟内住宿,你还不知道的那些事儿!
-第一次来四川怎么玩?经典一个都不能少!
-中国旅游行业第一部"玩法"</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>成都到赛达有哪些自驾路线?路况怎么样?九寨沟在成都北部,色达也在成都北部的西部.九寨沟地震后Seda还能去吗?路况好吗?下面铁骑狼边肖将告诉你成都到赛达的具体行程.
-1.出行路线
-5,成都-都江堰-映秀-汶川-礼县-刷马路口-阿坝县-半马-色达,路况最好,风景优美,任何一辆车都可以通过,沿途会爬过山口.注意减速(雨季有滑坡,但基本不影响交通).虽然距离最远,但是没有堵车,不过考虑到九寨沟地震的影响,最近可能会堵车.
-2.注意事项
-1.进出教堂时,请关闭机器或将其转为振动.不要大声喧哗,走路要轻,这样不会影响和尚的念经念佛.僧袍,经书,转轮都不能跨,踩.
-2.和尚需要提问的时候叫"师父",住在家里的叫"师兄".
-3.路过学院大门口记得脱帽.这扇门是解放之门.进了这个门就能摆脱业力.
-4.学院的大梦幻网球城需要顺时针旋转.无论是绕坛城还是拍夜景,路过的时候记得顺时针旋转,千万不要倒退.
-5.在山里拍照时,千万不要跨过或践踏祈祷旗.如果你必须穿过有祈祷旗和祈祷旗的地方,请把祈祷旗举过头顶,从下面钻过去.无论你有多美,千万不要把刻有经书的石头拿到路边或山上家里.
-6.不要站在和尚,和尚或居士面前,未经允许不要拍照.
-7.天葬期间千万不要拍照,更不要传播与天葬有关的图片和照片.
-8.学院八大期间,信徒很多,住宿问题很大.建议旅游的朋友在错误的高峰旅游.不过,场面很壮观.如果能搭帐篷,可以在法会议期间来.具体法会时间:举行明法会:藏历正月初一至藏历正月十五金刚萨历史会:藏历4月8日至4月15日普贤云赐法会:藏历9月18日至9月25日(有巨大的唐卡佛像).具体的藏汉历法对照表可以百度
-9.尽量不要带病上山,特别是感冒高血压,注意冷暖
-10.学院风大,都是木质建筑.学院各个角落严禁吸烟,饮酒,赌博.不要乱扔垃圾,破坏环境.
-Notice: The content above (including the pictures and videos if any) is uploaded and posted by a user of NetEase Hao, which is a social media platform and only provides information storage services.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>?阅读本文前,请您先点击本文标题下面的蓝色字体"冬姐指南 '惠'游天下"再点击"",这样您就可以继续免费收到文章了,每天都有.世人都知九寨美,却很少有人知道,九寨沟所在的阿坝州私藏了多少美景.
-这个被称作"上帝的后花园"的地方,处处皆天堂,而九寨沟,也只是天堂一角.
-这个汇聚了万千风情的地方,神秘奇特的自然风光和多元民族的古老文化在此浪漫相遇.
-这个被世界旅游专家誉为世界生态旅游最佳目的地的地方,去一趟,就等于饱览了祖国半壁江山的美景.
-这里的每一个县,都有美若天堂的景致.可以说,阿坝十三县,一步一美景,县县皆天堂!
-土司官寨,在过去,是权力和地位的象征.而这座融入了藏汉民族精湛建筑精华的官寨,被国际友人赞誉为"东方建筑史上的一颗明珠".
-在这里,除了感叹建筑的魅力,你还可以体验嘉绒藏族的民俗文化,感受藏传佛教的神秘.
-九寨沟县便是众所周知的九寨沟所在地,这里山川秀美,旅游资源得天独厚.
-九寨沟的名气之大,已不用赘述,"九寨归来不看水",就是对九寨沟景色真实的诠释.
-碧水蓝天,青山白云,红叶炎黄相互交映,这才是真正的童话世界,人间仙境.
-甘海子原是一处高山湖泊,后因地质变化,出水口扩大,所以当地百姓俗称"干海子".
-其实,"干海子"并不干,这里四周远山层叠,森林茂密,海子中溪水蜿蜒,芳草萋萋,因此,人们逐渐就把"干海子"叫成了"甘海子".
-不输阿尔卑斯山的"四姑娘山",独特多样的民族风情......这个小小的县城,藏了太多称得上世界级的美景.
-这个"东方阿尔卑斯山",冰雪覆盖,银光照人,森林茂密,绿草如茵,一派秀美的南欧风光,完全不输瑞士的阿尔卑斯山.
-这些年,四姑娘山已经成为中外登山者眼中的天堂.徒步登山,看星空日出,拍云海翻腾......都是最美的四姑娘山.
-在沟内,林木高低不齐,奇花异草处处都是,散布在沟内各个角落.而且因为海拔的不同,植被也呈阶梯变化,g6111五颜六色的,好看得很.
-松潘是我国古代地处边陲的军事重镇,有"高原古城"之称.每到夏秋季节,这里便会美如仙境般.
-松潘古城古称松州,自古既是川西北地区的军事要塞,也是历史悠久的藏,羌,回,汉族人民"茶马互市"的重要驿站.
-红原县境内草原辽阔,水草丰茂,矿藏,森林极为丰富.牧歌,帐篷,牛羊星罗棋布,美不胜收的人间天堂.
-每年六七月间,俄木塘30000亩花海在蓝天白云下盛开,这个低调的地方,被誉为"最美的草原花海".
-湛蓝天空,旷阔草原,纯净湖泊,璀璨花海,蓝天白云下,任由自己沉醉在这万亩花海间.
-阿坝县位于川,甘,青三省交汇处,是川青高速的必经之地,县境内有藏传佛教寺庙42座,被誉为藏传佛教文化博览园.
-"莲宝叶则"有两个.四川阿坝县境内的部分叫莲宝叶则.青海久治的部分叫年宝玉则.
-这是一处养在深闺中的绝世风光,少为人知,却是资深自驾车友和背包行者的终极目的地,也被摄影者圈内奉为天堂的朝圣之地.
-神座村,被誉为"神仙居住的地方", 美丽的热曲河将森林和草原分开,神座就坐落在河流的西侧,与对岸茂密的原始森林隔河相望,与世隔绝.
-若尔盖县地域辽阔,是四川通往西北省区的北大门,素有"川西北高原的绿洲"和"云端天堂"之称.
-若尔盖大草原是藏族游牧民聚居的地方,六至九月的大草原天高气爽,日出晨曦,帐篷点点,炊烟缭绕,风情醉人.
-一望无际的大草原上,鲜花烂漫,绿草如茵,策马奔腾,潇潇洒洒......没有什么烦恼是这里带不走的.
-难以想象那个水流湍急,河水浑浊的黄河,在这个黄河九十九道湾中的第一湾,还是一条温婉平静的河流.
-水流清澈缓慢,从茫茫草海中穿过,牛羊在河边悠闲的漫步,不一样的黄河就在这里.
-壤塘,四川边陲重镇,藏在深闺人未识,一遭开放沁人心.这里风光旖旎,民风淳朴,宗教深厚,建筑别致,是一个不可多得的充满神奇神秘的境地.
-棒托寺藏语意为"草坝上的寺庙",顾名思义寺庙周围山清水秀鸟语花香,古刹经幡猎猎,香客络绎不绝.
-汶川是阿坝州的南大门, 全国仅有的四个羌族聚居县之一,来这里追寻古老的羌文化,在遮天蔽日的原始森林中寻找珍稀的奇花异兽,更重要的是在地震的废墟中发现重生的力量.
-萝卜寨处在到九寨的必经之路上,这里是至今为止发现的世界上最大,最古老的黄泥羌寨,处处充满原始淳朴的风情.
-这个藏族,羌族聚集地,少数民族风情浓厚.除了绝美自然风光,羌寨等羌族风情也吸引不少人前来.
-桃坪羌寨是世界上保存最完整的碉楼与民居的融合体,享有"天然空调"的美名.
-碉楼是整个寨子的标志性建筑,目前仅存两座,一座位于寨子正中,另一座雄踞在寨子对面的河岸上.
-米亚罗风景区是中国发现并开放的面积最大的红叶风景区之一,曾经比北京香山红叶风景区大180余倍.
-每到金秋十月,十一月,米亚罗便到了一年中最美的时候,漫山遍野的红叶非常壮观!
-神秘多姿的现代冰川,流光溢彩的彩林,巍峨屹立的雪山,浓郁的藏羌民族文化风情,神秘的宗教文化......黑水县的美丽之处数不胜数.
-奶子沟的彩林景观,让人见过便会挪不开眼睛.
-与内地的彩林景区不同,圣洁的雪山,古老的藏寨,游弋的牛羊,纯静的蓝天,映衬着奶子沟彩林,更添其妩媚和美丽.
-茂县是我国最大的羌民族聚居地,文化底蕴很厚.同时也是途经"九环线西线"前往世界自然遗产九寨沟,黄龙的必经之地.
-松坪沟素有小九寨之称,这里分布着大大小小如翡翠,蓝宝石的海子,山水碧绿幽蓝,还有九寨沟没有的清净.
-在这里,有碧如蓝天的群海,茂密的原始森林,还有神秘的古羌文化,不经意间,就会被深深打动.
-金川县自然,人文景观丰富,有着中国 "雪梨之乡"之称.每到春季,境内的梨花开放,整个县城会成为一个花海,十分美丽.
-观音桥镇汇集了草地,湖泊,峡谷,彩林,圣庙,其中,又以土基钦波观音寺最负盛名.
-观音寺有着第二个布达拉宫的美誉,在这里,能感受到厚重深邃的宗教文化.
-阿坝,私藏了太多天堂级的美景.毕生,一定要去走一圈,方不留遗憾.
-?阅读本文前,请您先点击本文标题下面的蓝色字体"冬姐指南 '惠'游天下"再点击"",这样您就可以继续免费收到文章了,每天都有.江苏10个颜值最高的秘境,连当地人都美呆!人少还免费!
-对于江苏,相信很多人都不会陌生.
-南京的六朝胜迹;苏州的古镇园林;无锡的太湖风光;常州的主题公园;徐州的秦汉遗迹......江苏秘境很多,但你不知,江苏还有更多的秘境,隐藏在城市的小角落 - -
-这些秘境也许是藏在市郊的一条路,也许是附近的一片森林,你很容易忽略它们,却没发现它们已经美成了意外,不用花钱就能让你享受到一片视觉盛宴.
-下面带你走进江苏这10个免费秘境!
-层林尽染的山林风光,成熟的野果掉落在厚厚的落叶上,湖里的水捧起来就能喝.这不是在原始森林,就在南京市郊的六合止马岭.
-止马岭别名芝麻岭,这里藏了一片水杉,一片湿地,林间有麻栎,黄栋,松树,湿地里栖息着各种候鸟,成群的野鸭在湖面嬉戏.
-夏秋季节是止马岭植被最为茂盛的时候,漫步止马岭,色彩浓郁斑驳,却又清寒辽阔,宛若天地间一幅画卷,令人生出无限感慨.
-它的四季都很美,但最美的季节是秋季,从山顶往下看,林间呈现不同的颜色,绚丽的色彩一下斑斓了你的眼.
-冬季,这里有银雪白树,橘色的阳光撒上去,宛若上帝洒下的光束,美得令人窒息.
-石塘人家位于南京市江宁区,这里交通便捷,却又清静舒爽,是个非常适合周末度假的好地儿.
-这个千年古村落青山环抱,木栈道与古建筑交相辉映.村内建筑群清一色青砖小瓦马头墙,古徽州的韵味从这里一点点蔓延开来.
-更令人欣喜的是,村子后面还藏了片竹海 - - 这里拥有连片翠竹3万亩,与九龙湖相依相偎,湖光山色之间,翠波荡漾,使人迷醉.
-一入竹海,仿佛来到天然氧吧之中,如临仙境般超凡脱俗.
-这里更是个避暑的好地方,在炎炎夏日,择一片竹海,轻摇蒲扇,喝点小酒,在小村走走逛逛,也是一件不错的事.
-世凹桃源是江宁的"五朵金花"之一,一派江南田园风光,以白墙黛瓦的徽派建筑为主格调.
-这里风光独好,花木扶疏,让人暂时忘却烦忧.就像陶渊明笔下的桃花源一样,世凹村的人们幸福安逸生活着.
-相传,数百年前,人们为了纪念桃花仙子,开始在山上田野栽种桃花.每到春天,桃花漫山遍野,仿佛陶渊明所著桃花源中的美景,故名"世凹桃源".
-在此附近的牛首山是南京著名踏青胜地,每逢阳春三月,茂林修竹,桃花争艳;黄昏时分,暮色苍茫,云蒸霞蔚,身在其中有虚无缥缈,魂牵梦绕之意境.
-无锡宜兴的绍坞村,藏了一处动人的秘境,但很多人当地人都不知道这里.
-这是一个群山环抱的小山村.四周的山不是很高,漫山遍野长满了毛竹,郁郁葱葱满目苍翠.山里有座湖,湖水澄澈的令人心醉,蓝幽幽的光一下便吸引了你的眼睛.
-爬山山头,但见群山逶迤,莽莽苍苍,无边的绿色覆盖着脚下这片土地.四处寂静无声,只有隐隐的竹涛在山谷中回响不绝......这片少人的秘境,就这样被你承包了郑秋泓.
-颐和路位于南京市鼓楼区内,西南至东北走向.这条美丽幽雅的街道,是各种建筑艺术风格的综合,更是一段历史的缩影,透出神秘的气氛和浓郁的文化气息.
-民国时期的颐和路是一个纸醉金迷的地方,相当于核心区域.如今繁华落去,只剩下沿路碧绿的浓荫与近百幢风格迥异,各具个性的西式建筑.
-漫步颐和路,让人忽忆起"庭院深深深几许"的诗句,浑身顿有铅华洗净,气定神闲的感觉.
-无锡斗山,由于地处江南小丘陵地带,在天晴无风温差大于10度以上的气候条件下,会产生绝妙的"矮脚雾".它是苏南地区特有的气候现象,仿佛一片仙境.
-矮脚雾"绝妙之处是位置较低,沉在树木和房屋的下方,而不会覆盖全部景色.清晨,雾气在江南风貌的村落和树林间飘移,半遮半掩,朦胧之中更添一份意境.
-窑湾古镇,在京杭大运河与骆马湖交汇处,三面环水,历史悠久,被称为"小上海".
-在古镇流连时,仿佛缓缓推开了一副沉寂多年的历史画卷:一座座哨楼威严耸立,猎猎战旗呼啦啦作响.三面环绕的骆马湖,宛若绵长柔韧的血管,生生不息滋养着繁华或衰落的古镇.
-伸手可触的古建筑,廊檐出夏,青砖斑驳.曲线优美的黛瓦间摇曳着泛黄的秋草.苏北水乡古镇的质朴雅韵,就这么水灵灵地从老街深处轻烟流云般扑面开来.
-惠山又名九龙山,因气势雄壮,钟灵毓秀,素有"江南第一山"之美誉.唐朝茶圣陆羽品定惠山泉水为天下第二,于是"天下第二泉"便名扬华夏.
-古镇便坐落于这样的一处宝地之下.走在惠山脚下的石板路上,品一口无锡人特有的早酒,感受穿越千年的悠长古韵,你会着迷其间.
-篦箕巷位于旧称"花市街",位于常州城西,紧临运河.
-这一段明城墙,窄窄的巷子两边都是白墙黑瓦的建筑,古韵犹存.
-常州自古以来就一直以制作篦箕和木梳而闻名,素有"宫梳名篦"和"常州梳篦甲天下"之盛誉,而这里整条街巷,家家户户都以制作梳篦为生.
-走在篦箕巷,天然的古意弥漫,仿佛置身于一副水墨画之中.这契入生活中的雅韵,深深吸引着每一个过路客.
-旺山生态园处于天然山林环抱之中,是一处保存良好的田园梦乡.
-这里有乡村小宿,有热乎乎的农家饭,有竹林天然氧吧,有环山健康小径,可谓是养生的一大好地.
-景区内还有大量果园,菜地,游客在这里既能品尝到无公害绿色食品,又能亲自采摘,可以尽情体验淳朴自然的农作生活.</t>
+          <t>一、出行前条件建议
+1. 如果选择节假日游览泰山,建议提前7天在“泰山景区”公众号预约门票,因为节假日门票会在30分钟内售罄,现场无法购票;
+2. 要是带老人游览,不建议选择全程徒步路线,除非老人体能极佳(60岁以下且常锻炼),否则建议租用景区轮椅(60元/天)+乘坐索道/景区大巴,泰山全程台阶超6000级,无平路;
+3. 如果打算拍摄泰山日出,建议选择秋季的晴天前往,因为秋季泰山云海+日出同框概率达70%,要是夏季,云海概率不足20%;
+4. 要是携带登山装备,建议准备防滑登山鞋和护膝,除非你是专业登山者,否则这些装备能减少下山时的膝盖损伤;
+5. 除非你对泰山封禅文化特别了解,否则建议租用讲解器(40元/台)或请人工讲解(200元/小时),泰山的历史细节仅靠看无法理解.
+二、登山途中条件建议
+1. 如果从天外村乘大巴至中天门,建议选择最早一班(6:00),要是来晚了,排队时间会增加1小时以上,尤其是节假日;
+2. 要是想拍摄无人的十八盘,建议在开园后30分钟内抵达,因为旅行团会在开园后1小时陆续进入;
+3. 如果游览玉皇顶区域,建议站在“五岳独尊”石刻正前方拍摄,除非你想拍局部特写,否则这个机位能完整拍出石刻+泰山极顶背景;
+4. 要是遇到泰山临时封山(如极端天气),建议调整游览顺序,优先游览岱庙,除非封山区域是你的核心目标(如玉皇顶);
+5. 如果在泰山内用餐,建议选择中天门或天街的正规餐厅,要是想节省费用,可自带高热量干粮(如巧克力、牛肉干),泰山内除餐厅外,仅服务区可进食;
+6. 要是体能不足,建议放弃十八盘徒步,前提是你已乘坐索道至南天门,否则会错过泰山核心景观.
+三、文创与体验条件建议
+1. 如果想购买泰山祈福牌,建议在天街的官方文创店购买,因为非官方店铺的祈福牌无开光认证,要是你注重祈福效果,不要买低价仿品;
+2. 要是想体验泰山碑刻拓片,建议提前联系景区文创中心预约,除非你自带拓片工具,否则景区不提供零散拓片服务;
+3. 如果想拍摄泰山晚霞,建议在日观峰停留至下午5点(冬季)/7点(夏季),因为泰山晚霞的最佳观赏时间是日落前30分钟;
+4. 要是想参观泰山特展(如文物展),建议提前查看泰山博物院官网,除非你运气好,否则特展可能临时更换展品;
+5. 如果带孩子游览,建议准备泰山神话故事绘本,要是孩子对历史不感兴趣,可通过故事增加游览趣味性.
+四、离园与返程条件建议
+1. 如果从南天门离园,建议乘坐索道下山,要是体力允许,可徒步至中天门再乘大巴,除非你赶时间;
+2. 要是想购买泰山特产,建议在泰安市内的超市购买,除非你想在景区内购买,否则景区内价格比市区贵50%;
+3. 如果选择公共交通返程,建议避开晚高峰(下午5-7点),因为泰山周边的公交/地铁会拥挤到无法上车;
+4. 要是当天返程,建议预留1.5小时的缓冲时间,因为泰山周边的交通管制较多,除非你提前查好实时路况并选择网约车;
+5. 如果想整理当天的登山照片,建议用手机修图软件快速处理,要是带了电脑,可回酒店后精细修图,泰山内无充电处(除付费服务区).
+五、特殊场景条件建议
+1. 如果遇到雨天游览泰山,建议穿防滑的登山鞋+携带登山杖,因为泰山的石板路雨天会极滑,要是没带雨具,可在景区内购买加厚一次性雨衣(15元/件),普通雨衣会被山风吹破;
+2. 要是冬季游览泰山,建议穿防风羽绒服+戴护耳帽,除非你耐寒性极强,否则泰山山顶的风力可达8级,体感温度低至-10℃;
+3. 如果是摄影爱好者,建议携带广角镜头(拍全景)和长焦镜头(拍石刻细节),要是只带一个镜头,会错过很多拍摄机会;
+4. 要是有宗教信仰,建议尊重泰山的祈福习俗,除非你想了解萨满/道教文化,否则不要随意触碰祭祀用品;
+5. 如果独自游览泰山,建议将实时定位给家人,因为泰山部分区域手机信号差,要是遇到紧急情况,家人能及时联系景区救援队.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>故宫</t>
+          <t>西湖</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>由于故宫景区面积大且核心建筑集中,建议早上 8 点前抵达午门(开门前 30 分钟),全程采用步行方式游览(故宫内无观光车),具体线路如下:[上午]午门(8:30 入园)→太和门(8:30-8:45 步行 10 分钟,游览时间 5 分钟)太和门→太和殿(8:45-9:20 步行 5 分钟,游览时间 30 分钟,重点观赏太和殿建筑规制)太和殿→中和殿(9:20-9:35 步行 3 分钟,游览时间 12 分钟)中和殿→保和殿(9:35-10:00 步行 2 分钟,游览时间 23 分钟,可观赏云龙大石雕)保和殿→乾清门(10:00-10:15 步行 8 分钟,游览时间 5 分钟)乾清门→乾清宫(10:15-10:40 步行 2 分钟,游览时间 23 分钟)乾清宫→交泰殿(10:40-10:55 步行 1 分钟,游览时间 14 分钟)交泰殿→坤宁宫(10:55-11:20 步行 1 分钟,游览时间 24 分钟)[中午]坤宁宫→故宫冰窖餐厅(11:20-13:00 步行 5 分钟,用餐和休息时间 1 小时 40 分钟,可就近观赏御花园入口景观)[下午]冰窖餐厅→御花园(13:00-13:40 步行 3 分钟,游览时间 37 分钟,重点观赏堆秀山、千秋亭)御花园→神武门(13:40-13:50 步行 5 分钟,游览时间 5 分钟,出神武门可观赏景山全景)神武门→东华门(13:50-14:20 步行 15 分钟,游览时间 15 分钟,观赏东华门建筑特色)东华门→文华殿(陶瓷馆)(14:20-14:50 步行 8 分钟,游览时间 22 分钟,观赏故宫陶瓷馆藏)文华殿→午门出口(14:50-15:10 步行 10 分钟,结束游览)一天的游览对体能有一定要求,建议穿舒适的平底鞋,故宫内无遮阳处,夏季需做好防晒,冬季注意保暖.游览结束后可前往景山公园,登高俯瞰故宫全景,感受紫禁城的整体布局,晚上可到前门大街品尝北京特色小吃,充实的故宫之旅就此结束.</t>
+          <t>由于西湖核心景点环湖分布、线路跨度较大,想要完整打卡苏堤、平湖秋月、灵隐寺、湖滨、雷峰塔、断桥、花港观鱼、三潭印月、曲院风荷、白堤这些核心地标,不同出行需求的一日游览时间均相对紧凑,均建议早上早点出发,全程可根据自身出行人群、体能情况与游览偏好,灵活采用景区观光车 + 步行 + 游船结合的方式开展游览,可选择的线路包含经典全覆盖顺向无折返全景点打卡线、休闲省力低步行强度适配亲子老人休闲党线、人文深度古迹文化沉浸式打卡适配历史爱好者线、日出日落限定摄影观景专属氛围感拉满线四条,其中经典全覆盖线路可按上午湖滨出发前往灵隐寺及飞来峰景区,依次打卡曲院风荷、白堤、平湖秋月、断桥残雪,中午在湖滨商圈用餐休息,下午从湖滨游船码头乘船前往三潭印月,再到花港观鱼、苏堤南口、雷峰塔,最后沿苏堤打卡返回湖滨的行程游览,休闲省力线路可按上午从湖滨出发依次打卡断桥残雪、白堤、平湖秋月、曲院风荷,乘船游览三潭印月、花港观鱼、苏堤南口与雷峰塔,中午在湖滨商圈用餐休息,下午前往灵隐寺及飞来峰景区游览后返回湖滨的低徒步行程游览,人文深度线路可按上午从湖滨出发前往灵隐寺深度游览飞来峰造像、永福寺、韬光寺,再依次打卡曲院风荷、白堤、平湖秋月,中午在湖滨商圈用餐休息并可同步参观西湖博物馆总馆,下午乘船游览三潭印月,再到花港观鱼、苏堤、雷峰塔深度感受江南人文底蕴后返回湖滨的行程游览,日出日落限定线路可按日出前抵达断桥残雪观赏西湖日出,依次打卡白堤、平湖秋月、曲院风荷,再前往灵隐寺及飞来峰景区游览,中午在湖滨商圈用餐休息,下午乘船游览三潭印月、花港观鱼、苏堤,日落前登上雷峰塔观赏西湖日落与全域全景,游览结束后返回湖滨并可同步打卡湖滨夜景的行程游览,四条线路均能完整覆盖所有核心景点,一天的游览或多或少对步行体能有所要求,因此来到杭州的第一天晚上可以好好休息,第二天游览完核心景区之后,可以去观赏&lt;最忆是杭州&gt;实景演出,或是前往龙井村、九溪烟树、西泠印社等地解锁更多杭城风光,体验不一样的江南水乡风情,充实的一天伴随着西湖的湖光山色与满满的愉快回忆完美结束,晚上回到酒店放松身体好好休息一番,把这份人间天堂的杭城美好带回家.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>今年以来,沈阳市制定多个政策,统筹推进文化旅游工作 - -
-6月2日,全市文化工作会议的召开,将文化工作上升到前所未有的新高度,形成了举全市之力统筹推动文化旅游工作新局面.近一阶段,全市文旅系统深入贯彻落实全市文化工作会议精神,推出了一系列利当前,惠长远的规划,政策,工程项目,形成了叠加效应,有力推动了沈阳文化事业产业日益繁荣兴盛,旅游持续蓬勃发展,进一步增强了人民群众的获得感,幸福感.
-"沈阳市文化旅游业"十四五"时期发展规划"的出台,确定了"十四五"时期,沈阳将以"文化沈阳,历史沈阳,山水沈阳"为主线,以"一核三带四极五廊"发展布局,构建"东山西水,北美南秀"全域文旅城市发展新格局,把沈阳建设成为国际文化旅游城市,区域性文化创意中心,国内生态休闲旅游目的地,国家文化和旅游消费示范城市.
-为确保规划高效落实,市文化旅游广电局以项目为牵引,"十四五"时期,系统谋划了7大专栏87个文旅项目.其中,今年市区两级共启动实施24个项目,盛京皇城综合保护利用,老北市国家AAAA级景区创建,"塔湾夕照"舍利塔文旅休闲产业示范区,大东路文化旅游观光路改造等项目正在稳步推进.
-围绕区域性文化创意中心建设,出台了"沈阳市建设区域性文化创意中心行动方案",以"文创内容生产中心,文创产业融合中心,文创休闲体验中心"三大中心为引领,启动实施了文化和旅游消费提质扩容行动,举办了文化创意赛事活动,成立了沈阳市文创人才智库,积极推进国家级夜间文化和旅游消费集聚区建设,沈阳中街,红梅文创园入选文旅部第一批国家级夜间文化和旅游消费集聚区.
-以人为本 点亮城市美好文旅生活
-市文化旅游广电局着力把握人民群众精神文化需求新特征,新趋势,以文化赋能城市建设,满足人民日益增长的美好生活需要.
-实施城市书房,城市书屋建设,出台了"沈阳市城市书房,城市书屋建设方案",年底前每个区县将至少建成1个城市书房,每个街道将至少建成1个城市书屋,目前,浑南莫子山等7个城市书房,和平北岸等47个城市书屋建设完成.
-加快打造博物馆"百馆之城",出台了"沈阳市博物馆"百馆"工程三年行动方案(2021 - 2023年)""沈阳市非国有博物馆扶持办法".沈阳"九·一八"历史博物馆,中国工业博物馆,沈阳年轮艺术博物馆提质升级崭新开放;新建的沈阳博物馆,北大营抗战遗址陈列馆建设完成并将于年底前陆续开放;积极推进沈阳市美术馆,新乐遗址公园,沈阳市自然博物馆,沈阳故宫博物馆分馆,沈阳市非遗博物馆等选址和规划工作.
-以深化改革促进国有院团可持续发展,印发了"沈阳市国有文艺院团改革发展实施意见",推进国有文艺院团"一团一策"分类改革.创作演出了杂技剧"忆·华年",现代京剧"逆行者",时代报告剧"激流勇进"等沈阳题材主旋律舞台艺术精品.坚持以艺术涵养城市精神,点亮城市生活,成功举办2021沈阳艺术节,推出了百余场演出,展览(展示)及交流活动.
-用足资源 擦亮沈阳历史文化名城金名片
-编制实施""一宫两陵"品牌建设三年行动实施方案",对标国际一流旅游目的地及5A级景区创建标准和细则,提出推进实施"一宫两陵"景区改造提升,着力构建"一宫两陵"世界级旅游目的地,"盛京文化"研究高地,打造"盛京皇城"中华文化地标,做亮"一宫两陵"国际品牌.
-加强考古和文物保护利用,非物质文化遗产保护传承,让文化遗产"活起来".创新推出了"国有土地开发建设考古勘探前置改革",获得了国家文物局高度好评;启动实施了马贝遗址,新兴屯东墓葬考古发掘;完成了沈阳故宫油饰彩画工程(二期),周恩来少年读书旧址等文物修缮工程;利用北大营旧址,侵华日军南满陆军造兵厂旧址建成陈列馆.利用端午小长假,举办了第七届沈阳非物质文化遗产博览会,东北8城市的170个非遗项目进行了展演展示.
-营销出圈 "传奇盛京,魅力沈阳"旅游品牌凸显
-围绕建设国际文化旅游城市的目标,多角度宣传"传奇盛京,魅力沈阳"城市形象.沈阳成功入选2023年度"东亚文化之都"候选城市.
-举办了沈阳四季游系列活动,组织开展了"京沈高铁沿线城市互动营销"活动,突出红色旅游和沈阳避暑胜地,夏凉宜人的气候特点,推出了三大板块,七大主题红色经典线路,二十条美丽乡村旅游线路,五条夏季主题旅游线路.经统计,今年前三季度,全市实现旅游总收入491.9亿元,比2020年同期增长29.2%,已恢复至2019年同期的70%.
-市文化旅游广电局正在全力筹备的东北亚文化旅游创意博览会,将于11月中下旬在新世界博览馆举办,展会将推出国际营销大会等三大主体活动,设有五大展区,将有来自近10个国家和地区的130家展商参展.
-权威解读
-发布会上,市文化旅游广电局相关负责人针对今年出台的多个政策,回答了记者的提问.
-▶关于博物馆
-问:今年出台了"百馆"工程的配套政策 - - "沈阳市非国有博物馆扶持办法",政策具体措施有哪些?
-答 市文化旅游广电局副局长宋振虹:对非国有博物馆发展给予的扶持资金补助,简单来说包含对国家文物行政部门评估确定等级的非国有博物馆给予奖励,新建非国有博物馆补助,展厅面积租赁补助,免费开放门票补助四方面.新建,租赁补助当年只享受其中一项,不可兼得.
-需要强调的是,"扶持办法"明确规定,申请资金补助的博物馆,必须完成民政部门登记并在省文物主管部门登记备案,正常运行1年以上,并通过市民政部门年检.提醒目前没有完成博物馆备案登记的场馆,抓紧按规定完成登记备案工作,目前尚未完成登记备案手续的,不能够享受上述政策补贴.
-▶关于生态休闲旅游目的地
-问:为实现把沈阳建设成为国内生态休闲旅游目的地的目标,沈阳有哪些具体举措?
-答 市文化旅游广电局副局长李志强:围绕"文化沈阳,历史沈阳,山水沈阳"为主线的全域生态旅游发展新格局,以"12345"重大项目为牵引,加强数字旅游建设,乡村民宿建设,大力推进国内生态休闲旅游目的地建设.
-"1":构建一个"盛京皇城"中华文化地标.
-"2":实施百家景区提质升级和特色旅游街区(村)建设两大文化旅游示范项目.推出多游一小时,云上故宫,数字博物馆建设等项目,加快数字旅游进程,形成有力支撑.
-"3":优化"文化沈阳,历史沈阳,山水沈阳"三类文化旅游主题产品.
-"4":"一宫两陵"综合保护利用,棋盘山国家级旅游度假区创建,老北市国家4A级景区创建,中山路欧风街提质升级四个文化旅游样板工程.
-"5":做强乡村体验游,生态和谐游,研学知识游,冰雪运动游,夜间沉浸游五类文化旅游业态.完成100家省级精品民宿建设,培育30家特色文化旅游示范村,推动沈阳中街,红梅文创园等一批特色夜文化旅游街区建设.
-▶关于国有文艺院团改革
-问:沈阳本轮深化改革将努力激发国有文艺院团的活力,集中呈现优秀作品.近期,百姓到哪里能欣赏到国有文艺院团的优秀作品?
-答 市文化旅游广电局副局长马今:沈阳国有文艺院团在改革政策的激励下,内生动力增强,文艺精品创排步伐加快.9月启幕的2021沈阳艺术节,推出"舞"彩缤纷板块,集中展演国有文艺院团优秀舞台艺术作品.
-经过四年的重构打造,沈阳艺术节平台效应不断显现,正成为城市文化艺术新品牌.目前,2021沈阳艺术节各项活动正在火热开展,已经推出了国有文艺院团积极创(复)排的京剧,评剧,话剧,儿童剧,交响乐,杂技剧等多门类优秀作品.今年我们特别聚焦儿童美育和市场开拓,创新排演多部儿童剧,获得了多方好评.接下来,大家还可在盛京大剧院,梨园剧场及其他公共文化场所欣赏到国有文艺院团带来的现实题材原创儿童剧"我来教你当爸爸",新版大型常态演出音舞诗画"沈阳印记"及歌舞曲艺演出,传统戏曲专场等.大家可媒体,剧场,院团等多渠道发布的具体演出信息.
-答 市文化旅游广电局副局长孟繁涛:""一宫两陵"品牌建设三年行动实施方案"从六方面规划主要任务:一是文化遗产保护工作全面达标,严格履行世界遗产公约,保护遗产的真实性和完整性,统筹实施文物古松和历史风貌保护;二是创建国际一流旅游目的地,升级景区软硬环境和配套服务,提升环境生态;三是构建"盛京文化"学术研究高地,成立"盛京文化"研究中心;四是凸显"一宫两陵"文化活态,创意品牌文化项目;五是做强文旅经济业态,促进文体商旅融合;六是建设东北智慧旅游旗舰,加快数字化,网络化,智能化发展,统筹推进数字博物馆和智慧景区建设.
-根据上述六方面内容,对重点项目进行梳理,形成了"三年行动方案项目表",共6大类,55个项目.</t>
+          <t>标题:杭州西湖一日游｜10大核心景点全覆盖,顺向不折返保姆级路线
+副标题:从湖滨到灵隐,游船+观光车+步行结合,新手也能一天逛完西湖
+来源:小红书
+:4.8w+ :6.2w+ 评论:1389
+标签:西湖攻略 | 杭州旅游 | 环湖路线 | 江南水乡
+来杭州不逛西湖,等于白来!但很多朋友来西湖都走了回头路,一天下来只逛了两三个景点,还累的要死,今天作为杭州本地土著,给大家整理了这条顺向不折返的环湖路线,一天就能打卡苏堤、平湖秋月、灵隐寺、湖滨、雷峰塔、断桥、花港观鱼、三潭印月、曲院风荷、白堤10大核心景点,全程不走回头路,新手也能轻松拿捏!
+想要获取高清环湖路线图、西湖私藏小众机位、杭州美食避坑指南的姐妹,可以加我话:,邮箱:,免费发给大家!
+西湖景区官方预约入口:
+:我的小红书账号[杭州本地通小夏],这篇笔记,抽3个姐妹送杭州美食探店双人霸王餐!
+1. 西湖环湖观光车招手即停,全程40元/人,分段收费,不想走路的姐妹直接冲!
+2. 三潭印月只能坐游船上去,船票55元/人,包含往返船票和岛上门票,一定要提前预约!
+3. 节假日西湖人超级多,建议早上6:30就出发,避开人流高峰,不然拍照全是人头!
+4. 西湖景区免费开放,只有灵隐寺、雷峰塔、三潭印月等小景点需要单独买票!
+早上6:30 我们从湖滨商圈出发,直接打了车前往灵隐寺,车程30分钟,人均20元,早上不堵车,真的太快了!这里提醒大家,千万不要坐地铁去灵隐寺,节假日地铁口到灵隐寺还要走1公里,人挤人,打车直接到景区门口,真的太香了!
+早上7:00 我们抵达灵隐寺景区,首先要购买飞来峰的门票,45元/人,灵隐寺的香花券30元/人,要进去灵隐寺必须先买飞来峰的门票,大家不要搞错了!
+早上7:10 我们先逛了飞来峰景区,这里有超多五代到宋代的佛教造像,最有名的就是弥勒佛造像,真的太震撼了,哪怕是早上,也有很多人来祈福,我们在这里逛了40分钟,看了所有的核心造像,还爬了飞来峰,山顶可以看灵隐寺的全景,真的超美
+早上7:50 我们进入灵隐寺,门口会免费给三炷香,不用自己带香,灵隐寺真的是杭州最灵的寺庙,我每年都会来祈福,这次也求了平安和财运,希望今年顺顺利利!灵隐寺一共有七座大殿,我们从天王殿一直逛到了华严殿,全程逛了1个小时,内心真的特别平静,所有的焦虑都烟消云散了.
+早上8:50 我们从灵隐寺出来,去了旁边的永福寺,这里被称为杭州最美寺庙,人比灵隐寺少很多,风景也特别好,里面还有一个慈杯咖啡,网红寺庙咖啡,我们买了两杯,味道还不错,28元一杯,在景区里真的很良心了,我们在这里逛了30分钟,拍了超多好看的照片.
+早上9:20 我们从灵隐寺出发,乘坐景区直通车前往曲院风荷,车程30分钟,人均10元,早上10:00准时抵达曲院风荷!这里是西湖十景之一,夏天来真的太美了,满池的荷花,风吹过来还有淡淡的荷香,我们在这里逛了30分钟,沿着湖边走,看了荷花池、风荷御酒坊,还拍了超多古风照片,真的太出片了
+早上10:30 我们从曲院风荷出发,步行10分钟就到了白堤的起点,白堤真的是西湖最浪漫的一条路,两边都是柳树和桃树,春天桃花开的时候,真的像走在画里一样!我们沿着白堤往前走,全程步行20分钟,就到了平湖秋月,这里是西湖十景之一,秋天的晚上来这里看月亮,真的绝美,我们在这里停留了15分钟,看了西湖的湖景,吹了吹湖边的风,真的太治愈了.
+早上11:05 我们从平湖秋月出发,步行15分钟就到了断桥残雪,这里是西湖的标志性景点,哪怕是春天,人也超级多,我们在这里打卡了断桥,拍了照片,停留了15分钟,这里提醒大家,断桥的最佳拍照机位不是在桥上,而是在断桥对面的湖边,拍出来的照片完全没有人头!
+中午11:20 我们从断桥残雪出发,乘坐环湖观光车前往湖滨商圈,车程10分钟,人均10元,中午11:30抵达湖滨,这里是杭州最繁华的商圈,有超多好吃的,杭帮菜、奶茶、小吃应有尽有,我们选了一家本地老字号的杭帮菜餐厅,人均80元,吃了东坡肉、西湖醋鱼、龙井虾仁、宋嫂鱼羹,味道真的太正宗了!
+中午11:30-13:30 我们在这里用餐和休息了整整2个小时,吃完饭还在湖滨步行街逛了逛,买了一些杭州特产,西湖藕粉、杭白菊、定胜糕,当作伴手礼送给朋友,湖滨还有西湖博物馆总馆,免费开放,我们进去逛了20分钟,了解了西湖的历史和文化,真的收获满满.
+下午13:30 我们从湖滨出发,步行10分钟就到了一公园游船码头,我们买了前往三潭印月的船票,55元/人,包含往返船票和岛上门票,下午13:40准时开船,乘船20分钟就抵达了三潭印月岛!
+这里是人民币1元纸币的背景图,西湖的核心地标,来西湖一定要来这里!岛上的风景真的太美了,湖中有岛,岛中有湖,我们沿着岛逛了一圈,全程步行40分钟,找到了人民币1元的同款机位,拍了超多好看的照片,还在三潭印月的核心打卡点停留了20分钟,感受了西湖的湖光山色,真的太绝了
+下午14:40 我们从三潭印月的花港观鱼码头下船,直接就到了花港观鱼景区,这里也是西湖十景之一,里面有超大的红鱼池,里面有超多红鲤鱼,我们买了鱼食喂鱼,10元一包,小朋友真的超爱,我们在这里逛了30分钟,还看了牡丹园、芍药园,哪怕不是花季,风景也特别好.
+下午15:10 我们从花港观鱼出发,步行10分钟就到了苏堤的南口,苏堤是西湖十景之首,全长2.8公里,一共有六座桥,我们沿着苏堤往北走,全程步行30分钟,沿途都是柳树和湖水,风吹过来特别舒服,我们在苏堤上拍了超多好看的照片,还在每一座桥上都停留了一下,看了西湖的全景,真的太美了!
+下午15:40 我们从苏堤南口出发,步行10分钟就到了雷峰塔景区,雷峰塔的门票40元/人,我们买了票进去,直接坐电梯上了塔顶,塔顶可以看西湖的全景,整个西湖尽收眼底,真的太震撼了!我们在这里逛了1个小时,看了雷峰塔的遗址,还有很多佛教的文物,下午16:40刚好赶上了日落,在雷峰塔上看西湖的日落,橘红色的阳光洒在湖面上,整个西湖都变成了金色,真的是这辈子见过最美的日落!
+下午17:30 我们从雷峰塔出发,乘坐环湖观光车返回湖滨商圈,车程20分钟,人均15元,下午17:50抵达湖滨,结束了这次完整的西湖环湖之旅!
+最后给大家几个避坑提醒:
+1. 西湖边上的“环湖游船10元一人”全是骗人的,根本不会带你去三潭印月,只会在湖边划一圈
+2. 不要买路边小贩的西湖藕粉,全是假的,一定要去正规的超市买
+3. 节假日千万不要开车来西湖,根本找不到停车位,地铁、打车、观光车才是最优解
+4. 不要相信路边的“杭州一日游”,全是购物团,坑人的很!
+我的公众号[杭州本地生活指南],获取杭州最全的旅游攻略、美食探店、小众打卡地,不迷路,带你玩转杭州!</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>山西旅游网1月19日讯 1月18日,八达岭长城官方大众号宣告"八达岭长城景区暂停对大众开放"的布告.布告称,自2022年2月2日0时至2022年2月3日12时,北京八达岭长城景区执行封锁料理,暂停对大众开放.此举是为了保障2022年北京冬奥会和冬残奥会的顺利从事.此外,八达岭古长...... &amp;别苍蝉辫;阅读全文&amp;驳迟;&amp;驳迟;
-对于旅游目的地来说,品牌营销的目的是"出圈儿"么?是,也不是.毕竟,这个天下上本来没有圈,想红的人多了,就有了圈.面临形成范式的营销政策,以及无法抗拒的"出圈"红利,大多旅游目的地会选择如法炮制.于是,在故宫文创火了后来,文创跨界遍地开花,景区雪糕形成了颜值鄙夷链,各地口红扎堆聚......&amp;别苍蝉辫;&amp;别苍蝉辫;阅读全文&amp;驳迟;&amp;驳迟;
-作为受到新冠疫情最直接影响到的第叁个春运周期,不同于2020年疫情突然暴发引发满天下"进改签"的纷乱局势;也不同于2021年"就地过年"的主基调提早扑灭了"黄金周"的预期;2022年春运在一种对未知远景的渺茫中开启大幕.之因此使春运这场"大迁移"本应带给旅游出行企业的"开年盛宴"......&amp;别苍蝉辫;&amp;别苍蝉辫;阅读全文&amp;驳迟;&amp;驳迟;
-山西旅游网1月18日讯 1月17日,湖南省十三届人大五次会议在长沙开幕,湖南省政协委员,省文明和旅游厅一级巡查员王超祥体现,报告中对于大肆发展文旅产业的内容,让他感触颇深.政府工作报告指出,要加快全域旅游建设,促进文明旅游低质量融合发展;要培育一批文旅产业千亿市,百亿县,亿元镇....... &amp;别苍蝉辫;阅读全文&amp;驳迟;&amp;驳迟;
-1月18日,在北京市新型冠状病毒肺炎疫情防控工作第268场新闻宣告会上,北京市疾病防止控制中心副主任,全国新型冠状病毒肺炎专家组成员庞星火通报,1月17日0时至1月18日15时,本市新增1例核酸检测阳性者.核酸检测阳性者:现住朝阳区平房乡石各庄村,2021年11月来京务工.1月1......&amp;别苍蝉辫;&amp;别苍蝉辫;阅读全文&amp;驳迟;&amp;驳迟;
-1月14日,2022年冬奥会和冬残奥会北京主办城市系列新闻宣告会 - - 社会交通料理方式专场召开,北京市交通委,北京市交管局等相关单位负责人引见冬奥会和冬残奥会期间临时交通料理方式.北京年青报记者从会上获悉,冬奥会和冬残奥会期间北京尾号限行政策不变,但需要注意的是1月29日(周六)按......&amp;别苍蝉辫;&amp;别苍蝉辫;阅读全文&amp;驳迟;&amp;驳迟;
-近期疫情多点散发,中国工程院院士,天津中医药大学荣誉校长张伯礼在答复央视新闻"相对论"发问时体现,散发疫情不免呈现,各地应做好预案,储备好物资,训练好队列,"这些至关重要".张伯礼同时提醒:要是要回家过年,特定要严峻遵守防疫要求,最好是点对点,不要过多聚首."对你自己来说,对别人......&amp;别苍蝉辫;&amp;别苍蝉辫;阅读全文&amp;驳迟;&amp;驳迟;
-1月17日,陕西西安市召开疫情防控新闻宣告会,引见疫情防控最新状况.西安市交通局总工程师杨党校引见,从1月18日起西安全市将有序恢复公共交通运力,首要有以下四个方面的安排和要求.一,维持原则,确保必要交通出行.按照工作安排和部署,维持"外防输入,内防反弹"的原则,在落实疫情防控方......&amp;别苍蝉辫;&amp;别苍蝉辫;阅读全文&amp;驳迟;&amp;驳迟;
-张文宏最新研判:这可能是最终一个"寒冬"
-国家卫健委16日通报,15日0时至24时,31个省(自治区,直辖市)和新疆出产建设兵团报告新增新冠肺炎确诊病例119例,其中本土病例65例(天津33例,其中津南区32例,西青区1例;河南29例,其中安阳市15例,许昌市7例,郑州市7例;北京1例,在海淀区;广东1例,在珠海市;陕西......&amp;别苍蝉辫;&amp;别苍蝉辫;阅读全文&amp;驳迟;&amp;驳迟;
-山西旅游网1月18日讯 昨天记者获悉,交通输送部印发"对于做好2022年道路水路春运疫情防控和输送服务保障工作的通知",根据通知要求,各地交通行业经营者应严查途经北京,张家口旅客48小时内核酸检测阴性证实.通知明确,要落实北京冬奥会防疫要求,鞭策经营者严峻查验终到,途经北京,张家...... &amp;别苍蝉辫;阅读全文&amp;驳迟;&amp;驳迟;</t>
+          <t>标题:读懂西湖的千年文脉｜小众人文深度游路线,避开人流解锁西湖的另一面
+赞同数:2.4w 喜欢数:1.6w 数:3.1w
+很多人来西湖,只知道打卡断桥、雷峰塔、苏堤这些网红景点,逛了一圈只觉得西湖就是一个普通的公园,完全没有感受到西湖的魅力.其实西湖的灵魂,从来都不是网红打卡点,而是它背后承载的千年江南文脉,从白居易到苏东坡,从南宋画院到明清文人,西湖的每一座桥、每一片水、每一块石头,都藏着说不尽的历史故事.
+这次我用2天的时间,走了这条西湖人文深度游路线,避开了人流高峰,打卡了西湖最有文化底蕴的景点,读懂了西湖的千年历史,今天把这条路线全部给大家,不管你是第一次来西湖,还是已经来过很多次,这条路线都能让你看到一个完全不一样的西湖.
+想要获取完整的西湖人文景点讲解词、文史资料、小众打卡点位的朋友,可以给我发私信,也可以加我的交流:,我会把整理好的资料免费发给大家.
+浙江省博物馆官方网址:西湖博物馆总馆网址:
+1. 这条路线以人文景点为主,建议大家提前了解一下西湖的历史,逛的时候会更有代入感
+2. 所有的博物馆、纪念馆都是周一闭馆,大家一定要避开周一出行
+3. 这条路线步行强度不大,全程可以结合景区观光车,不用赶时间,慢慢逛慢慢感受
+4. 很多小众人文景点都免费开放,只需要提前预约就可以进去,大家一定要提前预约
+早上8:00 我们从湖滨出发,步行20分钟就到了断桥残雪,早上的断桥人非常少,完全没有节假日的人头攒动,我们可以安安静静的感受断桥的历史.很多人只知道断桥是白娘子和许仙相遇的地方,却不知道断桥的名字来源于唐代,宋代的时候叫宝祐桥,元代的时候叫段家桥,后来才谐音为断桥,断桥残雪也是西湖十景里唯一一个以雪景闻名的景点,冬天雪后,桥的阳面冰雪融化,阴面还有残雪,远远看去,桥就像断了一样,真的特别有意境.我们在这里停留了30分钟,沿着断桥走了一圈,看了西湖的晨景,感受了千年的历史底蕴.
+早上8:30 我们从断桥出发,沿着白堤往前走,全程步行20分钟,就到了平湖秋月.白堤是白居易在杭州做刺史的时候修建的,当年白居易为了治理西湖,修建了这条堤坝,解决了杭州百姓的灌溉问题,百姓为了纪念他,就把这条堤坝叫做白堤.很多人以为白堤是白居易修的那条堤坝,其实不是,白居易当年修的堤坝已经消失了,现在的白堤是后人为了纪念他命名的,但这并不影响我们在这里感受白居易的那句“最爱湖东行不足,绿杨阴里白沙堤”.
+早上8:50 我们抵达平湖秋月,这里是西湖十景之一,最早建于南宋时期,是南宋画院的取景地之一,康熙皇帝南巡的时候,在这里题写了“平湖秋月”的匾额,这里也是西湖看月亮最好的地方,秋天的晚上,湖面平静如镜,月亮倒映在湖里,真的就是“万顷湖平长似镜,四时月好最宜秋”.我们在这里停留了20分钟,看了里面的碑刻,还有历代文人题写的诗词,真的感受到了中国传统文人的审美意境.
+早上9:10 我们从平湖秋月出发,步行10分钟就到了孤山,孤山是西湖里最大的一个岛,也是西湖文脉最核心的地方,这里有西泠印社、浙江省博物馆孤山馆区、文澜阁、放鹤亭、林和靖墓,每一个地方都藏着西湖的文化灵魂.
+我们首先去了浙江省博物馆孤山馆区,这里是浙江省博物馆的老馆,免费开放,只需要提前预约就可以进去,里面有超多国宝级的文物,最有名的就是雷峰塔出土的文物,还有良渚文化的玉器、越窑的青瓷,我们在这里逛了整整2个小时,看了所有的核心展厅,尤其是雷峰塔文物馆,里面有阿育王塔、鎏金铜佛像,还有当年雷峰塔倒塌的时候出土的佛经,真的太震撼了,让我们对西湖的历史有了更深刻的了解.
+中午11:30 我们从浙江省博物馆出来,去了旁边的文澜阁,这里是清代四库全书七阁之一,也是江南地区唯一保存下来的四库全书阁,里面完整的保存了清代的皇家藏书楼建筑,还有四库全书的复制品,我们在这里逛了30分钟,感受了清代的藏书文化,真的特别有意义.
+中午12:00 我们在孤山脚下的杭帮菜餐厅吃了午饭,人均70元,吃了西湖醋鱼、龙井虾仁、叫花鸡,味道特别正宗,餐厅就在湖边,吃饭的时候还能看西湖的风景,真的太舒服了.
+中午12:00-14:00 我们在这里用餐和休息了整整2个小时,吃完饭在孤山的湖边坐了坐,吹了吹湖边的风,安安静静的感受西湖的氛围,完全没有节假日的喧嚣.
+下午14:00 我们去了西泠印社,这里是中国金石篆刻的圣地,创建于1904年,有“天下第一名社”的美誉,里面的建筑依山而建,一步一景,真的是江南园林的巅峰之作,我们在这里逛了1个半小时,看了印社的碑刻、印章、书画,还有吴昌硕的纪念馆,感受了中国传统金石文化的魅力,哪怕你对篆刻不了解,也会被这里的氛围所感染.
+下午15:30 我们从西泠印社出来,去了放鹤亭,这里是为了纪念宋代的隐士林和靖修建的,林和靖一生隐居孤山,不娶不仕,以梅为妻,以鹤为子,留下了“疏影横斜水清浅,暗香浮动月黄昏”的千古名句,我们在这里停留了20分钟,看了放鹤亭的碑刻,还有林和靖的墓,感受了中国传统文人的隐士风骨.
+下午16:00 我们从孤山出发,步行15分钟就到了曲院风荷,这里是西湖十景之一,最早是南宋时期的酿酒作坊,旁边有很多荷花,夏天的时候,荷香和酒香混在一起,所以叫曲院风荷,我们在这里逛了30分钟,看了里面的园林建筑,还有历代文人题写的关于荷花的诗词,感受了江南园林的审美意境.
+下午16:30 我们从曲院风荷出发,乘坐景区观光车返回湖滨,车程15分钟,结束了第一天的唐宋文脉之旅.
+早上8:00 我们从湖滨出发,乘坐景区直通车前往灵隐寺,车程30分钟,早上8:30抵达灵隐寺景区.灵隐寺建于东晋咸和元年,距今已经有1600多年的历史了,是中国十大古刹之一,也是江南地区最有名的佛教寺庙,很多人来灵隐寺只知道烧香祈福,却不知道灵隐寺背后的历史,还有飞来峰造像的艺术价值.
+我们首先逛了飞来峰景区,飞来峰造像是中国南方石窟艺术的巅峰之作,一共有300多尊五代到宋代的佛教造像,最有名的就是宋代的弥勒佛造像,还有元代的藏传佛教造像,这些造像历经千年,依然保存完好,艺术价值极高,我们在这里请了专业的讲解,100元/小时,讲解的老师讲的特别好,给我们讲了每一尊造像的历史、艺术风格,还有背后的佛教故事,我们在这里逛了整整2个小时,完全刷新了我对灵隐寺的认知.
+早上10:30 我们进入灵隐寺,灵隐寺的建筑是清代重建的,规模宏大,气势恢宏,我们从天王殿一直逛到了华严殿,看了里面的佛像、碑刻,还有历代皇帝题写的匾额,尤其是大雄宝殿里的释迦牟尼佛像,高24.8米,是中国最大的木雕坐式佛像之一,真的太震撼了,我们在这里逛了1个小时,安安静静的感受了佛教文化的氛围.
+早上11:30 我们从灵隐寺出来,去了旁边的永福寺和韬光寺,永福寺建于东晋时期,比灵隐寺还要早,里面的建筑依山而建,风景特别好,韬光寺在山上,是唐代高僧韬光修建的,里面有观海楼,可以看钱塘江的全景,我们在这里逛了1个半小时,人非常少,完全没有灵隐寺的喧嚣,安安静静的感受了佛教寺庙的静谧.
+中午13:00 我们在灵隐寺旁边的素斋馆吃了素斋,人均60元,味道特别好,都是用菌菇、蔬菜做的,口感和肉一样,真的太惊艳了.
+中午13:00-15:00 我们在这里用餐和休息了整整2个小时,吃完饭在寺庙的院子里坐了坐,喝了茶,真的特别放松,所有的焦虑都烟消云散了.
+下午15:00 我们从灵隐寺出发,乘坐景区直通车前往雷峰塔,车程30分钟,下午15:30抵达雷峰塔景区.很多人对雷峰塔的印象只有白娘子,却不知道雷峰塔建于北宋太平兴国二年,是吴越国王钱俶为了供奉佛螺髻发舍利修建的,原来的雷峰塔在1924年倒塌了,现在的雷峰塔是2002年在原址上重建的,里面完整的保存了原来雷峰塔的遗址.
+我们进去之后,首先看了雷峰塔的遗址,遗址坑里有很多当年游客扔的硬币,还有雷峰塔倒塌的时候留下的砖块,然后我们坐电梯上了塔顶,塔顶可以看整个西湖的全景,真的太震撼了,我们在这里逛了1个半小时,看了里面的佛教壁画、文物,还有雷峰塔的历史介绍,对雷峰塔有了全新的认识,完全不是之前印象里的“网红打卡点”.
+下午17:00 我们从雷峰塔出发,步行10分钟就到了苏堤的南口,苏堤是苏东坡在杭州做知州的时候修建的,当年苏东坡治理西湖,用挖出来的淤泥修建了这条堤坝,百姓为了纪念他,就把这条堤坝叫做苏堤,苏堤全长2.8公里,一共有六座桥,对应着苏东坡的那句“六桥横绝天汉上,北山始与南屏通”,我们沿着苏堤走了一段,逛了30分钟,感受了苏东坡的文人风骨,还有西湖的千年文脉.
+下午17:30 我们从苏堤出发,乘坐环湖观光车返回湖滨,结束了这次西湖人文深度之旅.
+很多人问我,为什么来西湖这么多次,还是会被它打动.其实西湖的美,从来都不是单一的风景美,而是风景和人文的完美融合,你走的每一步,都踩在千年的历史上,你看到的每一片风景,都被无数文人墨客写进诗词里,这种穿越千年的共鸣,才是西湖最动人的地方.
+希望这篇攻略,能让你在逛西湖的时候,不仅仅是打卡拍照,更能读懂它背后的千年文脉,感受到江南文化的魅力.
+我的知乎专栏「江南文史札记」,后续会给大家更多江南地区的人文历史、旅行攻略,带你读懂江南的千年文脉.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>儿童价格标准:年龄0-6周岁(不含),不占床,不含早餐,其余服务标准同成人.
-听军号早起天安门观看祖国庄严的[升旗仪式],在雄壮的国歌声中行注目礼,随后游览世界上最大的城市中心广场-[天安门广场]特别赠送集体合照,观毛主席纪念堂,人民大会堂,国家大剧院外景,后游览明,清两代的皇宫,目前世界现存最大,最完整的木质结构的古建筑群-[故宫博物院],下午晚乘车欣赏首都的魅力夜色,游览[警察博物馆](约30分钟)(政策性关闭除外)馆内还设置了寓教于乐的可参与操作项目,如模拟仿真设计训练系统,交通道路情况实时显示,消防逃生自救训练等;乘车经过"北京向上看"[世贸天阶]欣赏全球第二大规模的电子[梦幻凌空天幕]
-打包早餐后攀登[天下第一雄关―居庸关长城],登长城做好汉!中餐后去往[郑家花园](约1.5小时):此地为郑成功第十九代世孙郑家旗的私人家园,您与伟大领袖毛泽东的扮演者国家一级演员王世威老师亲切握手,近距离合影留念;您可以免费品尝到地道的老北京大碗茶,欣赏到濒临灭绝的[老北京天桥绝活](赠送价值220元)后游[科技馆新馆],包括"科学乐园","华夏之光","探索与发现","科技与生活"和"挑战与未来"五大常设主题展厅和公共空间展示区,近观2008年奥运主会场[鸟巢]和水蓝色梦幻游泳馆[水立方]外景,您可下车拍照留念后返回酒店
-餐后参观[清华大学]或[北京大学校] ,后游览中国开放最早,饲养展出动物种类最多的动物园--[北京动物园],这里饲养展览动物500余种5000多只;海洋鱼类及海洋生物500余种10000多尾. 中餐后参观[国子监](游览约150分钟),游皇家学府,参加[国子监"开笔礼"]仪式,这是中国传统中对少儿开始识字习礼的一种启蒙教育形式.参观皇帝举行国家祭孔子先师仪式的场所[孔庙].车游中华世纪坛,远观中央电视塔(405米),后游览美国"时代"周刊25个"亚洲最佳风情地"之一[南锣鼓巷],后乘火车赴南京.
-特别注明:清华北大在暑期会有临时活动政策性关系(如开学典礼 毕业典礼等)只参观外景,下车门口拍照留念.
-南京早接团,同学们在导游的带领下,游览[中山陵]景区(周一陵寝关闭)参观孙中山先生的陵墓,听国父生前的故事,感知今天的幸福生活来之不易!参观青少年爱国主义教育基地 - - [南京大屠杀纪念馆](周一闭馆),参观万人坑,和平广场,纪念馆表馆,警钟缅怀南京30万死难同胞.整个展区肃穆,宁静.主体设施为大型墓室史料陈列厅,立体化的还原历史.游览[十里秦淮夫子庙商业街]自由活动,寻找唐代诗人刘禹锡诗中描写的"乌衣巷",我们一起走进大文豪朱自清笔下"浆声灯影里的秦淮河"吧,参观我国古代考场 - - 江南贡院,唐伯虎,郑板桥,林则徐,董必武都曾经在这里学习过,考试过;今天的我们是否也该从他们身上学习那种"十年寒窗"的刻苦精神!
-早餐后车赴杭州,中餐后游览天下西湖三十六,就中最好是杭州的一--[西湖风景区],该景区是一处以秀丽清雅的湖光山色与璀璨丰蕴的文物古迹和文化艺术交融一体的国家级风景名胜区,有苏东坡纪念馆,漫步苏堤,花港观鱼,阮墩环碧,孤山烟岚等.参观[岳王庙景区],参观观牌楼,忠烈祠,精忠柏亭,碑廊,岳飞墓等.欣赏中国人气最旺的主题公园 - - [宋城景区](不含宋城千古情表演)这里是中国非物质文化遗产集聚地,孩子们可以尽情享受"宋城泼水节"的淋漓快乐!水上竞技比赛激励拼搏!
-早餐后参观中国百年名校----[浙江大学].这是一所具有百年历史底蕴的教育部直属全国重点大学,是中国首7所"211工程",首批9所"985工程","珠峰计划","111计划"重点建设的名牌大学之一.车赴铜乡,游览旧时江南,梦里水乡,江南六大古镇之一[乌镇东栅]原汁原味的水乡风貌和千年积淀的文化底蕴,使乌镇成为目前江南古镇独具风韵的佼佼者,游览江南百床馆,江南民俗馆,三白酒作坊,宏源泰染坊,江南木雕陈馆等.车赴上海,游览[上海科技馆]是上海重要的科普教育基地和休闲旅游基地,展示内容由天地馆,生命馆,智慧馆,创造馆,未来馆等五个主要展馆和临展馆组成,在赏心悦目的活动中,孩子们接受现代科技知识的教育和科学精神的熏陶.
-早餐后游览[上海迪斯尼乐园]作为中国大陆首座迪士尼主题乐园,上海迪士尼乐园将为孩子们提供无限可能,创造值得珍藏一生的回忆.上海迪士尼乐园将会是一座神奇王国风格的迪士尼主题乐园,包含六个主题园区:米奇大街,奇想花园,探险岛,宝藏湾,明日世界,梦幻世界.六大主题园区充满郁郁葱葱的花园,身临其境的舞台表演,惊险刺激的游乐项目 - - 其中还有许多前所未见的崭新体验 - - 孩子们将会在这里找到快乐的天地.
-早餐后我们游览[上海巧克力乐园]上午在中国第一家大型巧克力主题公园来一次激情碰撞,在里能看到中国最大的巧克力城堡,欣赏到独一无二的面包音乐打击秀,品尝到各色奇异的美食,同时我们经典烘培学院大师们还会亲自出马教我们怎么制作饼干,披萨,巧克力,棉花糖等,我为"爸爸. 妈妈"亲手制作的自己的巧克力!后游览[中华艺术宫](原世博会中国馆,不含清明上河图小门票)中华艺术宫是具有保管,学术研究,陈列展示,普及教育和对外交流为基本职能的艺术博物馆,将,展示和陈列反映中国近现代美术的起源与发展脉络的艺术珍品.晚根据列车时刻前往火车站,返回乌鲁木齐,预计第11天抵达,结束愉快的旅途
-住宿:北京入住商务连锁酒店,华东入住高端连锁酒店(预备四星级),如果产生单男单女,将由领队调整为三人间.请谅解.
-当地空调VIP旅游车,每人一正座(21座以下的车型均无行李箱);
-门票:景点第一大门票(不含景区电瓶车及自理项目;赠送项目,如遇不可抗拒因素无法成行,门票不退)
-1,自由活动期间交通费,餐费,等私人费用;
-2,不提供自然单间,产生单房差或加床费用自理.非免费餐饮费,洗衣,理发,电话,饮料,烟酒,行李搬运等费用;
-3,行程中未提到的其它费用:如特殊门票,游船(轮),缆车,景区内电瓶车,动车票等费用;
-4,不含因旅游者违约,自身过错,自身疾病,导致的人身财产损失而额外支付的费用;
-5,因交通延误,取消等意外事件或不可抗力原因导致的额外费用;
-6,"旅游费用包含"内容以外的所有费用.
-1,全程使用空调旅游车,每人一个正座位,提供导游兼司机服务.如有特别要求车辆,请提前说明,重新核价.旅游车到景点,餐厅期间客人统一下车,不在单独开车门给客人上车休息和开空调.贵重物品不能存放在车上.
-2,当地酒店标准比内地偏低,请旅游者提前做好心理准备.如遇旺季(每年3月1日至10月15日之间及特殊节假日)酒店资源紧张或政府临时征用等特殊情况,造成行程中备选酒店客满,我社有权调整为同等级标准以上酒店.酒店的退房时间为中午的12:00,返程为晚班机的旅游者可把行李寄存在酒店前台后自由活动或自补房差开钟点房休息.
-3,行程中所含的餐食,早餐为酒店房含,不用不退.正餐按产品用餐标准操作,不含酒水.
-4,行程所含门票指进入景区的首道门票,不包括该景区内电瓶车或景区内其他另行付费景点门票.行程中所含的所有景点门票已按景点折扣门票核算,故客人持有军官证,残疾证,老年证等优惠证件及其他特殊身份人士,则无退还.
-如遇人力不可抗拒因素或政策性调整导致无法游览的景点,我社有权取消或更换为其它等价景点,赠送景点费用不退,并有权将景点及住宿顺序做相应调整;景区后括号内备注游玩时间为抵达景区开始到离开景区为止时间.
-5,维权事宜注意:客人必须填写"游客意见书",如果客人在意见单上填写"不满意"一栏后,可视为投诉范畴,并在意见单上填写投诉理由;恕不受理客人因虚填或不填意见书而产生的后续争议.请各位游客必须认真仔细填写,由此而造成的一切损失由客人自负.投诉问题在旅游目的地就地解决,请组团社告知游客/领队/全陪,返程后我社不接收投诉!旅行社不受理因虚假填写或不填意见书而产生的后续争议和投诉;</t>
+          <t>发布时间:2025-09-15 18:00:00
+来源:马蜂窝旅游网
+本次西湖游全程8小时,覆盖20个核心景点,涉及游船、观光电瓶车、共享单车、步行4种交通方式,所有时间节点精确到分钟,以下为完整记录:
+08:00:从杭州市西湖区湖滨银泰酒店出发,骑行共享单车(哈啰单车,1.5元/15分钟)至西湖湖滨三公园,骑行10分钟,08:10抵达.
+08:10:在湖滨三公园租赁西湖观光电瓶车(60元/人,环湖线),核验租车码,耗时20分钟,08:30发车开始游览.
+08:30:电瓶车从湖滨三公园出发,5分钟至断桥残雪(08:35),停留25分钟(08:35-09:00),打卡断桥、拍摄西湖全景.
+09:00:电瓶车从断桥出发,8分钟至白堤(09:08),下车步行5分钟至平湖秋月(09:13),停留20分钟(09:13-09:33),观赏西湖秋月碑、湖面风光.
+09:33:从平湖秋月出发,步行10分钟至孤山公园(09:43),停留10分钟(09:43-09:53),打卡孤山“天下第一孤山”石刻,休整至10:00.
+10:00:从孤山公园出发,步行5分钟至中山码头(10:05),购买西湖游船票(55元/人,含三潭印月门票),排队10分钟(10:05-10:15),登船前往三潭印月,航行15分钟,10:30抵达.
+10:30:从三潭印月码头出发,步行5分钟至“三潭印月”石塔观景台(10:35),停留30分钟(10:35-11:05),拍摄人民币1元背景同款视角.
+11:05:从观景台出发,步行10分钟至九曲桥(11:15),停留10分钟(11:15-11:25),休整5分钟至11:30,登船返回花港码头.
+11:30:游船从三潭印月出发,航行15分钟至花港码头(11:45),步行5分钟至花港观鱼餐厅(11:50),用餐30分钟(11:50-12:20),人均60元(推荐西湖醋鱼、龙井虾仁),休整10分钟至12:30.
+12:30:从花港观鱼餐厅出发,步行8分钟至花港观鱼核心区(12:38),停留25分钟(12:38-13:03),观赏红鱼池、牡丹园.
+13:03:从花港观鱼出发,骑行共享单车至雷峰塔景区(13:03-13:18,骑行15分钟),购买雷峰塔门票(40元/人),排队5分钟(13:18-13:23),入园后乘电梯至塔顶,停留30分钟(13:23-13:53),俯瞰西湖全景,休整至14:00.
+14:00:从雷峰塔出发,乘坐观光电瓶车至苏堤南入口(14:00-14:10,车程10分钟),步行5分钟至苏堤春晓(14:15),停留40分钟(14:15-14:55),徒步苏堤前两桥(映波桥、锁澜桥),观赏两岸风光.
+14:55:从苏堤出发,步行10分钟至曲院风荷(15:05),停留20分钟(15:05-15:25),观赏荷花池(夏季)、风荷亭,休整至15:30.
+15:30:从曲院风荷出发,骑行共享单车返回湖滨银泰酒店(15:30-15:55,骑行25分钟),归还单车,耗时5分钟(15:55-16:00),结束行程,休整30分钟至16:30.
+- 景点POI:湖滨三公园、断桥残雪、白堤、平湖秋月、孤山公园、三潭印月、九曲桥、花港观鱼、雷峰塔、苏堤春晓、曲院风荷;
+- 交通方式:共享单车、观光电瓶车、西湖游船、步行;
+- 时间节点:08:00(出发)、08:30(电瓶车发车)、10:00(登船)、11:30(午餐)、12:30(花港观鱼)、14:00(苏堤)、15:30(返程);
+- 消费实体:共享单车1.5元+后续计费3元、观光电瓶车60元、游船票55元、午餐60元/人、雷峰塔门票40元.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>刚过去的元宵节,你是不是被故宫的上元节灯光秀翻了屏?要想起中国最红的博物馆,非故宫什科了.
-本文摘要:刚过去的元宵节,你是不是被故宫的上元节灯光秀翻了屏?要想起中国最红的博物馆,非故宫什科了.
-刚过去的元宵节,你是不是被故宫的上元节灯光秀翻了屏?要想起中国最红的博物馆,非故宫什科了.从纳着雍正,乾隆等皇帝温柔卖萌,到开卖故宫口红上线即被抢走断货,再行到如今94年来首次对外开放夜场票,票价爆炒到9999仍一票难求.被迫说道,靠着不跪不吃"紫禁城"的老本,这位600多岁的刻苦老人因不断创新,让"故宫"这座就让高冷的中华文化圣地,大大"火"上新台阶,沦为受到全民欢迎的最红景区.事实上,这样的例子在旅游行业不是个案.
-重庆奥陶纪,湖南张家界等景区,都靠着不断创新,挣脱了历史,区位和大自然禀赋的束缚,从一众景区中脱颖而出,逆天改命.靠创意战胜"年龄" 600岁故宫实力演译"老来俏" 这个元宵节,故宫夜景翻轰很多人的微博和朋友圈.
-在"超级大月亮"的点缀下,闪亮的灯光将故宫的飞檐,红墙,黄瓦等传统元素照亮的时尚迷人,94年来首次夜间对外开放的紫禁城,令其无数无法到现场的网友于隔年屏艳羡.可以意识到,如果不创意,最近几年的"故宫热"会再次发生,故宫还不会向之前一样,做到一位高冷的长者,拒绝接受着世人的凭吊,祭拜以及敬而远之.故宫的创意,一是不畏年龄,擅于利用媒体展开IP传播.
-一部"我在故宫建文物"豆瓣评分9.2分,让无数年长网民从此酷爱了故宫这座人类文化宝库,现在每年,都有将近4万年轻人录取故宫,要来这里建文物.一张故宫雪景照片,可以在微博惹来5000万网友围观.
-二是不畏身份,耕耘文创,将皇家威仪暂放一旁,喊出皇帝,娘娘笑面迎接人陪你玩骗.比如,人们必须手机壳,故宫文创就获取480种有所不同样式的手机壳.有手机就必须充电器,于是就设计了印上"正大光明"字样的充电器.
-2018年底,故宫再度出大讨,发售199一支的故宫口红,预售就卖断了货.业内人士回应,对于故宫这种低频旅游景区来说,如果只能靠旅游,很多人一生有可能只来一次,但是靠着进占文创,故宫走出了每个人的生活,几乎转变了低频消费的痛点.
-有网友说道,"订立了故宫出有的真丝睡衣,涂抹上故宫的口红,摇着故宫天猫分店快活的扇子,感觉自己就是皇后娘娘!"故宫院长单霁翔回应,去年故宫文创产品超强15亿元,秒杀1500多家A股上市公司.一系列活动,将近年来的"故宫热"推上一个个新的高潮.作为享有600多年历史的老人,故宫就让向一位低冻,疲乏的长者,拒绝接受着世人的敬重和凭吊,可他却没想到不愿,总算换回了一副面孔,每日红光满面陪伴你一起"蹦迪".
-年龄和过往的威仪,不仅没沦为他的包袱,反而让他逆的愈发不会玩游戏,谓之人祭拜.靠创意战胜"区位" 奥陶纪靠"悬崖+游乐场"逆袭成网红 相比于故宫依赖创意转变了自己古老,高冷的形象,重庆一家网红景区 - - 万盛奥陶纪,则用创意转变了自己的区位短板,从一众主打大自然美景的区县景区中脱颖而出,沦为重庆可与洪崖洞相媲美的一线景区.
-2015年五一节,奥陶纪景区在距离主城1.5小时车程的万盛黑山门口.最初,这个景区的主打是大自然美景,科幻馆,游乐场和夜间表演.但是,结果并不理想,由于区位不出主城,大自然景色也稍大众化,更加没有人在山野中等到晚上看夜间表演,因此首年门票收益只有将近100万元,和周边的黑山谷相去甚远.
-奥陶纪未早已堕落,而是自由选择从仿效和同质化中回头出来,回头内容创意之路.最近两年,奥陶纪发明者了一种全新的景区形态 - - 悬崖主题游乐场.市场上从来不缺乏以大自然大自然地貌著称的景区,更加不缺乏游乐场,但是,却缺乏一个将悬崖地貌和体验式游乐融合一起的新型景区.
-在这里,悬崖为游乐场特了一层实景体验的滤镜,坠楼机,秋千等奇怪的游乐设备因为修筑在了悬崖边瞬间令人毛骨悚然;游乐场又让悬崖仍然冰冷,当你搭乘每个项目时,都是在跟悬崖对话,任你"勾引".为了做到浅悬崖游乐场的大逆转与性刺激,奥陶纪研发了诸多原创高空项目,例如,这里有破吉尼斯世界纪录的悬崖悬挑空中玻璃廊桥 - - 天空悬廊,让你就越回头就越响,全球九大最大逆转高空项目 - - 无限大进步,一不留神就安全性坠崖的性刺激,中国最久的悬崖秋千 - - 21米可怕秋千等,让你体验前一秒坠楼,后一秒飞天的反感高差感觉.更加最重要的是,奥陶纪景区空缺了全国景区另一空白,即几乎符合了18-35岁年长客群的市场需求.他们老实,富裕活力,奥陶纪为他们自定义了九大原创高空项目,让游客需要乐趣获释荷尔蒙;他们乐意共享,奥陶纪就通过创新性引领,希望他们在时尚的响音,幸福的慢手上晒出自己拍下的大逆转视频.
-如今,一个普通游客在奥陶纪摄制悬崖秋千,无限大进步等网白项目的短视频,经常以致于就能超过上百万播出量.即使窜红之后,奥陶纪也没"吃老本",而是大大展开项目创意.仅有在2018年,就将景区项目由此前的20多个减少至50多个,全面符合仅有客群的游览市场需求.
-例如开办西南唯一一个同时可符合玩雪滑雪和玩游戏冰滑冰的项目,阳春三月都能打雪仗,新人奖冰灯;例如修筑景区酒店,更有游客在奥陶纪2日游.玩法大大装修.
-2019年7天的春节假期,奥陶纪人流量倒数5天超过景区仅次于承载量.其中,6成都是第一次来这里的外地游客,再度检验了奥陶纪作为网红景区的持续魅力.靠创意突破"既有优势" 张家界从很美的景区到一生无以去之地 在湖南,有一个景区本身就具备得天独厚的大自然优势,却仍大大依赖景区创意,突破了既有优势,被网友受封和所有大自然景区有所不同的"一生无以去之地".
-自创办之初,张家界就以其得天独厚的旅游资源闻名于世.区内以世界少见的石英砂岩峰林峡谷地貌为主体,集桂林之秀,黄山之魁,华山之险,泰山之雄于一体,藏赂,桥,洞,湖,瀑于一身,有"不断扩大的盆景,增大的仙山"之美称.如果没创意,在最不补美景的国内景区行业,后起之秀张家界有可能意味着是个"小五岳",沦为一个区域性旅游品牌.
-但是,从景区问世起,张家界就将做事情的创新者本色充分发挥的淋漓尽致.趁此机会飞机飞到天门山,世界特技飞行大师以头脑的勇气顺利驾驶员飞机穿过天门洞,建构出有人类首次驾机穿过大自然山洞的飞行中奇迹,"穿过天门"的伟业一时间震撼世界,神秘的张家界天门洞也因此声名远播.然后就是联姻好莱坞王牌编剧卡梅隆,电影"阿凡达"在张家界哈利路亚山取景,被游客称作现实版的潘多拉星球.
-再就是大手笔修筑知名的张家界大峡谷玻璃桥,这座桥面长375米,长6米,桥面距谷底300米的全透明玻璃桥,不仅踏上去让人胆寒,更加刷新世界最低最久玻璃桥的纪录,沦为张家界旅游的标志性项目.业内人士回应,如今,国内很多特色小镇此起彼伏,但是,却没确实修出特色.故宫,奥陶纪,张家界的三个案例,才是认为了决心,只有通过内容创意,传播创意,才能道别"泯然众人",顺利被人忘记并青睐.</t>
+          <t>发布时间:2025-09-15 18:00:00
+来源:马蜂窝旅游网
+层级1(整体):1天经典环线
+层级2(核心分段):
+- 上午:断桥残雪→白堤→平湖秋月→三潭印月;
+- 下午:花港观鱼→雷峰塔→苏堤春晓→曲院风荷.
+层级3(子路线):各景点线性串联,无摄影适配、无季节适配建议.
+层级1(整体):3天2晚季节适配环线(基于官方路线优化,分摄影时段+季节分支)
+层级2(每日结构):核心摄影段+休整段+小众季节分支段
+层级3(时段细分):清晨/上午/中午/下午/傍晚,含停留时长+摄影建议+季节适配.
+层级2-1:核心摄影段(06:00-10:00,清晨黄金光)
+层级3-1:06:00 骑行共享单车至断桥残雪(06:10),步行5分钟至断桥东侧机位(06:15),停留40分钟(06:15-06:55),拍摄春季断桥桃花+湖面晨雾(官方路线无季节适配);
+层级3-2:06:55-07:03 步行至白堤(8分钟),停留30分钟(07:03-07:33),拍摄白堤柳丝(春季最佳);
+层级3-3:07:33-07:43 步行至平湖秋月(10分钟),停留25分钟(07:43-08:08),拍摄平湖秋月晨景(官方路线无摄影时段);
+层级3-4:08:08-08:23 步行至孤山公园(15分钟),停留30分钟(08:23-08:53),拍摄孤山梅花(春季小众景观);
+层级3-5:08:53-09:03 步行至中山码头(10分钟),停留17分钟(09:03-09:20),等待早班游船(避开人流);
+层级3-6:09:20-09:35 乘坐游船至三潭印月(15分钟),停留25分钟(09:35-10:00),拍摄春季三潭印月水域的睡莲.
+层级2-2:休整段(10:00-12:00)
+层级3-1:10:00-10:15 乘船返回花港码头(15分钟),步行10分钟至花港观鱼餐厅(10:25),用餐45分钟(10:25-11:10);
+层级3-2:11:10-12:00 餐厅周边休整(50分钟),整理摄影素材(官方路线无素材整理).
+层级2-3:小众季节分支段(12:00-17:00,春季小众景观)
+层级3-1:12:00-12:15 骑行共享单车至柳浪闻莺(15分钟),停留40分钟(12:15-12:55),观赏春季柳浪闻莺的黄莺栖息地(官方路线未提及);
+层级3-2:12:55-13:10 骑行至钱王祠(15分钟),停留30分钟(13:10-13:40),拍摄钱王祠春季牡丹;
+层级3-3:13:40-17:00 返回断桥,补拍春季午后的湖面光影(3小时20分钟),避开人流高峰.
+层级2-1:核心深度段(07:00-11:00)
+层级3-1:07:00-07:15 骑行至雷峰塔(15分钟),步行5分钟至雷峰塔西侧机位(07:20),停留35分钟(07:20-07:55),拍摄春季雷峰塔与西湖的“雷峰夕照”预拍(官方路线无深度摄影);
+层级3-2:07:55-08:10 步行至花港观鱼(15分钟),停留30分钟(08:10-08:40),观赏春季红鱼池的锦鲤+牡丹;
+层级3-3:08:40-08:55 步行至苏堤南入口(15分钟),停留40分钟(08:55-09:35),徒步苏堤映波桥至锁澜桥(春季苏堤春晓最佳段);
+层级3-4:09:35-09:50 步行至压堤桥(15分钟),停留25分钟(09:50-10:15),讲解苏堤六桥的历史背景;
+层级3-5:10:15-10:30 步行至望山桥(15分钟),停留30分钟(10:30-11:00),拍摄春季苏堤的油菜花田.
+层级2-2:休整段(11:00-13:00)
+层级3-1:11:00-11:20 骑行至知味观(20分钟),用餐50分钟(11:20-12:10);
+层级3-2:12:10-13:00 知味观周边休整(50分钟),体验西湖龙井茶品鉴(官方路线无民俗体验).
+层级2-3:小众文化分支段(13:00-17:00)
+层级3-1:13:00-13:20 骑行至郭庄(20分钟),停留1小时(13:20-14:20),参观春季郭庄花展(官方路线未推荐);
+层级3-2:14:20-14:40 骑行至虎跑公园(20分钟),停留40分钟(14:40-15:20),了解虎跑泉的茶文化;
+层级3-3:15:20-17:00 返回苏堤,补拍春季傍晚的苏堤落日(1小时40分钟),官方路线无傍晚摄影.
+层级2-1:核心补充段(09:00-11:00)
+层级3-1:09:00-09:30 湖滨采购西湖特产(30分钟);
+层级3-2:09:30-10:30 参观西湖博物馆(1小时),了解西湖的水文生态(官方路线无生态体验);
+层级3-3:10:30-11:00 整理行李、返程准备(30分钟).
+1. 官方路线:线性层级(整体→分段→景点),无摄影适配、无季节分支、无文化体验;
+2. 实际路线:摄影+季节层级(整体→每日摄影段→核心/休整/小众→时段/摄影建议/季节),按春季摄影黄金时段设计,增加小众机位和茶文化体验,适配深度游客.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>急求北京4日自由游最佳线路方案第一天:天安门,人民大会堂,故宫,景山,北海(天坛) 坐地铁1号线在天安门东或天安门西下,步行就能到天安门. 如果你想看升旗,天不亮就得要起床,不过那时候地铁还没开,如果住得较远的话,就只
-坐地铁1号线在天安门东或天安门西下,步行就能到天安门. 如果你想看升旗,天不亮就得要起床,不过那时候地铁还没开,如果住得较远的话,就只能打的去了.看完升旗后可以在天安门广场上转转,等到8点的时候,可以在天安门广场去排队参观毛主席纪念堂.出来后你就从天安门广场的地下通道到天安门城楼附近,你可以到天安门城楼上去看看,下来后你一直往里面走,就是故宫的午门,沿着中轴线向北游览三大殿,从神武门出来,对面就是景山公园,从景山公园的西
-起了个大早,飞机11:00左右到达北京机场,出机场坐了机场大巴,16元一张票.由于之前在前门的酒店订了房间,所以我们坐到了雅宝路(也就是国际饭店),再打车过去,不远.
-吃了简单的午饭,我带上租的U伴电子导游,朋友介绍的,说是用得不错,讲解很详细,没导游也可以玩得很好.是GPS定位,有电子地图,去哪都不迷路,还有就是如果打车的时候给司机看看,司机都不敢绕道了,估计这次能省出不少打车冤枉的车钱.
-北京四日游 怎么玩好?请推荐详细点的路线~酒店在天安门那边,想去长城,798,三里屯,故宫......请指点下~
-我建议您分这样几天:
-第一天,早起一点儿,上午游览故宫,如果是十一假期以后,从南门进,顺便看看天安门,大剧院,如果是十一期间,故宫好像有些地方不开放,你可以坐一站5路汽车从北门进,故宫最好多转转,珍宝馆是单收费的,不过看看挺不错的.下午2点多钟从故宫北门出来,进北海右边的一条胡同,打听一下,里边有家很正宗也很便宜的北京小吃店,东西很多,要是不嫌贵,那里也有大三元或者进北海吃仿膳.下午逛北海,出北门,有时间可以转恭王府(不过既然已经去了故宫,恭王府转不转意义不大)在地安门附近吃晚饭,晚上可以在后海转转</t>
+          <t>08:00 从湖滨银泰出发,骑行共享单车前往断桥残雪,骑行10分钟.抵达后,我先在断桥边的长椅坐下,这里的清晨很安静,只有鸟鸣声,它的湖面像镜子一样,能倒映出断桥的轮廓.
+08:20 走到断桥的东侧,它是拍摄断桥全景的最佳机位,这里的游客不多,比其他机位安静,要是你想拍无人的照片,一定要在清晨来,因为它的人流高峰在9点后.断桥的栏杆是石质的,它的上面刻着花纹,和其他桥梁的栏杆不同,它的花纹是荷花图案,代表西湖的荷文化.
+08:40 从断桥走到白堤,它是西湖的长堤,这里的柳树是西湖的特色,它的枝条垂到水面,和其他地方的柳树不同,它的枝条更细更长.走在白堤上,微风拂过,它的柳丝会扫过脸颊,这里的空气里有淡淡的桂花香(秋季),它的香味很清新,让人放松.
+09:10 从白堤走到平湖秋月,它是西湖十景之一,这里的石碑是康熙皇帝题写的,它的字体是楷书,和其他石碑的字体不同,它的笔画更工整.平湖秋月的湖面很平静,它的倒影比其他地方更清晰,要是你带了相机,一定要用慢门拍摄它的水面.
+09:30 从平湖秋月走到中山码头,它是西湖游船的主要码头,这里的游船有两种,一种是画舫,一种是快艇,它的画舫更适合观光,因为它的速度慢,能欣赏沿途的风景.购买游船票后,排队10分钟登船,它的船舱很宽敞,能坐50人,这里的座位靠窗的最好,因为它的视野无遮挡.
+10:00 乘坐游船前往三潭印月,它是西湖的标志性景观,这里的石塔是人民币1元背景的原型,它的数量是三座,和其他景观不同,它的位置在湖中心.登上三潭印月岛,走到九曲桥,它的桥身是弯曲的,这里的锦鲤很多,它的颜色有红、白、黑,要是你投喂鱼食,它会围过来抢食.
+10:40 从三潭印月返回花港码头,步行至花港观鱼,它是西湖十景之一,这里的红鱼池是核心景观,它的锦鲤有上百条,和其他鱼池的鱼不同,它的鱼更大更肥.花港观鱼的牡丹园(春季),它的牡丹品种有几十种,这里的花色很丰富,它的花期在4月,要是你春季来,能看到它的盛景.
+11:20 从花港观鱼走到雷峰塔,它是西湖的地标,这里的新塔是重建的,它的内部有电梯,和旧塔不同,它的设施更现代化.登上雷峰塔顶层,俯瞰西湖,它的全景尽收眼底,这里的视野比其他地方更好,因为它的海拔更高.雷峰塔的底层有木雕,它的内容是白蛇传的故事,和其他木雕不同,它的细节更丰富.
+12:00 从雷峰塔走到餐厅,这里的主打菜是西湖醋鱼,它的味道酸甜,和其他地方的醋鱼不同,它的鱼是西湖的草鱼,肉质更嫩.吃完饭休息了一会儿,走到餐厅外的茶摊,这里的龙井茶是西湖的特产,它的茶叶是明前茶,和其他茶叶不同,它的口感更鲜爽.
+12:40 从茶摊走到苏堤,它是苏轼修建的长堤,这里的六桥是苏堤的特色,它的映波桥是第一桥,这里的荷花是西湖的名荷,它的花期在7-8月,要是你夏季来,能看到它的荷花盛开.走在苏堤上,它的路面是石板铺的,和其他长堤不同,它的石板更平整,走起来不累.
+13:20 从苏堤走到曲院风荷,它是西湖十景之一,这里的荷花池是核心景观,它的荷叶铺满水面,和其他荷花池不同,它的荷叶更大,它的荷花是粉色的,很娇艳.曲院风荷的风荷亭,它的位置在荷花池中心,这里的拍照视角最好,因为它能拍到它的全景.
+14:00 从曲院风荷骑行共享单车返回酒店,它的骑行路线沿湖,这里的风景很美,和来时的路线不同,它的路线更贴近湖面.回到酒店,回顾当天的行程,西湖的美在于它的婉约,这里的每一个景点都有诗意,它的文化底蕴深厚,要是你没来过,一定要来感受一下它的温柔.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>今日(2月8日)是农历小年,沈阳故宫博物院在景区内挂起了门神和对联,迎接新春的到来."到沈阳故宫过大年"活动是沈阳故宫博物院推出的传统文化项目,从2005年春节举办首届伊始,至今连续举办了13届,在沈阳文博界已经形成品牌效应.昨日,沈阳晚报,沈报融媒记者从沈阳故宫博物院了解到,2018年"到沈阳故宫过大年"活动将继续为观众奉上形式多样的文化大餐.
-沈阳故宫与沈阳演艺集团的清文化主题演出"皇宫过大年"将于2月17日(大年初二)到2月21日(大年初六),3月2日(正月十五)每天10时,11时在崇政殿前广场演出两场,共演出12场,重现当年盛京皇宫中过春节的喜庆场面.此外,非物质文化遗产将走进沈阳故宫,届时沈阳故宫将邀请省市,各级非遗传承人进行展示表演;今年春节期间,沈阳故宫首次推出儿童体验馆活动,孩子们和家长一起进行亲子手工艺活动,一家人把喜气洋洋的手作工艺品带回家,何乐而不为.
-过年期间,沈阳故宫推出"白银时代 - - 中国外销银器展""花开富贵 - - 院藏牡丹画展""院藏十二生肖展"三项展览,以飨观众.昨日沈阳故宫还向记者展示了2018新春特供文创产品,包括服饰,首饰,皮包等,产品上的纹饰元素是从文物"清大红缂丝八团金龙单袍"中提炼出来,堪称传统与现代的结合,精美无比.
-沈阳晚报,沈报融媒记者 张宁 摄影记者 常晟罡
-声明:本文由入驻搜狐号的作者撰写,除搜狐官方账号外,观点仅代表作者本人,不代表搜狐立场.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>本文摘要:时隔故宫之后,本市又多了一家中止纸质门票的博物馆.
-时隔故宫之后,本市又多了一家中止纸质门票的博物馆.北京青年报记者昨日得知,国家博物馆月中止纸质门票,今后观众所持身份证才可必要转入国博参观.据国家博物馆官微消息,国博月底近期月道别纸质门票,实施免票参观.这意味着,今后观众所持身份证才可必要入馆.
-除了身份证,非纸质临时身份证,老年证,户口本,户籍证明,社保卡,中小学生学生证,残疾证,军官证,士兵证,护照,港澳通行证,台胞证,驾驶执照等有效证件也都可以作为入馆凭证.对于观众广泛关心的否限流问题,国博方面回应,目前继续没容许人数,观众可以刷身份证必要进馆,也可以提早购票.改扩建后的国博自开馆以来,仍然实施免费参观制度(特展除外),观众可提早购票,并于参观当日在西门南侧票务中心凭有效证件换领国家博物馆免费参观券后,从西门入场参观各免费展出.
-如没能提早购票,也可以于参观当日通过现场领票方式取得免费参观券.不过,提早购票可以节省不少时间,提早购票顺利的观众还可保证腾出当日免费参观券.此前,曾有网友责怪,转入国博参观要排队两三个小时,算上存包,取票,安全检查,中间要经历多次排队.对于此次中止纸质门票,网友态度不一.
-有人在国博官微下方facebook,指出"较少一个领票的程序显然便利多了~",也有人抱着浪漫心理回应:"有票知道也很好!我的票都保有着,显然票又是过去式啦!"根据新近公布的"中国国家博物馆观众数据报告(2017年度)",2017年中国国家博物馆总共对外开放312天,招待观众总数8062625人次,平均值每天招待观众2.6万人次.其中,2月观众接待量仅次于,超过861194人次,1月观众接待量大于,为517568人次.6月至10月的5个月中观众接待量月均维持在70万 - 80万人次.据报,去年10月10日,故宫早已首度构建了纸质票"除役".
-有所不同的是,故宫采行全网售票,并设每日8万人的参观下限.据报导,故宫网售过程基本构建了观众无逗留,观众免职排队购票的苦恼,人均购票等候时间减少至5分钟左右.</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>故宫重华宫,养心殿还处于未开放状态,但在全景故宫上便可一键畅游这些地方.
-故宫博物馆的全景故宫集全景和科普于一身,可360度浏览故宫,全景故宫利用三维空间整体展示故宫全貌,文字解说,多角度翻转,切换秋冬模式,在全景故宫上可以轻松畅游三大殿,后三宫,东六宫,三大御苑花园等众多区域,云游体验古代宫廷生活!
-摄图网:ID-501531024除此之外,还有线上数字文物库,故宫名画记可以浏览,张择端,阎立本,顾恺之等众多名家的画作都可欣赏,可随时调放大小,查看画作细节.
-小提示:在[西安本地宝]字展馆,参展名画秦始皇陵博物馆数字展厅分为全景兵马俑,平天下展览,四海一虚拟展览以及馆内展览.
-摄图网:ID-401908875在数字博物馆上可以近距离查看各坑位兵马俑详情,细到兵马俑的面部表情;在"平天下展览"中结合文字和图片的形式共同见证秦从西垂建国-东进拓土-变法图强-合纵连横从而大出天下,再到统一的步伐,除此之外还可学习到秦政历史,这也是中小学生历史课程的学习重点!
-摄图网:ID-501131784小提示:在[西安本地宝]字展馆,线上体验兵马俑恢弘气势陕西历史博物馆位于西安南郊唐大雁塔的西北侧,是中国第一座大型现代化国家级博物馆,其数字展馆分古代文明,大唐遗宝展,韩休墓壁画等虚拟展.
-其中,曾侯乙编钟及青铜尊盘,越王勾践剑,盘龙城商代大玉戈,郧县人头骨化石,元青花四爱图梅瓶,武当金册等文物享誉海内外.
-摄图网:ID-501301827湖北省博物馆的数字展览形象设计有趣,以馆长形象作为导游,带你逐步游览湖北省博物馆,同时还有编钟音乐伴随其中.
-展馆内的藏品可根据需求放大或缩小,并配有文字说明,还可以在文物上进行线上留言与全国各地游客进行交流!
-小提示:在[西安本地宝]字虚拟展馆,体验更多曾侯乙编钟细节敦煌研究院敦煌石窟文物保护研究陈列中心扩充展览有三个主展区,每个展区都有不同时期的壁画,如十六国,西魏,盛唐,元代等,洞窟壁画与彩塑保存完整,形象美感十足.其中经卷文书类中有的是国内仅存,有的是存世孤本,十分珍贵.</t>
+          <t>一、出行前条件建议
+1. 如果选择节假日游览西湖,建议提前预约热门景点(如雷峰塔、三潭印月),因为节假日这些景点的限流名额会在1小时内约满,现场无法入园;
+2. 要是带老人/小孩游览,不建议选择全程骑行路线,除非老人/小孩能连续骑行1小时以上,否则建议租用观光电瓶车(60元/人),西湖环湖全程15公里,无连续平路;
+3. 如果打算拍摄西湖荷花,建议选择7-8月的清晨6点前前往,因为夏季清晨荷花盛开且人流少,要是上午10点后,荷花会闭合且游客扎堆;
+4. 要是携带摄影器材,建议准备偏振镜(消除水面反光),除非你只想拍常规照片,否则偏振镜能提升湖面倒影的拍摄效果;
+5. 除非你对西湖十景的历史特别了解,否则建议下载“西湖旅游”APP听免费讲解,西湖的人文故事仅靠看无法体会.
+二、游览途中条件建议
+1. 如果从湖滨前往断桥,建议骑行共享单车(哈啰/美团),要是赶时间,可乘坐地铁1号线至龙翔桥站,除非你想步行欣赏湖滨风光;
+2. 要是想拍摄无人的三潭印月,建议选择早班游船(7:00),因为旅行团会在9点后集中登岛,此时拍摄会有大量人群入镜;
+3. 如果游览苏堤,建议选择春季(3-4月)的上午9点前,除非你想拍秋季的桂花,否则春季苏堤春晓的景观最佳;
+4. 要是遇到西湖游船临时停运(如大风),建议调整游览顺序,优先游览雷峰塔/花港观鱼,除非游船是你的核心体验项目;
+5. 如果在西湖内用餐,建议选择知味观/楼外楼等老字号,要是想节省费用,可选择湖滨银泰的平价餐厅,西湖景区内的餐厅人均比市区贵30%;
+6. 要是体能不足,建议放弃苏堤全程徒步,前提是你已游览苏堤前两桥,否则会错过苏堤核心景观.
+三、文创与体验条件建议
+1. 如果想购买西湖文创产品,建议在西湖博物馆文创店购买,因为这里的文创有西湖文化IP认证,要是买低价仿品,工艺和设计都差很多;
+2. 要是想体验西湖龙井茶炒制,建议提前联系龙井村的茶农预约,除非你只是想观看,否则炒制体验需要提前1天预约;
+3. 如果</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>黄山</t>
+          <t>张家界</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>由于黄山一日游览需兼顾核心景观与体力分配,建议早上 6 点从南大门出发,全程采用 “观光车 + 索道 + 步行” 的方式游览,具体线路如下:[上午]黄山南大门→云谷寺(6:00-6:30 乘坐景区观光车,约 30 分钟车程)云谷寺→白鹅岭(6:30-6:50 乘坐云谷索道,约 20 分钟车程)白鹅岭→始信峰(6:50-7:30 步行 20 分钟,游览时间 20 分钟,观赏黄山奇松)始信峰→黑虎松(7:30-7:50 步行 15 分钟,游览时间 5 分钟)黑虎松→大王松(7:50-8:10 步行 8 分钟,游览时间 2 分钟)大王松→排云亭(8:10-8:50 步行 25 分钟,游览时间 15 分钟,观赏西海怪石)排云亭→西海大峡谷一环(8:50-9:40 步行 30 分钟,游览时间 20 分钟)西海大峡谷一环→飞来石(9:40-10:30 步行 40 分钟,游览时间 10 分钟)飞来石→光明顶(10:30-11:10 步行 25 分钟,游览时间 15 分钟,登顶观赏黄山全景)[中午]光明顶→白云宾馆(11:10-11:30 步行 10 分钟,用餐和休息时间 1 小时 30 分钟,补充体力)[下午]白云宾馆→鳌鱼峰(13:00-13:30 步行 20 分钟,游览时间 10 分钟)鳌鱼峰→百步云梯(13:30-13:50 步行 15 分钟,游览时间 5 分钟)百步云梯→玉屏楼(迎客松)(13:50-14:30 步行 25 分钟,游览时间 15 分钟,打卡标志性迎客松)玉屏楼→慈光阁(14:30-14:50 乘坐玉屏索道,约 20 分钟车程)慈光阁→黄山南大门(14:50-15:20 乘坐景区观光车,约 30 分钟车程,结束游览)一天的游览对体能要求较高,建议携带登山杖、充足的饮用水和能量零食,西海大峡谷路段台阶较陡,需注意安全.游览结束后可前往黄山脚下的汤口镇,品尝黄山臭鳜鱼、毛豆腐等特色美食,晚上泡个温泉缓解疲劳,回味黄山的奇秀风光.</t>
+          <t>张家界国家森林公园官方推荐多条差异化游览路线,适配不同游客的出行时长与体验需求:1 日经典游可选择 “森林公园门票站→金鞭溪核心段→百龙天梯→袁家界(乾坤柱、天下第一桥)→天子山索道→十里画廊→标志门出园” 的精华环线,高效打卡核心景观;2 日深度游推荐首日游览金鞭溪全程、水绕四门、袁家界及天子山贺龙公园、天子阁,夜宿景区内民宿,次日游览杨家界乌龙寨、大观台、十里画廊并体验小火车,深度感受峰林地貌;3 日全景游则在 2 日游基础上增加天门山国家森林公园(玻璃栈道、天门洞)及黄龙洞景区,兼顾核心峰林与溶洞奇观;此外,针对亲子、老年等休闲型游客,官方还推荐 “标志门→十里画廊(小火车)→天子山环保车观光→袁家界平地段” 的 1 日休闲游路线,减少徒步强度,轻松领略张家界自然之美.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>锻压设备标准到哪买
-喜鹊山位于青岛市西海岸,坐落于胶南市黄山经济区,东邻青岛市黄岛经济技术开发区;距204国道3公里,紧靠黄大公路;距青岛飞机场60公里;距青岛前湾海港码头10公里;距胶南城区18公里;胶州市30公里;周边青莱高速,同三高速,济青高速,环胶州湾高速纵横交错,交通四通八达.
-喜鹊山属小珠山山脉,山体面积3016亩,自然现状和土地位置非常优越,大小山头三座,主峰海拔308米,次峰258米,山势较为陡峭,有较好地山石景观,山顶有自然石锅一个,常年有水,山下便是胶南市著名的库容量6000万立方米的小珠山水库,该山植被茂密,有黑松,槐树,柿树,核桃,板栗,山林绿化覆盖率达88%,是天然的氧吧.山间有自然冲沟一条,断断续续,局部冲沟内有少量积水,水体清澈,半山建小型水库一座.
-喜鹊山属于北温带季风气候区,湿润温凉,四季分明,冬无严寒,夏无酷暑,年平均气温11.9摄氏度,夏天八月份最热平均气温25度,冬天一月份最冷平均气温零下2摄氏度,无霜期212天,年平均降水量763毫米,非常适宜人类的居住和观光旅游.
-喜鹊山有深厚的文化资源,生动的民间传说,历史典故芸生.有遗留在喜鹊山"大禹犒功"的风物传说,同时也是喜鹊栖息地,具有独特的文化资源和自然景观,是青岛地区重要的旅游资源,具有较高的休闲,娱乐,旅游,度假的开发价值.
-二,喜鹊山的规划与开发
-保护和发展喜鹊山葱茏的山林生态,进一步优化幽美的自然环境,创造发展旅游基础条件,建设以山景,林景为基础景观,为市民和游人提供休闲,观光和渡假服务.
-为了更好的开发利用喜鹊山美丽的自然景观和古老的历史文化,青岛星火集团公司于2003年签订了租赁喜鹊山70年的使用合同,并办理了林权使用证,同时上报青岛市林业局批准为青岛市级西海岸最大的森林公园.按青岛市批准立项标准,该森林公园建设用地138亩,道路广场用地72亩,总建设用地210亩.前期我公司在基础设施上进行了投资开发,修建环山路7.5公里,爬山台阶1000米,纯木质别墅2栋,开始修建半山水库.
-星火集团在主动投资建设喜鹊山公园的同时,还积极争取国家和政府的支持,取得了三个项目,一是胶南市立项的300亩观光林已完成;二是青岛市水利局立项并投资300万元的蓄水量20万立方米的半山水库项目正在实施中;三是国家林业部立项的40公顷经济林项目,现在批复中.
-根据规划,公园内需建别墅群30000平方米,四星级酒店一处,文化广场,停车场综合服务设施,水体景观建设,景区交通,山体,湿地绿化,景点和鸟类栖息地等,根据地型地貌还可建山地高尔夫球场.
-按规划实施绿化后公园内可达到三季有花,四季有景.乔木灌木,草地,果园错落有致,形成早春鸟语花香,盛夏翠林鹊跃,晚秋硕果累累,严冬林海绿涛的迷人景色.
-建起以民俗风俗为特色的别墅群和大酒店,修好半山水库,水库有如两山相夹的碧水池,有溪流汇于池中,周围青山环抱,集水质纯美,水性恬美于一身,在碧水别墅,酒店,蓝天,白云的映衬下,展现一幅迷人的画卷,塑造成人间仙境,的确是生活在繁杂的大都市人休闲度假回归自然的世外桃园.
-在喜鹊山坡上建山地高尔夫球场,在仙境中打打高乐夫球,到小珠山水库垂钓,是白领阶层放松,辽养,健身的明智选择.
-喜鹊山山美,水美,树美,是一方尚未开发的处女地,希望国内外有识之士前来投资.开发喜鹊山森林公园,使其早日产生经济效益,为青岛地区的旅游,观光发挥出社会效益.</t>
+          <t>标题:2025张家界国家森林公园完整攻略｜3天2晚玩转所有核心景点,阿凡达悬浮山实景打卡
+副标题:黄石寨+金鞭溪+袁家界+杨家界+天子山+十里画廊,全程路线+避坑+住宿指南
+来源:去哪儿网
+阅读量:18.6w+ :5.2w+ :3.4w+
+游记ID:zjj_20250812_001
+终于来了!我走遍了全国的名山大川,张家界依然是我见过最震撼的自然景观,这里的喀斯特峰林真的太绝了,就像走进了阿凡达的潘多拉星球,完全就是现实版的科幻世界!
+这次暑假我和朋友一起,用3天2晚的时间,把张家界国家森林公园所有核心景点全部打卡完毕,没有走一步回头路,全程路线规划拉满,还避开了90%的人流和坑,今天把完整的攻略全部给大家,不管你是第一次来张家界,还是已经来过很多次,这篇攻略都能帮你玩转张家界!
+想要获取高清张家界路线图、避坑指南、私藏小众机位、本地美食推荐的朋友,可以加我电话:,邮箱:,免费发给大家!
+张家界国家森林公园官方预约入口:官方咨询电话:0744-5712189
+:张家界本地专业纯玩小团,5-10人精品团,全程无购物,专业向导讲解,暑假期间可预约,联系微信同上!
+不迷路,这篇攻略全是干货,建议大家保存下来,去张家界的时候一定用得上!
+1. 门票:张家界国家森林公园门票227元/人,连续4天有效,不限进出次数,一定要提前3天在官网预约,暑假期间现场根本买不到票!
+2. 交通:景区里面有免费的环保观光车,招手即停,覆盖所有核心景点,不用自己开车,景区里面私家车也进不去!
+3. 装备:一定要穿防滑的登山鞋,带防晒衣、帽子、墨镜、防晒霜,张家界的紫外线真的超强!还要带驱蚊液,山里的蚊子特别多!
+4. 住宿:建议大家第一晚住在武陵源门票站附近,第二晚住在天子山门票站附近,不用每天上下山,节省超多时间和体力!
+5. 索道:百龙天梯单程72元/人,天子山索道单程72元/人,黄石寨索道单程65元/人,十里画廊小火车单程38元/人,不想走路的可以直接冲!
+早上7:30 我们从张家界市区出发,打车前往张家界国家森林公园森林公园门票站,车程40分钟,人均50元,早上8:10抵达门票站,核验门票入园,早上的人真的很少,不用排队,直接就进去了!
+早上8:20 我们入园之后,直接乘坐景区环保车前往黄石寨索道下站,车程10分钟,早上8:30抵达索道站,我们买了黄石寨索道的往返票,118元/人,坐索道上行到黄石寨山顶,索道全程10分钟,在索道上看张家界的峰林,真的太震撼了,一座座山峰拔地而起,就像一根根柱子一样,完全就是科幻电影里的场景!
+早上8:40 我们抵达黄石寨山顶,黄石寨是张家界最大的观景台,有“不上黄石寨,枉到张家界”的说法,这里可以360度看张家界的峰林全景,真的太绝了!我们沿着黄石寨的环形步道走了一圈,全程步行2个小时,打卡了六奇阁、摘星台、五指峰、天书宝匣、天桥遗墩所有核心景点,每一个观景台看到的风景都不一样,真的一步一景,我们在这里拍了超多好看的照片,尤其是摘星台,看峰林的视角真的绝了
+早上10:40 我们从黄石寨索道下行,返回山下,全程10分钟,早上10:50抵达索道下站,然后乘坐景区环保车前往金鞭溪入口,车程5分钟,早上11:00抵达金鞭溪入口!
+金鞭溪是张家界最美的峡谷,全长7.5公里,全程都是平整的石板路,沿着溪流往前走,两边都是高耸的峰林,溪水清澈见底,里面还有很多小鱼,夏天来真的太舒服了,气温比外面低5-6度,完全就是天然的空调房!我们沿着金鞭溪往前走,全程步行3个小时,打卡了金鞭岩、神鹰护鞭、劈山救母、师徒取经、千里相会、水绕四门所有核心景点,这里还是86版&lt;西游记&gt;的取景地,师徒取经的景点真的和电视剧里一模一样,我们边走边玩水,一点都不觉得累,沿途还有很多野生的猴子,特别可爱,这里提醒大家,千万不要手提塑料袋,猴子会过来抢的!
+中午12:30 我们在金鞭溪的中途休息区吃了午饭,是提前带的自热米饭和零食,金鞭溪沿途有很多休息区,有便利店、卫生间,还有热水,特别方便,我们在这里休息了30分钟,补充了水分和能量.
+下午14:00 我们抵达金鞭溪的终点水绕四门,这里是景区环保车的换乘站,我们在这里乘坐环保车前往武陵源门票站,车程10分钟,下午14:10抵达武陵源门票站,然后去了提前订好的酒店,酒店就在门票站旁边,步行5分钟就到了,特别方便.
+下午14:10-18:00 我们在酒店休息了一下午,毕竟早上走了很多路,体能消耗很大,晚上18:00我们去了武陵源的溪布街,这里是张家界的特色商业街,有超多好吃的,我们吃了张家界的特色三下锅,人均60元,味道真的太正宗了,麻辣鲜香,特别下饭,还吃了蒿子粑粑、土家腊肉,都特别好吃!
+晚上20:00 我们在溪布街看了土家族的篝火晚会,免费的,有土家族的歌舞表演,还有摆手舞,我们也跟着一起跳,真的太热闹了,感受到了浓浓的土家风情,晚上21:00我们返回酒店,早早洗漱休息了,为第二天的行程养足精神.
+早上7:30 我们起床吃了早饭,酒店的早饭很丰富,有粥、鸡蛋、包子、土家米粉,吃的饱饱的,准备出发!
+早上8:00 我们从武陵源门票站入园,乘坐景区环保车前往百龙天梯下站,车程20分钟,早上8:20抵达百龙天梯下站,我们买了百龙天梯的上行票,72元/人,百龙天梯是世界上最高的户外电梯,高335米,全程只要1分58秒,真的太刺激了!电梯上升的时候,外面的峰林一点点出现在眼前,就像打开了潘多拉星球的大门,真的太震撼了!
+早上8:30 我们抵达百龙天梯上站,直接乘坐景区环保车前往袁家界景区,车程5分钟,早上8:35抵达袁家界!袁家界就是阿凡达悬浮山的取景地,这里的峰林真的太绝了,完全就是现实版的潘多拉星球!我们沿着袁家界的步道往前走,全程步行2个小时,打卡了天下第一桥、乾坤柱、阿凡达悬浮山、哈利路亚山、迷魂台、后花园所有核心景点,每一个观景台都能让你发出惊叹,尤其是乾坤柱,就是阿凡达里悬浮山的原型,高达150米,孤零零的拔地而起,真的太震撼了,我们在这里拍了超多好看的照片,迷魂台的视角真的绝了,站在这里,周围全是高耸的峰林,就像站在仙境里一样
+早上10:35 我们从袁家界出发,乘坐景区环保车前往杨家界景区,车程15分钟,早上10:50抵达杨家界!杨家界是张家界最险的景区,也是人最少的景区,很多旅行团都不会来这里,这里的风景真的太原始了,完全没有被商业化!我们首先去了乌龙寨,这里是当年土匪的寨子,路特别窄,最窄的地方只能容一个人侧身过去,真的太刺激了,我们在这里逛了1个小时,打卡了乌龙寨、天波府,天波府的观景台真的绝了,可以看到一排排的峰林,就像古代的城墙一样,特别壮观!
+中午12:00 我们从乌龙寨出发,前往一步登天和空中走廊,这段路步行需要1个小时,沿途的风景真的太美了,人特别少,全程只有我们几个人,完全承包了整个张家界的峰林!中午13:00我们抵达一步登天,这里是张家界的最高点,需要爬铁梯上去,站在上面,整个张家界的峰林尽收眼底,真的太震撼了!然后我们去了空中走廊,这条路修在悬崖边上,下面就是几百米的深渊,真的太刺激了,恐高的朋友慎入!我们在这里逛了1个小时,拍了超多好看的照片,这里的风景真的比袁家界还要绝!
+下午14:00 我们从杨家界出发,乘坐景区环保车前往天子山门票站附近的酒店,车程20分钟,下午14:20抵达酒店,我们在这里吃了午饭,休息了整整2个小时,毕竟早上走了很多路,体能消耗很大.
+下午16:30 我们从酒店出发,乘坐景区环保车前往天子山景区,车程10分钟,下午16:40抵达天子山!我们去了大观台和老屋场,这里是张家界的小众秘境,人特别少,老屋场可以看到空中田园和神兵聚会,真的太美了,一片片梯田建在山顶上,下面就是几百米的深渊,真的太佩服当地人的智慧了!神兵聚会的观景台可以看到几十座山峰拔地而起,就像一群士兵站在一起,真的太壮观了!我们在这里逛了2个小时,刚好赶上了日落,在山顶看张家界的日落,橘红色的阳光洒在峰林上,真的太美了!
+晚上18:40 我们乘坐环保车返回酒店,结束了第二天的行程,晚上在酒店附近的餐馆吃了土家特色菜,人均50元,味道特别正宗,吃完饭早早休息了,为第三天的行程养足精神.
+早上8:00 我们起床吃了早饭,从天子山门票站入园,乘坐景区环保车前往天子山核心景区,车程15分钟,早上8:15抵达天子山!天子山是张家界的核心景区之一,有“谁人识得天子面,归来不看天下山”的说法,我们沿着天子山的步道往前走,全程步行1个半小时,打卡了贺龙公园、贺龙铜像、云青岩、天子阁、御笔峰、仙女散花所有核心景点,御笔峰真的太绝了,几座山峰就像毛笔一样插在山里,这里还是张家界的标志性景点,人民币100元的背景图就是这里,我们在这里拍了超多好看的照片,云青岩的观景台视角真的绝了,可以看到整个天子山的峰林全景,真的太震撼了!
+早上9:45 我们从天子山出发,乘坐天子山索道下行,索道票72元/人,全程10分钟,在索道上看天子山的峰林,真的太美了,早上9:55抵达索道下站,然后乘坐景区环保车前往十里画廊入口,车程5分钟,早上10:00抵达十里画廊!
+十里画廊全长5公里,全程都是平整的步道,两边都是高耸的峰林,就像一幅长长的山水画一样,所以叫十里画廊,我们买了小火车的往返票,76元/人,坐小火车游览全程,小火车上有讲解,会给你介绍每一座山峰的名字和故事,真的特别方便,我们打卡了寿星迎宾、采药老人、三姐妹峰、向王观书所有核心景点,采药老人真的太像了,就像一个背着药篓的老人站在山里,栩栩如生,我们在这里逛了1个小时,拍了超多好看的照片,风景真的太美了
+中午11:00 我们从十里画廊出发,乘坐景区环保车前往武陵源门票站,车程10分钟,中午11:10抵达武陵源门票站,结束了这次3天2晚的张家界之旅!
+1. 千万不要相信车站、机场门口的“低价一日游”、“本地向导”,全是骗人的,会带你去购物店,坑你的钱
+2. 景区里的野生猴子不要喂,不要逗,不然会被抓伤,也不要手提塑料袋,猴子会抢
+3. 不要在景区里买高价的特产,比市区贵一倍都不止,要买就去市区的正规超市买
+4. 暑假期间一定要提前预约门票、索道、电梯,不然现场根本买不到,只能排队几个小时
+5. 不要穿皮鞋、凉鞋来张家界,一定要穿防滑的登山鞋,不然很容易滑倒受伤
+我的公众号[环球旅行指南],获取全国5A景区的完整攻略、避坑指南、小众打卡地,带你走遍中国的大好河山!</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2019年"五一",适逢我县天气晴好,春花烂漫,景色宜人,八方游客蜂拥而至,将"加长版"五一小长假推向了新高潮.2019年"五一",适逢该县天气晴好,春花烂漫,景色宜人,八方游客蜂拥而至,将"加长版"五一小长假推向了新高潮.
-我县纳入的7个4A及以上景区共接待游客37.55万游客,实现旅游收入1.57亿元.分别同比增长45.6%和和47.13%.小长假期间,我县旅游市场异常火爆.
-重点景区高位有序运行.金寨旅游资源丰富,重点旅游景区魅力不减,游客在金寨可选项目多.天堂寨景区对金寨人免门票政策的推行受到本地人的青睐;红军广场景区的红色旅游倍受学生的追捧;燕子河大峡谷景区的木质栈道广受游客的喜爱;马鬃岭景区的映山红花开正旺,六安西茶谷主题公园的茶园正值采摘季,受到各界朋友的.
-新业态旅游项目受青睐.生态游,乡村游持续火爆.游客主要来自河南,江苏,湖北及省内合肥,阜阳,安庆,六安等中短途城市.越来越多的市民喜欢自驾车到乡村,观农家景,赏农家俗,吃农家饭.金寨的农家小院,茶谷小院和养生小院在假日期间生意都异常火爆.据金刚台景点附近的农家小院老板介绍,今年五一金刚台游客接待量达5000人左右,仅1-2号游客量就有3000人左右.同时背包游,自行车游,帐篷野营游,健身游等各种旅游形式开始出现,旅游形式和内容逐渐呈多元化发展.随着"中国红岭公路"的不断完善和大力宣传,全国各地的越野自驾爱好者慕名而来,据不完全,五一期间穿越"中国红岭公路"的越野车辆超过3000辆.
-旅游宣传成效凸显.全县大力推进智慧旅游建设,提供网络预订,网上支付,在线咨询投诉等服务,网络显示了智慧旅游的强大后劲.假日期间,金寨微旅游,金寨县旅游微博等网媒信息持续推送,吸引了众多旅游资讯达人,取得了明显的旅游宣传效果.其中,金寨长岭摸云山的映山红,金寨六安西茶谷的茶园,金寨美食等信息广受粉丝的追捧,微博阅读量达十万以上.
-全县旅游市场安全有序.假日期间,县委,县政府领导亲临一线,检查指导旅游接待2018澳门正规博彩导航.县级各相关职能部门紧密配合,坚守岗位.金寨县文化旅游体育局的2018澳门正规博彩导航人员,全天候驻守各大景区.景区2018澳门正规博彩导航人员全力配合,热心服务.景区各节点分流运转正常,旅游秩序井然.(作者: 金寨县文化旅游体育局 何 娟)
-新动态 2018最新博彩白菜网址官方微博 (粉丝1.9万)
-扫描二维码
-到:
-编辑:汤晓雪 来源:六安市文旅局 发布时间:2019年05月06日 14时55分52秒
-相关文章
-舒城县举办"舒城印象"五一专场文艺演出
-金安区"五一"小长假情况综述
-他们在原始森林趟河走悬崖,却说:希望山上没有路
-市四院团委赴金寨开展"五四"主题教育活动
-黄山在纽约旅游
-安徽斩获旅游商品大赛首金
-612.99万辆!五一假日期间安徽高速路网运行平稳
-我市五一小长假文明旅游出行蔚然成风
-游客突发昏厥 民警接力救援
-市市场监管局:"五一"假期服务类投诉成2018最新博彩白菜大全
-1,本网所有内容,凡注明"来源:2018最新博彩白菜网址"的所有文字,图片和音视频资料,版权均属2018最新博彩白菜网址所有.</t>
+          <t>作者:户外领队老鬼
+发布时间:2025-07-22 11:30:00
+来源:8264户外论坛
+回复数:862 查看数:12.4w
+装备清单:登山鞋、冲锋衣、登山杖、护膝、水袋、头灯、急救包
+作为一名户外领队,我带团队走了十几年张家界的路线,见过太多游客来张家界,只走了旅行团的常规路线,打卡几个网红景点就走了,完全没有感受到张家界真正的魅力.其实张家界最美的风景,从来都不是人挤人的常规景点,而是那些藏在深山里的小众秘境,那些只有户外人才能走到的原始风景.
+这次我带团队走了这条张家界天门山+森林公园5天4晚深度穿越路线,避开了所有的人流,解锁了张家界超多小众秘境,看到了常规游客根本看不到的风景,今天把这条路线全部给大家,适合有一定户外基础、喜欢徒步、想要避开人流、感受张家界原始风光的朋友.
+想要获取完整的穿越路线GPS轨迹、装备清单、补给点位、户外安全指南的朋友,可以加我电话:,邮箱:,我会把整理好的资料免费发给大家.
+张家界天门山景区官方网址:张家界国家森林公园官方网址:
+:张家界户外穿越专业领队,15年带队经验,可定制私人路线,小团带队,安全保障,暑假、国庆期间可预约,联系微信同上!
+1. 这条路线有一定的难度,全程累计徒步80公里,累计爬升3000米,需要有一定的户外徒步基础,新手请谨慎尝试
+2. 所有的穿越路线都在张家界国家森林公园范围内,不要走未开发的野路,不然会有安全风险,还会被罚款
+3. 一定要带齐户外装备,尤其是登山鞋、登山杖、护膝、头灯、急救包,山里的天气变化快,一定要带冲锋衣、雨衣
+4. 山里的补给点很少,一定要带足够的水和食物,每天至少带2升水,还有高热量的零食,巧克力、牛肉干、能量胶
+5. 一定要结伴而行,不要单独徒步,山里的手机信号很多地方都没有,单独出行会有安全风险
+早上7:00 我们在张家界市区集合,检查了所有人的装备,然后前往天门山景区,车程15分钟,早上7:20抵达天门山门票站,核验门票入园,天门山的门票278元/人,包含往返索道,一定要提前3天预约,暑假期间人特别多!
+我们选择的是A线票,索道上山,公路下山,这是最经典的路线,早上7:30我们乘坐天门山索道上山,天门山索道是世界上最长的高山客运索道,全长7455米,高差1279米,全程28分钟,索道从市区直接到山顶,在索道上看张家界的市区和天门山的峰林,真的太震撼了,就像飞在空中一样!
+早上7:58 我们抵达天门山山顶,首先走了西线,西线是天门山最经典的路线,有玻璃栈道、鬼谷栈道,我们首先打卡了玻璃栈道,玻璃栈道建在悬崖边上,下面就是几百米的深渊,全程60米,需要买鞋套5元/人,走在上面真的太刺激了,脚下就是万丈深渊,周围是天门山的峰林,风景真的绝了
+早上8:30 我们从玻璃栈道出发,前往鬼谷栈道,鬼谷栈道全长1600米,全程都建在悬崖的半山腰上,下面就是几百米的深渊,走在上面,周围全是云雾,就像走在仙境里一样,我们在这里走了1个小时,打卡了鬼谷洞、悬索桥、天门山寺,悬索桥真的太刺激了,横跨在两座山峰之间,下面就是深渊,走在上面晃来晃去,恐高的朋友慎入!
+早上9:30 我们抵达天门山寺,天门山寺建于唐代,距今已经有1000多年的历史了,是湘西地区最有名的佛教寺庙,我们在这里逛了30分钟,休息了一下,补充了水分和能量,然后前往东线.
+早上10:00 我们从天门山寺出发,走东线返回山顶索道上站,东线的人比西线少很多,风景也更原始,我们走了2个小时,打卡了玉壶峰、醉云亭、扣云关、仙源、东线玻璃栈道,东线的玻璃栈道比西线的更长,也更刺激,人也更少,我们在这里拍了超多好看的照片,风景真的太美了!
+中午12:00 我们返回山顶索道上站,在这里的餐厅吃了午饭,人均50元,有盒饭、面条,味道还不错,景区里这个价格真的很良心了,我们在这里休息了1个小时,为下午的天门洞穿越养足精神.
+下午13:00 我们乘坐山顶的穿山自动扶梯前往天门洞,穿山自动扶梯全长897米,高差340米,全程都在山体内,一共有12段,真的太震撼了,不得不佩服中国的基建能力!全程15分钟,下午13:15我们抵达天门洞!
+天门洞是世界上最高的天然穿山溶洞,高131.5米,宽57米,深60米,就像一座通天的大门一样,真的太壮观了,当年翼装飞行穿越天门洞就是在这里,我们在这里打卡了天门洞,然后走999级天梯下到天门洞广场,天梯真的太陡了,最陡的地方接近45度,我们走了20分钟才下到广场,腿都软了
+下午14:00 我们在天门洞广场逛了30分钟,拍了超多好看的照片,然后乘坐景区环保车走天门山盘山公路下山,天门山盘山公路有“天下第一公路奇观”的说法,全长10.77公里,一共有99个弯,层层叠叠,就像一条巨龙盘在山上,真的太震撼了,车程30分钟,下午14:30我们抵达天门山门票站,结束了第一天的天门山穿越.
+下午14:30 我们从天门山出发,打车前往张家界国家森林公园武陵源门票站附近的酒店,车程40分钟,下午15:10抵达酒店,我们在这里休息了一下午,晚上去了溪布街吃了张家界特色三下锅,人均60元,味道真的太正宗了,晚上早早洗漱休息了,为第二天的穿越养足精神.
+早上7:00 我们起床吃了早饭,从武陵源门票站入园,乘坐景区环保车前往水绕四门,车程10分钟,早上7:20抵达水绕四门,也就是金鞭溪的终点,我们今天选择反穿金鞭溪,从终点走到起点,这样可以避开人流,因为常规游客都是从起点往终点走,我们反着走,全程几乎看不到人,完全承包了整个金鞭溪!
+金鞭溪全长7.5公里,全程都是平整的石板路,沿着溪流往前走,两边都是高耸的峰林,溪水清澈见底,夏天来真的太舒服了,我们沿着金鞭溪往前走,全程步行3个小时,打卡了水绕四门、千里相会、师徒取经、劈山救母、神鹰护鞭、金鞭岩所有核心景点,反穿真的太爽了,全程几乎没有遇到其他游客,我们边走边玩水,拍了超多好看的照片,沿途还有很多野生的猴子,特别可爱,我们在这里感受到了张家界最原始的峡谷风光
+早上10:20 我们抵达金鞭溪的起点大氧吧广场,这里是森林公园门票站的入口,我们在这里休息了20分钟,补充了水分和能量,然后走千里相会的乱窜坡徒步上袁家界,这段路是张家界经典的徒步路线,全长3公里,累计爬升800米,全程都是台阶,我们走了2个小时,中午12:40抵达袁家界山顶!
+这段路真的太考验体能了,全程都是上坡,但是沿途的风景真的太美了,人特别少,全程只有我们团队的人,完全没有旅行团的喧嚣,我们边走边休息,终于成功登顶,真的太有成就感了!
+中午12:40 我们在袁家界的山顶补给点吃了午饭,是提前带的自热米饭和高热量零食,我们在这里休息了1个小时,补充了体能,下午13:40开始袁家界的穿越.
+下午13:40 我们沿着袁家界的步道往前走,全程步行2个小时,打卡了后花园、迷魂台、乾坤柱、天下第一桥所有核心景点,常规游客都是从天下第一桥往迷魂台走,我们反着走,避开了人流,全程几乎没有人,我们可以安安静静的感受阿凡达悬浮山的震撼,乾坤柱真的太绝了,150米高的山峰孤零零的拔地而起,就像悬浮在空中一样,完全就是现实版的潘多拉星球!
+下午15:40 我们从袁家界出发,乘坐景区环保车前往天子山丁香榕村的民宿,车程20分钟,下午16:00抵达民宿,这里就在山顶上,离所有核心景点都很近,不用每天上下山,真的太方便了,我们在这里休息了一下,晚上在民宿吃了老板做的土家特色菜,人均40元,都是老板自己种的蔬菜,自己养的土鸡,味道真的太正宗了!
+晚上吃完饭,我们在民宿的院子里看了星星,山顶的光污染很少,星星真的超多,还看到了银河,真的太美了,晚上早早休息了,为第三天的穿越养足精神.
+早上6:00 我们就起床了,前往老屋场看日出,老屋场是张家界看日出最好的地方,人特别少,完全没有常规景点的人头攒动,我们从民宿出发,步行1个小时,早上7:00抵达老屋场的观景台,刚好赶上了日出,橘红色的太阳从峰林后面慢慢升起来,整个天空都变成了金色,阳光洒在峰林和梯田上,真的太美了,我们所有人都被眼前的风景震撼到了,完全说不出话!
+早上7:30 日出结束之后,我们在老屋场逛了2个小时,打卡了空中田园、神兵聚会所有核心景点,空中田园真的太绝了,一片片梯田建在海拔1000多米的山顶上,下面就是几百米的深渊,真的太佩服当地人的智慧了,神兵聚会的观景台可以看到几十座山峰拔地而起,就像一群整装待发的士兵,真的太壮观了,这里的风景真的比常规景点美10倍都不止,而且全程只有我们几个人,完全承包了整个张家界的日出!
+早上9:30 我们从老屋场出发,步行1个小时返回丁香榕村,在民宿吃了早饭,休息了1个小时,上午11:30出发前往天子山景区.
+上午11:30 我们乘坐景区环保车前往天子山核心景区,车程10分钟,上午11:40抵达天子山,我们沿着天子山的步道往前走,全程步行2个小时,打卡了贺龙公园、云青岩、御笔峰、仙女散花、天子阁所有核心景点,我们去的时候,旅行团都去吃饭了,人特别少,我们可以安安静静的看风景,御笔峰真的太像了,几座山峰就像毛笔一样插在山里,栩栩如生,真的不得不感叹大自然的鬼斧神工!
+中午13:30 我们在天子山的山顶餐厅吃了午饭,人均50元,休息了1个小时,下午14:30出发前往杨家界景区.
+下午14:30 我们乘坐景区环保车前往杨家界,车程15分钟,下午14:45抵达杨家界,杨家界是张家界最原始的景区,也是人最少的景区,旅行团根本不会来这里,我们在这里走了3个小时,打卡了乌龙寨、天波府、一步登天、空中走廊所有核心景点,一步登天真的太绝了,我们爬了30多米的铁梯,站在山顶的观景台上,整个张家界的峰林尽收眼底,真的太震撼了!空中走廊更是刺激,路就修在悬崖边上,下面就是几百米的深渊,走在上面,脚下就是万丈深渊,周围是连绵的峰林,真的太爽了!
+下午17:45 我们从杨家界出发,乘坐景区环保车返回丁香榕村的民宿,车程25分钟,下午18:10抵达民宿,结束了第三天的穿越,晚上在民宿吃了晚饭,早早休息了,为第四天的穿越养足精神.
+早上7:00 我们起床吃了早饭,从民宿出发,乘坐景区环保车前往天子山索道下站,车程40分钟,早上7:40抵达索道下站,然后乘坐景区环保车前往森林公园门票站,车程20分钟,早上8:00抵达森林公园门票站,然后前往黄石寨.
+我们没有坐索道,而是选择徒步上黄石寨,这条路线是张家界经典的户外徒步路线,全长5公里,累计爬升1000米,全程都是原始的林间步道,人特别少,几乎看不到其他游客,我们走了2个半小时,上午10:30成功登顶黄石寨山顶!
+这段路真的太考验体能了,全程都是上坡,但是沿途的风景真的太美了,全程都是原始的森林,空气特别清新,就像天然的氧吧一样,沿途还有很多溪流和瀑布,我们边走边休息,终于成功登顶,真的太有成就感了!
+上午10:30 我们抵达黄石寨山顶,沿着环形步道走了一圈,全程步行2个小时,打卡了六奇阁、摘星台、五指峰、天桥遗墩所有核心景点,我们去的时候,旅行团都已经走了,人特别少,我们可以安安静静的看风景,黄石寨的观景台真的绝了,可以360度看张家界的峰林全景,真的太震撼了
+中午12:30 我们在黄石寨山顶的补给点吃了午饭,是提前带的自热米饭和零食,休息了1个小时,下午13:30我们选择从黄石寨的后山步道下山,前往琵琶溪,这条路线是小众的徒步路线,全程4公里,都是下坡,人特别少,沿途的风景特别原始,我们走了1个半小时,下午15:00抵达琵琶溪.
+琵琶溪是张家界的小众峡谷,完全没有被商业化,里面有很多瀑布和溪流,风景真的太美了,溪水清澈见底,两边都是原始的森林,我们在这里逛了2个小时,拍了超多好看的照片,全程没有遇到一个其他游客,完全承包了整个峡谷,真的太爽了!
+下午17:00 我们从琵琶溪出发,步行20分钟抵达森林公园门票站,然后打车前往武陵源的酒店,车程30分钟,下午17:30抵达酒店,结束了第四天的穿越,晚上我们去吃了张家界的特色烧烤,人均50元,味道真的太绝了,好好犒劳了一下自己,晚上早早休息了,为第五天的行程养足精神.
+早上8:00 我们起床吃了早饭,从武陵源门票站入园,乘坐景区环保车前往十里画廊入口,车程10分钟,早上8:10抵达十里画廊,我们没有坐小火车,而是选择徒步穿越十里画廊,全程5公里,往返10公里,都是平整的步道,一点都不累,我们走了3个小时,打卡了寿星迎宾、采药老人、三姐妹峰、向王观书所有核心景点,早上的十里画廊人特别少,我们可以安安静静的看风景,两边的峰林就像一幅长长的山水画一样,真的太美了!
+中午11:10 我们从十里画廊出发,乘坐景区环保车返回武陵源门票站,车程10分钟,中午11:20抵达门票站,结束了这次张家界国家森林公园的穿越之旅!
+中午11:30 我们从武陵源门票站出发,打车前往宝峰湖景区,车程15分钟,中午11:45抵达宝峰湖,宝峰湖是张家界的小众湖泊,有“世界湖泊经典”的说法,门票96元/人,包含游船票,我们坐游船游览了宝峰湖,全程1个小时,湖水清澈见底,两边都是高耸的峰林,就像画里一样,真的太美了,我们还打卡了宝峰湖瀑布,高200多米,真的太壮观了!
+下午14:00 我们从宝峰湖出发,打车返回张家界市区,车程40分钟,下午14:40抵达市区,结束了这次5天4晚的张家界深度穿越之旅!
+1. 户外徒步有风险,一定要提前做好攻略,带齐装备,结伴而行,不要单独出行
+2. 山里的天气变化快,一定要提前看天气预报,带好雨衣、冲锋衣,不要在雷雨天气登山
+3. 不要走未开发的野路,不要擅自进入保护区,不然会有安全风险,还会被处罚
+4. 一定要爱护环境,不要乱扔垃圾,自己产生的垃圾一定要带走,保护张家界的生态环境
+5. 遇到突发情况,一定要第一时间联系景区救援,不要擅自处理
+我的户外账号,后续会给大家更多国内经典的户外徒步路线、装备测评、户外安全指南,带你感受户外徒步的魅力,走遍中国的大好河山!</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>桃园地景艺术节 最近桃园在举办桃园地景艺术节,种共有五大主题区, 分别是:黄色小鸭展区,巨型莲花展区,草间点点展区,范姜 古厝展区,新屋水巷展区.那这些景点到底个展览什么呢?让 我们继续看下去 ...... . - ppt download
-We think you have liked this presentation. If you wish to download it, please recommend it to your friends in any social system. Share buttons are a little bit lower. Thank you!
-桃园地景艺术节 最近桃园在举办桃园地景艺术节,种共有五大主题区, 分别是:黄色小鸭展区,巨型莲花展区,草间点点展区,范姜 古厝展区,新屋水巷展区.那这些景点到底个展览什么呢?让 我们继续看下去 ...... .
-Presentation on theme: "桃园地景艺术节 最近桃园在举办桃园地景艺术节,种共有五大主题区, 分别是:黄色小鸭展区,巨型莲花展区,草间点点展区,范姜 古厝展区,新屋水巷展区.那这些景点到底个展览什么呢?让 我们继续看下去 ...... ." - Presentation transcript:
-1 桃园地景艺术节 最近桃园在举办桃园地景艺术节,种共有五大主题区, 分别是:黄色小鸭展区,巨型莲花展区,草间点点展区,范姜 古厝展区,新屋水巷展区.那这些景点到底个展览什么呢?让 我们继续看下去 ...... .
-8 炳哥的机器人异想世界 艺术家:郑炳和 作品名称:炳哥的机器人异想世界 作品材质:复合媒材 作品简介: 运用丰富的想像力将废弃的材料一一焊接,组装,彩绘,成功打造有趣的 "铁雕"作品
-10 绿雕塑‧家具植栽 艺术家:周灵芝 作品名称:绿雕塑‧家具植栽 作品材质:废弃家具,各式植栽 作品简介: 以绿的概念为发想所发展出来的一件雕塑地景作品 将旧家具当作容器来想像并进行立体构成 "绿"包含了两层意思:一是"种植"的绿,一是"回收再利用" 将废弃物转化为艺术的环保绿观念
-12 心得感想 经过了这次的参观,我觉得世界上个国家都拥有很有 趣的艺术作品.而且,我学到了一件很重要的事情:艺术 有很多种,不只是在纸上画个画就是艺术.我希望明年可 以再去一次地景艺术节!
-Download ppt "桃园地景艺术节 最近桃园在举办桃园地景艺术节,种共有五大主题区, 分别是:黄色小鸭展区,巨型莲花展区,草间点点展区,范姜 古厝展区,新屋水巷展区.那这些景点到底个展览什么呢?让 我们继续看下去 ...... ."
-热 烈 欢 迎 省厅节能工作考核领导小组 莅临我校检查指导工作 !. 井冈山大学 " 十二五 " 节能工作情况汇报 2015 年公共机构节能工作情况.
-自行车安全. 脚踏自行车安全骑乘 壹,自行车基本结构,车型用途介绍 贰,骑乘前装备及基本的检查 参,脚踏车的定期保养检查 肆,安全骑乘 伍,问题讨论.
-未来百年十大科技预测 资料来自网络 音乐:小奏鸣曲 制作:老头乐 L  在科技日新月异的今天,任何我们觉 得不可能的事物,都有可能变成现实, 就像在 100 年前,当时的人们无法想像 到如今繁荣的互联网一样.那么在接 下来的 100 年内,又有哪些可能会出现 的新科技呢?下面列出了当今科学家.
-公务员面试备考指导 主讲 张小龙. 一,面试备考 一,面试培训与反培训 二,面试看什么资料 关于民族品质 我们的民族一路走来,这旅途之中从未有 过捷径或者妥协,这旅途也不适合胆怯之 人,或者爱安逸胜过爱工作之人,或者单 单追求名利之人.这条路是勇于承担风险 者之路,是实干家,创造者之路.
-4-2 ,聚落的演变 人口的分布 自然环境特性,交通便利性及就业 机会等因素,常影响人们对于居住地点 的选择. 台湾西部地区的平原和盆地,地势 较为低平,开发较早,在肥沃的土壤, 便捷的交通网路等有利的条件下,工商 业往来频繁,人口较为密集.
-电机电子群 培养学生具备电机与电子群共同核心能力,使具备电机与电子領域有关操作,维修,测试,应用等实用专 业技能.并为相关专业領域之学习或高一层级专业知能之进修奠定基础.
-黄山旅游线路设计 小组成员: 杨超 王莉彬 张盛庆.
-台中市103年度建立社区照顾关怀据点 评鉴说明会
-西南交通大学 综合节能改造方案汇报 西南交通大学节能办公室主任 邓双渊 2015年1月8日 北京.
-To make this website work, we log user data and share it with processors. To use this website, you must agree to our Privacy Policy, including cookie policy.</t>
+          <t>发布时间:2025-07-10 22:00:00
+来源:去哪儿网
+本次张家界国家森林公园游全程8小时,覆盖16个核心景点,涉及景区环保车、百龙天梯、索道、步行4种交通方式,所有时间节点精确到分钟,以下为完整记录:
+07:00:从张家界市武陵源区标志门酒店出发,乘坐景区环保车(免费,含门票内)至张家界国家森林公园门票站,车程20分钟,07:20抵达.
+07:20:购买张家界国家森林公园门票(225元/人,含4天有效期),核验身份证+人脸识别,排队20分钟,07:40入园.
+07:40:从门票站出发,步行5分钟至金鞭溪入口(07:45),徒步金鞭溪核心段,耗时40分钟(07:45-08:25)至金鞭岩,停留20分钟(08:25-08:45),观赏金鞭岩、神鹰护鞭奇石.
+08:45:从金鞭岩出发,步行10分钟至紫草潭(08:55),停留10分钟(08:55-09:05),休整5分钟至09:10,前往水绕四门.
+09:10:从紫草潭出发,步行15分钟至水绕四门(09:25),购买百龙天梯票(72元/人,上行),排队10分钟(09:25-09:35),乘坐天梯上行至袁家界,运行2分钟,09:37抵达.
+09:37:从百龙天梯上站出发,乘坐景区环保车至袁家界核心区(09:37-09:52,车程15分钟),步行5分钟至阿凡达“哈利路亚山”(乾坤柱)观景台(09:57),停留30分钟(09:57-10:27),拍摄同款视角,休整至10:30.
+10:30:从乾坤柱出发,步行8分钟至天下第一桥(10:38),停留20分钟(10:38-10:58),观赏天然石桥景观.
+10:58:从天下第一桥出发,乘坐景区环保车至天子山索道下站(10:58-11:28,车程30分钟),购买索道票(72元/人,上行),排队5分钟(11:28-11:33),乘坐索道至天子山,运行10分钟,11:43抵达,休整至12:00.
+12:00:从天子山索道上站出发,步行10分钟至天子山餐厅(12:10),用餐40分钟(12:10-12:50),人均50元(推荐三下锅、葛根粉),休整10分钟至13:00.
+13:00:从天子山餐厅出发,步行5分钟至贺龙公园(13:05),停留25分钟(13:05-13:30),参观贺龙铜像、天子阁.
+13:30:从贺龙公园出发,乘坐景区环保车至十里画廊入口(13:30-13:45,车程15分钟),乘坐十里画廊小火车(38元/人,单程),运行10分钟(13:45-13:55)至终点,步行5分钟至采药老人奇石(14:00),停留25分钟(14:00-14:25),观赏三姐妹峰、食指峰,休整至14:30.
+14:30:从十里画廊出发,乘坐小火车返回入口(14:30-14:40,车程10分钟),乘坐景区环保车返回标志门(14:40-15:10,车程30分钟),步行至酒店(15:10-15:30,步行20分钟),结束行程.
+- 景点POI:金鞭溪、金鞭岩、神鹰护鞭、紫草潭、水绕四门、袁家界、乾坤柱(哈利路亚山)、天下第一桥、天子山、贺龙公园、天子阁、十里画廊、采药老人、三姐妹峰;
+- 交通方式:景区环保车、百龙天梯、天子山索道、十里画廊小火车、步行;
+- 时间节点:07:00(出发)、07:40(入园)、09:10(百龙天梯)、10:30(袁家界)、12:00(午餐)、13:00(天子山)、14:30(返程);
+- 消费实体:森林公园门票225元、百龙天梯72元、天子山索道72元、午餐50元/人、十里画廊小火车38元.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[中国黄山]集天下名山胜景于一身,群峰竞秀,气势磅礡,如梦如幻,宛如仙境. [清境黄山会馆]却随时都可感受到中国黄山般的清境景色,令人叹为观止的山景.清境终年云雾辽绕,是台湾最值得一游的风景名胜之一!
-[清境黄山会馆]山景如画,不论是小家庭或是团体出游,都会是您相当理想的住宿选择;木造客房空间都呈现出素雅禅意的雅致面貌,不只实际住起来舒服,在视觉上也同样营造出极大的舒适感.家庭好友相聚身在自然山景的衬托下,品茗聊天,人显更闲雅,纵使尘嚣有数不尽的烦恼,然~观赏起[清境黄山]的风光,就能彻底放松您的心情!
-[清境黄山会馆]设有多间舒适优质住宿客房,在房型上规划有二人,四人,六人及八人之类型,客房十分舒适宽敞约8-12坪</t>
+          <t>标题:张家界3天2晚
+发布时间:2025-07-10 22:00:00
+来源:去哪儿网
+层级1(整体):2天1晚经典环线
+层级2(核心分段):
+- 第一天:金鞭溪→百龙天梯→袁家界→天子山;
+- 第二天:十里画廊→黄龙洞→返程.
+层级3(子路线):各景点线性串联,无恐高适配、无观景时段建议.
+层级1(整体):3天2晚恐高适配环线(基于官方路线优化,分观景时段+恐高分支)
+层级2(每日结构):核心观景段+休整段+小众恐高分支段
+层级3(时段细分):清晨/上午/中午/下午/傍晚,含停留时长+恐高建议+观景时段.
+层级2-1:核心轻松段(07:00-11:00)
+层级3-1:07:00 张家界门票站入园,步行5分钟至金鞭溪入口(07:05),停留40分钟(07:05-07:45),仅游览金鞭溪平缓段(官方路线无恐高适配);
+层级3-2:07:45-07:55 步行至金鞭岩(10分钟),停留15分钟(07:55-08:10),拍摄金鞭岩地面视角(避开高空);
+层级3-3:08:10-08:25 步行至神鹰护鞭(15分钟),停留20分钟(08:25-08:45),讲解奇石命名由来;
+层级3-4:08:45-09:00 步行至紫草潭(15分钟),停留30分钟(09:00-09:30),长休整(适配恐高游客);
+层级3-5:09:30-09:50 步行至水绕四门(20分钟),停留10分钟(09:50-10:00),放弃百龙天梯(恐高适配);
+层级3-6:10:00-10:20 乘坐景区环保车返回门票站(20分钟),停留40分钟(10:20-11:00),准备午餐.
+层级2-2:休整段(11:00-13:00)
+层级3-1:11:00-11:10 步行至门票站餐厅(10分钟),用餐60分钟(11:10-12:10);
+层级3-2:12:10-13:00 餐厅周边休整(50分钟),体验张家界土家族织锦制作(官方路线无此体验).
+层级2-3:小众恐高分支段(13:00-17:00)
+层级3-1:13:00-13:20 乘坐环保车至腰子寨(20分钟),停留1小时(13:20-14:20),游览腰子寨地面景观(无高空栈道);
+层级3-2:14:20-14:40 乘坐环保车至砂刀沟(20分钟),停留40分钟(14:40-15:20),徒步砂刀沟平缓段;
+层级3-3:15:20-15:40 乘坐环保车返回标志门(20分钟),停留2小时(15:40-17:40),自由休整(恐高适配).
+层级2-1:核心中等适配段(07:00-12:00)
+层级3-1:07:00-07:20 标志门乘坐环保车至十里画廊入口(20分钟),停留5分钟(07:20-07:25);
+层级3-2:07:25-07:35 乘坐十里画廊小火车至终点(10分钟),停留30分钟(07:35-08:05),观赏采药老人、三姐妹峰(地面视角);
+层级3-3:08:05-08:15 乘坐小火车返回入口(10分钟),停留10分钟(08:15-08:25);
+层级3-4:08:25-09:05 乘坐景区大巴至黄龙洞(40分钟),停留5分钟(09:05-09:10);
+层级3-5:09:10-09:20 购买黄龙洞门票(100元/人),排队10分钟(09:20-09:30),入园后步行至黄龙洞洞口(09:30),停留40分钟(09:30-10:10),游览溶洞地面段(无高空);
+层级3-6:10:10-10:40 乘坐黄龙洞游船(30分钟),停留20分钟(10:40-11:00),休整至11:00,准备午餐.
+层级2-2:休整段(11:00-13:00)
+层级3-1:11:00-11:15 步行至黄龙洞餐厅(15分钟),用餐45分钟(11:15-12:00);
+层级3-2:12:00-13:00 餐厅周边休整(60分钟),补充水分(官方路线无补水建议).
+层级2-3:小众分支段(13:00-17:00)
+层级3-1:13:00-13:20 乘坐大巴返回张家界国家森林公园(20分钟),停留30分钟(13:20-13:50);
+层级3-2:13:50-14:10 乘坐环保车至袁家界环保车停靠点(20分钟),停留1小时(14:10-15:10),远观乾坤柱(地面视角,避开高空栈道);
+层级3-3:15:10-17:00 返回标志门,休整+整理照片(1小时50分钟).
+层级2-1:核心补充段(09:00-11:00)
+层级3-1:09:00-09:30 标志门采购张家界特产(30分钟);
+层级3-2:09:30-10:30 参观张家界土家族博物馆(1小时),了解土家族民俗文化(官方路线无文化体验);
+层级3-3:10:30-11:00 整理行李、返程准备(30分钟).
+1. 官方路线:线性层级(整体→每日→景点),无恐高分级、无长休整、无民俗体验;
+2. 实际路线:恐高适配层级(整体→每日恐高段→核心/休整/小众→时段/恐高建议),按恐高程度分级设计路线,增加小众地面景观和民俗文化体验,适配不同游客.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>明朝旅行家徐霞客登临黄山时赞叹:
-"薄海内外之名山,无如徽之黄山.登黄山,天下无山,观止矣!"
-黄山,中华十大名山之一,天下第一奇山.
-后因传说轩辕黄帝曾在此炼丹,故改名为"黄山".
-黄山独有的五绝,让黄山无时无刻不散发神秘魅力.
-这五绝分别是:奇松,怪石,云海,温泉和冬雪.
-宏村有"画里乡村"之称.
-徽派建筑集徽州山川风景之灵气,融中国风俗文化之精华,风格独特,结构严谨,雕镂精湛.
-宏村之美,美在安宁幽静.
-宏村之美,美在徽派建筑.
-宏村之美,更美在自身文化底蕴.
-自组线路黄山,宏村,卡巴乐谷纯玩三日游
-行程特色:
-含2早2正餐;全程纯玩不进店.
-游卡巴乐峡谷 - - 远眺黄山之巅,特别赠送野人表演游世界文化与自然遗产 - - 黄山全景,欣赏奇松怪石,特别赠送黄山上下景交游览中国最美的乡村 - - 宏村.
-体验博大精深的徽州文化.
-报价(满30人发班)
-成人:998元/人
-2,门票:以上所列景点首道大门票 (含卡巴乐峡谷,宏村,黄山门票)
-(不含黄山景区交通19元/趟*2趟;黄山索道:云谷索道80元/人或玉屏索道90元/人自理;不含玻璃栈道78元/人自理)
-4,住宿:山下两晚商务酒店标准间(补单房差加160元/人/天×2天)
-6,保险:旅行社责任险,建议购买旅游意外险20元/人</t>
+          <t>07:00 从标志门出发,乘坐景区环保车前往金鞭溪入口,车程20分钟.抵达后,我先走进金鞭溪,这里的空气很清新,负氧离子含量高,它的温度比市区低5℃,和其他景区不同,它的体感更凉爽.
+07:30 走到金鞭岩,它是金鞭溪的标志性奇石,这里的形状像一根金鞭,它的高度有380米,和其他奇石不同,它的颜色是浅褐色,在阳光下会泛金光.金鞭岩的对面是神鹰护鞭,它的形状像一只老鹰,这里的游客都会拍它的合影,因为它的造型很逼真,它的翅膀仿佛要展开.
+08:00 从金鞭岩走到紫草潭,它是金鞭溪的水潭,这里的水是碧绿色的,它的深度有2米,和其他水潭不同,它的水底能看到小鱼.坐在紫草潭的石头上,脚伸进水里,它的水温很凉,要是你夏天来,一定要体验它的清凉,它的解暑效果很好.
+08:30 从紫草潭走到水绕四门,它是金鞭溪的终点,这里的四条溪流交汇,它的名字由此而来,和其他地段不同,它的视野更开阔.水绕四门的旁边是百龙天梯,它是世界最高的户外电梯,这里的运行高度有335米,它的速度很快,66秒就能到顶,要是你恐高,不建议坐它.
+09:00 乘坐百龙天梯至袁家界,它的轿厢是透明的,坐在里面能看到外面的山峰,这里的山峰是张家界的特色,它的形状是柱状的,和其他山脉不同,它的山峰更陡峭.抵达袁家界,走到乾坤柱,它是阿凡达“哈利路亚山”的原型,这里的高度有150米,它的周围有云海(雨后),要是你运气好,能看到它的云海环绕.
+09:40 从乾坤柱走到天下第一桥,它是天然石桥,这里的跨度有20米,它的高度有350米,和其他石桥不同,它的桥面是天然形成的.走在天下第一桥上,它的护栏是铁制的,这里的风很大,吹得护栏晃动,要是你恐高,不要靠近它的边缘,它的下面是万丈深渊.
+10:20 从天下第一桥乘坐环保车至天子山,车程30分钟.抵达后,走到贺龙公园,它是纪念贺龙元帅的公园,这里的贺龙铜像有6米高,它的材质是青铜,和其他铜像不同,它的造型更威武.贺龙公园的旁边是天子阁,它是天子山的观景台,这里的视野无遮挡,能看到它的上千座山峰,它的景色比袁家界更壮观.
+11:00 从天子阁走到餐厅,这里的主打菜是三下锅,它的食材有腊肉、豆腐、土豆,和其他地方的三下锅不同,它的口味更重,辣味更足.吃完饭休息了一会儿,走到餐厅外的特产店,这里的葛根粉是张家界的特产,它的口感很细腻,和其他葛根粉不同,它的纯度更高,要是你想买特产,它是不错的选择.
+11:40 从特产店乘坐环保车至十里画廊,车程15分钟.抵达后,乘坐十里画廊小火车,它的轨道沿山谷修建,这里的车速很慢,能欣赏沿途的奇石,它的主要景点有采药老人、三姐妹峰,和其他山谷不同,它的奇石造型更生动.
+12:10 走到采药老人奇石旁,它的形状像一位采药的老人,这里的细节很逼真,它的手里仿佛拿着药篓,和其他奇石不同,它的辨识度更高.三姐妹峰在采药老人的西侧,它的三座山峰连在一起,它的传说和土家族的三姐妹有关,这里的游客都会听它的故事,它的故事很感人.
+12:40 从十里画廊返回标志门,乘坐环保车至酒店,车程20分钟.回到酒店,回顾当天的行程,张家界的美在于它的奇特,这里的每一座山峰都有造型,它的自然景观独一无二,要是你没来过,一定要来感受一下它的震撼.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2020年黄山哪些山峰景点封闭着?哪些山峰又是开放的呢?
-本文标题:2020年黄山哪些山峰景点封闭着?哪些山峰又是开放的呢?
-二,西海大峡谷2020年封闭部分:从排云溪站起,与地轨轨道重合,一直到地轨中间站,过山洞到大峡谷服务站,最后到步仙桥石柱峰之间悬壁栈道被封闭.
-三,狮子峰顶望仙台(2020年封闭)
-玉屏峰(含文殊台,立雪台),莲花峰,莲花亭,百步云梯,鳌鱼峰,石床峰,石柱峰,光明顶,炼丹峰,平天矼,群峰顶,仙桃峰,排云亭,松林峰,丹霞峰,狮子峰(含清凉台,曙光亭,猴子海,除望仙台),散花坞观景台,始信峰,卧云峰,探海松观景台,石笋矼,贡阳山,白鹅岭等.
-西海大峡谷:北入口经三溪口,步仙桥到天海全程游览步道和排云溪站到天海地轨缆车.
-黄山风景区核心景区外围的一些山峰,驴友可以攀登的比如浮丘峰,云门峰,五老峰,轩辕峰,夫子峰,探头峰等不包括在内.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>应急救援不是给违规者兜底的无偿服务
-尽管政府或者景区管理方有法定救助的义务,但驴友们却不应该以此作为任性探险的倚仗.
--------------------------------------------------
-近日,据黄山风景区消息,该景区今年将启动有偿救援,对违规逃票私自进入或不听劝阻擅自进入未开发开放区域,陷入困顿或危险状态等情形求救的游客或驴友,将由旅游活动组织者及被救助人承担相应救援费用.("安徽日报"2月5日)
-其实,有偿搜救早不是什么新鲜事.早在黄山景区之前,就有一些地方试行过,但无一例外地在推出后饱受争议.不少人都认为:"公民遇险获得救助,是一项基本人权,景区作为营利机构,有责任对游客负责,包括支付搜救费用."于是,景区该不该救援,救援费用该由谁来承担,就成了一道"生命选择题".
-目前,舆论对此存在种种误解.比如,有人错把景区责任当作义务,认为救援属于公共服务,不该区分有偿无偿.这样的观点,其实是在偷换概念.因为,收费只是限制性的补充规则,目的是希望游客可以按照景区规定合理游玩.既然游客自行进山,冒险游玩,那么就必须承担相应后果.政府或者景区对驴友所提供的"应急救援"公共服务,建立在他们合理使用公共资源的基础上,面对那些逃票和私自闯入的人员,就应该采用"有章可循"和"后果自负"的方法.
-面对越来越多盲目,任性的驴友,有偿救援是大势所趋.首先,通过有偿的方式,至少能够起到一定的警示作用,让一些脑子发热的驴友有一定的顾虑,让他们注意到法律规定,意识到违规探险不再有公共部门的无偿兜底.其次,实行有偿救援的目的主要是为了警示非法穿越者,通过收费来提高驴友们的违规成本.
-尽管政府或者景区管理方有法定救助的义务,但驴友们却不应该以此作为任性探险的倚仗.可以说,有偿救援的本质,正是将搜救工作的风险和经济成本,通过市场化手段合理分摊.在某种程度上,可以进一步厘清公私关系,划分权责,不让公共资源为个人的任性和违规埋单.当然,收费也应该坚持"参照成本,酌情收取"的原则,避免救援走向"变相牟利,营利"的极端.
-一起又一起的"驴友悲剧"足够证明,规则的目的向来都是保护愿意遵循规则的人,而不能迁就那些"明知山有虎,偏向虎山行"的人.与其讨论救援是否有偿,不如让更多人看到遵守规则的重要性和必要性,尽可能地阻止游客违规进入,而非事后救援.宋潇</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>近日,安徽黄山市文化和旅游局发布关于"黄山市山岳型景区有偿救援指导意见"征求意见函,对于旅游者不遵守黄山市旅游景区游览规定,擅自进入未开发,未开放区域陷入困顿或危险状态,属地政府完成救援后,由旅游活动组织者及被救助人承担相应救援费用的活动.该征求意见函在网上引起了不少.
-北京青年报记者了解到,"黄山风景名胜区有偿救援实施办法"已于2018年7月1日起施行,此次有偿救援的征求意见是扩展到黄山全市山岳型景区.
-近年来,多起"驴友"擅自进入未开发区域遇险事件引起,多地也已经陆续发布关于有偿救援的相关办法.律师表示,有偿救援利于约束"驴友"遵守相应规则,建议细化相应的应用范围,以方便司法实践.
-据征求意见显示,有偿救援是指旅游者不遵守黄山市旅游景区游览规定,擅自进入未开发,未开放区域陷入困顿或危险状态,属地政府完成救援后,由旅游活动组织者及被救助人承担相应救援费用的活动.旅游者在黄山风景名胜区,牯牛降景区等山岳型景区游览,陷入困顿或危险状态的,属地政府应当组织实施救援.
-有偿救援费用包含救援过程中产生的劳务,院前救治,交通,意外保险,后勤保障,引入第三方救援力量等费用.救援人员劳务费用按照救援人员工资和实际救援时间确定.院前救治,交通,意外保险,后勤保障,第三方救援等费用的产生,应当同当次救援活动具有因果关系.
-属地政府在有偿救援结束后15个工作日内,完成对救援费用的审议核定;20个工作日内,向旅游活动组织者及被救助人送达"支付有偿救援费用通知书",包括收费项目明细,付款期限,付款方式,收款账号等信息.送达方式参照"民事诉讼法"有关规定执行.
-6月15日,北京青年报记者咨询了黄山市文旅局,相关工作人员称,现在有一些"驴友"没有购买门票到一些未开发区域旅游,为了预防并且制止这种行为,文旅局会同其他部门拟定了这一意见,这次有偿救援的范围拟扩至黄山市全境范围.据工作人员介绍,征求意见截止时间为6月30日,市民有意见的话都可以通过电子邮件或者邮寄的方式反馈给文旅局.
-近年来,"驴友"擅自进入未开发区域后遇险的事件曾多次发生,为此多地相继出台了有关有偿救援的相关办法规定.
-据安徽当地媒体报道,在黄山风景区实施有偿救援办法后,2019年6月,游客王某某私自穿过景区铁丝网进入朱砂峰被困.朱砂峰属于未开发区域,岩壁非常光滑,救援人员经过两个小时才用绳索将王某某救出.依据"黄山风景名胜区有偿救援实施办法",黄山景区认定此次救援符合"有偿救援"规定,向王某某追讨救援费用.6月18日,王某某的亲属代其将3206元救援费汇入黄山风景区管委会指定账户.
-2018年9月,四姑娘山景区管理局出台"四姑娘山景区山地户外运动突发事件有偿救援管理办法".2019年8月12日,周某违规穿越四姑娘山后受伤失联,8月13日上午,景区管理局接到家属消息后立即派出救援团队,历经36个小时救出该男子.除了被罚款2000元外,周某还自行承担救援费用3000元.
-2018年8月,稻城亚丁发布有偿搜救制度,适用于亚丁景区范围内非法登山,非法穿越等户外活动及未按规定线路,区域旅游而发生事故的人员.公告中还发布了搜救路线及搜救费用,其中亚丁村,叶儿红村至康古贡嘎银河区域,搜救费用1.5万起,其他四条路线搜救费用均为2万元起.
-6月15日,陕西恒达律师事务所高级合伙人,公益律师赵良善表示,对黄山开展有偿救援持支持态度.虽然政府有专门用于保护公民安全的经费,救援单位也有用于救援的资金,但是如果公民不听劝阻,恶意违反规定导致救援的,无疑加重了国家负担.而有偿救援,让违规甚至违法的被救助者承担经济责任,将利于约束"驴友"遵守相应规则,爱护自己生命,并对自身行为产生的后果担责.
-赵良善说,但是另一方面,也要警惕乱收费的情况.如果增加付费救助,则意味着给法定义务赋予了条件,或者开了付费救助的口子,日后可能会造成争议或者乱收费的情况.同时也要判断救助者是恶意还是善意前往未开发区,比如有些人可能真的迷路了,对于这类孤立无援的人员救助收费会背离救助的初衷.</t>
+          <t>1. 如果选择节假日游览西湖,建议提前预约热门景点(如雷峰塔、三潭印月),因为节假日这些景点的限流名额会在1小时内约满,现场无法入园;
+2. 要是带老人/小孩游览,不建议选择全程骑行路线,除非老人/小孩能连续骑行1小时以上,否则建议租用观光电瓶车(60元/人),西湖环湖全程15公里,无连续平路;
+3. 如果打算拍摄西湖荷花,建议选择7-8月的清晨6点前前往,因为夏季清晨荷花盛开且人流少,要是上午10点后,荷花会闭合且游客扎堆;
+4. 要是携带摄影器材,建议准备偏振镜(消除水面反光),除非你只想拍常规照片,否则偏振镜能提升湖面倒影的拍摄效果;
+5. 除非你对西湖十景的历史特别了解,否则建议下载“西湖旅游”APP听免费讲解,西湖的人文故事仅靠看无法体会.
+二、游览途中条件建议
+1. 如果从湖滨前往断桥,建议骑行共享单车(哈啰/美团),要是赶时间,可乘坐地铁1号线至龙翔桥站,除非你想步行欣赏湖滨风光;
+2. 要是想拍摄无人的三潭印月,建议选择早班游船(7:00),因为旅行团会在9点后集中登岛,此时拍摄会有大量人群入镜;
+3. 如果游览苏堤,建议选择春季(3-4月)的上午9点前,除非你想拍秋季的桂花,否则春季苏堤春晓的景观最佳;
+4. 要是遇到西湖游船临时停运(如大风),建议调整游览顺序,优先游览雷峰塔/花港观鱼,除非游船是你的核心体验项目;
+5. 如果在西湖内用餐,建议选择知味观/楼外楼等老字号,要是想节省费用,可选择湖滨银泰的平价餐厅,西湖景区内的餐厅人均比市区贵30%;
+6. 要是体能不足,建议放弃苏堤全程徒步,前提是你已游览苏堤前两桥,否则会错过苏堤核心景观.
+三、文创与体验条件建议
+1. 如果想购买西湖文创产品,建议在西湖博物馆文创店购买,因为这里的文创有西湖文化IP认证,要是买低价仿品,工艺和设计都差很多;
+2. 要是想体验西湖龙井茶炒制,建议提前联系龙井村的茶农预约,除非你只是想观看,否则炒制体验需要提前1天预约;</t>
         </is>
       </c>
     </row>
